--- a/需求整理/industry_indicator_system.xlsx
+++ b/需求整理/industry_indicator_system.xlsx
@@ -4,15 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Industry Indicators" sheetId="1" r:id="rId1"/>
     <sheet name="指标整理" sheetId="2" r:id="rId2"/>
     <sheet name="需求1—主线板块确认" sheetId="5" r:id="rId3"/>
-    <sheet name="需求1-产品文档" sheetId="3" r:id="rId4"/>
-    <sheet name="报表2—主线板块龙头" sheetId="4" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="6" r:id="rId6"/>
+    <sheet name="报表2—主线板块龙头" sheetId="4" r:id="rId4"/>
+    <sheet name="需求3—量化主线板块" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="562">
   <si>
     <t>指标名称</t>
   </si>
@@ -572,6 +571,9 @@
 | 预期  | 还很高 |</t>
   </si>
   <si>
+    <t>资金 + 价格 + 量能 + 位置</t>
+  </si>
+  <si>
     <t>Sheet 1: 主线板块量化逻辑总览</t>
   </si>
   <si>
@@ -630,6 +632,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>主线得分公式</t>
     </r>
     <r>
@@ -812,6 +821,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>主线等级标准</t>
     </r>
     <r>
@@ -1108,6 +1124,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t xml:space="preserve">1. </t>
     </r>
     <r>
@@ -1228,6 +1251,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>2. 行业指数 (</t>
     </r>
     <r>
@@ -1283,6 +1313,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>行业指数 (</t>
     </r>
     <r>
@@ -1308,6 +1345,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>行业资金流 (</t>
     </r>
     <r>
@@ -1369,6 +1413,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>涨停数据 (</t>
     </r>
     <r>
@@ -1424,6 +1475,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t>机构预期 (</t>
     </r>
     <r>
@@ -1473,6 +1531,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14.05"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t> </t>
     </r>
     <r>
@@ -1584,6 +1649,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="14.05"/>
+        <color rgb="FF060A26"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
       <t> </t>
     </r>
     <r>
@@ -1700,25 +1772,298 @@
     <t>iFinD, Choice</t>
   </si>
   <si>
-    <t>电网设备</t>
-  </si>
-  <si>
-    <t>半导体设备材料</t>
-  </si>
-  <si>
-    <t>有色/化工</t>
-  </si>
-  <si>
-    <t>机器人</t>
-  </si>
-  <si>
-    <t>其他</t>
-  </si>
-  <si>
-    <t>海外</t>
-  </si>
-  <si>
-    <t>恒生科技</t>
+    <t>交易日期</t>
+  </si>
+  <si>
+    <t>热点股票</t>
+  </si>
+  <si>
+    <t>是否龙头</t>
+  </si>
+  <si>
+    <t>重点介绍</t>
+  </si>
+  <si>
+    <t>一、Excel 整体结构建议（三层系统）</t>
+  </si>
+  <si>
+    <t>工作表名称</t>
+  </si>
+  <si>
+    <t>功能说明</t>
+  </si>
+  <si>
+    <t>01_原始数据</t>
+  </si>
+  <si>
+    <t>存放每日各行业（申万一级/二级）原始指标</t>
+  </si>
+  <si>
+    <t>02_因子计算</t>
+  </si>
+  <si>
+    <t>计算 F/T/E/L/P 各子因子和主因子</t>
+  </si>
+  <si>
+    <t>03_MainScore</t>
+  </si>
+  <si>
+    <t>汇总 MainScore 并排序，生成 Top3 主线池</t>
+  </si>
+  <si>
+    <t>04_信号判断</t>
+  </si>
+  <si>
+    <t>判断“启动”或“退潮”信号（布尔值）</t>
+  </si>
+  <si>
+    <t>05_参数配置</t>
+  </si>
+  <si>
+    <t>存放权重（如 0.3F+0.3T...）、阈值（如 RS&gt;1.2）等可调参数</t>
+  </si>
+  <si>
+    <t>关键字段与公式映射（按你的模型）</t>
+  </si>
+  <si>
+    <t>资金强度 F = 0.4A + 0.3V + 0.2ETF + 0.1H</t>
+  </si>
+  <si>
+    <t>计算方式</t>
+  </si>
+  <si>
+    <t>数据来源建议</t>
+  </si>
+  <si>
+    <t>A（成交额占比）</t>
+  </si>
+  <si>
+    <t>行业当日成交额 / 全A成交额</t>
+  </si>
+  <si>
+    <t>Wind / Tushare / 聚宽</t>
+  </si>
+  <si>
+    <t>V（成交额增速）</t>
+  </si>
+  <si>
+    <t>MA5(行业成交额) / MA20(行业成交额)</t>
+  </si>
+  <si>
+    <t>需滚动计算</t>
+  </si>
+  <si>
+    <t>ETF（ETF净流入强度）</t>
+  </si>
+  <si>
+    <t>行业相关ETF近5日净流入 / ETF总规模</t>
+  </si>
+  <si>
+    <t>需维护行业-ETF映射表（如芯片ETF→半导体）</t>
+  </si>
+  <si>
+    <t>H（换手活跃度）</t>
+  </si>
+  <si>
+    <t>行业平均换手率 / 全市场平均换手率</t>
+  </si>
+  <si>
+    <t>注意剔除新股/ST</t>
+  </si>
+  <si>
+    <t>2. 趋势强度 T = 0.4RS + 0.3N + 0.2R + 0.1M</t>
+  </si>
+  <si>
+    <t>RS（相对强度）</t>
+  </si>
+  <si>
+    <t>行业20日收益率 / 全A（如沪深300）20日收益率</t>
+  </si>
+  <si>
+    <t>N（创新高比例）</t>
+  </si>
+  <si>
+    <t>行业内近1年新高个股数 / 行业总股数</t>
+  </si>
+  <si>
+    <t>R（回撤修复速度）</t>
+  </si>
+  <si>
+    <t>最近一次回撤天数 / 修复至前高的天数（越小越好 → 取倒数或标准化）</t>
+  </si>
+  <si>
+    <t>M（均线斜率）</t>
+  </si>
+  <si>
+    <t>对MA30做线性回归，取斜率（可用SLOPE函数）</t>
+  </si>
+  <si>
+    <t>3. 情绪扩散 E = 0.35Z + 0.25J + 0.2B + 0.2U</t>
+  </si>
+  <si>
+    <t>Z（涨停扩散率）</t>
+  </si>
+  <si>
+    <t>行业涨停数 / 行业总股数</t>
+  </si>
+  <si>
+    <t>J（晋级率）</t>
+  </si>
+  <si>
+    <t>昨日涨停今日继续涨停数 / 昨日涨停总数</t>
+  </si>
+  <si>
+    <t>B（炸板率反向）</t>
+  </si>
+  <si>
+    <t>1 - （炸板数 / 触板数）→ 炸板越少越好</t>
+  </si>
+  <si>
+    <t>U（上涨扩散）</t>
+  </si>
+  <si>
+    <t>行业上涨个股数 / 总股数</t>
+  </si>
+  <si>
+    <t>4. 龙头强度 L = 0.5LR + 0.3LC + 0.2LP</t>
+  </si>
+  <si>
+    <t>LR（龙头超额收益）</t>
+  </si>
+  <si>
+    <t>龙头股20日收益 - 沪深300同期收益</t>
+  </si>
+  <si>
+    <t>LC（连板高度）</t>
+  </si>
+  <si>
+    <t>行业内最高连板数（如 5 连板）</t>
+  </si>
+  <si>
+    <t>LP（龙头溢价）</t>
+  </si>
+  <si>
+    <t>龙头股次日平均开盘/收盘涨幅（需历史回测统计）</t>
+  </si>
+  <si>
+    <t>5. 产业景气 P = 0.5Earnings + 0.3Policy + 0.2Forecast</t>
+  </si>
+  <si>
+    <t>实操建议</t>
+  </si>
+  <si>
+    <t>Earnings</t>
+  </si>
+  <si>
+    <t>行业一致预期净利润增速（可用 Wind 一致预期）</t>
+  </si>
+  <si>
+    <t>Policy</t>
+  </si>
+  <si>
+    <t>政策热度（可人工打分 0-1，或用 NLP 抓新闻关键词）</t>
+  </si>
+  <si>
+    <t>Forecast</t>
+  </si>
+  <si>
+    <t>机构上调评级比例 / 行业研报数量月环比</t>
+  </si>
+  <si>
+    <t>三、MainScore 计算（核心）</t>
+  </si>
+  <si>
+    <t>MainScore = $F$权重 * F标准化值 + $T$权重 * T标准化值 + $E$权重 * E标准化值 + $L$权重 * L标准化值 + $P$权重 * P标准化值</t>
+  </si>
+  <si>
+    <t>四、实战信号判断（04_信号判断）</t>
+  </si>
+  <si>
+    <t>信号类型</t>
+  </si>
+  <si>
+    <t>判断条件（AND）</t>
+  </si>
+  <si>
+    <t>主线启动</t>
+  </si>
+  <si>
+    <t>RS &gt; 1.2</t>
+  </si>
+  <si>
+    <t>A 连续3日上升</t>
+  </si>
+  <si>
+    <t>Z &gt; 1.5 × 全市场平均Z</t>
+  </si>
+  <si>
+    <t>龙头创新高</t>
+  </si>
+  <si>
+    <t>R ≤ 3（3日内修复）</t>
+  </si>
+  <si>
+    <t>主线退潮</t>
+  </si>
+  <si>
+    <t>RS &lt; 0.9</t>
+  </si>
+  <si>
+    <t>A 连续2日下降</t>
+  </si>
+  <si>
+    <t>龙头出现“A杀”（-7%以上）</t>
+  </si>
+  <si>
+    <t>B（炸板率）&gt; 40%</t>
+  </si>
+  <si>
+    <t>五、最终输出建议</t>
+  </si>
+  <si>
+    <t>每天收盘后运行，输出：</t>
+  </si>
+  <si>
+    <t>Top3 主线行业</t>
+  </si>
+  <si>
+    <t>是否触发启动/退潮信号</t>
+  </si>
+  <si>
+    <t>各因子雷达图（可视化）</t>
+  </si>
+  <si>
+    <t>数据获取建议（免费/低成本）</t>
+  </si>
+  <si>
+    <t>数据项</t>
+  </si>
+  <si>
+    <t>工具</t>
+  </si>
+  <si>
+    <t>行业行情、成分股</t>
+  </si>
+  <si>
+    <t>Tushare Pro（免费额度够用）</t>
+  </si>
+  <si>
+    <t>涨停/炸板数据</t>
+  </si>
+  <si>
+    <t>Tushare limit_list 或 AKShare</t>
+  </si>
+  <si>
+    <t>ETF资金流</t>
+  </si>
+  <si>
+    <t>东方财富网 / 集思录（需爬虫）</t>
+  </si>
+  <si>
+    <t>一致预期</t>
+  </si>
+  <si>
+    <t>如果无Wind，可用“过去4季度净利润增速”替代</t>
   </si>
 </sst>
 </file>
@@ -1731,7 +2076,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1740,11 +2085,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14.05"/>
-      <color rgb="FF060A26"/>
-      <name val="Segoe UI"/>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1756,8 +2100,21 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="18"/>
       <color rgb="FF060A26"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14.05"/>
+      <color rgb="FF060A26"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF222325"/>
       <name val="Segoe UI"/>
       <charset val="134"/>
     </font>
@@ -1768,10 +2125,11 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="宋体"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF060A26"/>
+      <name val="Segoe UI"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -1926,16 +2284,16 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10.5"/>
       <color rgb="FF060A26"/>
-      <name val="宋体"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
+      <sz val="12"/>
       <color rgb="FF060A26"/>
-      <name val="Consolas"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1948,6 +2306,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1955,12 +2319,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2327,140 +2685,241 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2468,112 +2927,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2939,273 +3294,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="42" t="s">
+      <c r="D2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="16" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="16" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:6">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B6" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="16" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="42" t="s">
+      <c r="F9" s="16" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="42" t="s">
+      <c r="A10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="F10" s="16" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="16" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="42" t="s">
+      <c r="A12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="42" t="s">
+      <c r="D12" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="16" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="42" t="s">
+      <c r="A13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="16" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" ht="100.8" spans="1:6">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="38" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="38" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3230,473 +3585,473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="42" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="38"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2" ht="115.2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="43"/>
+      <c r="F2" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="38" t="s">
+      <c r="G2" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" ht="273.6" spans="1:7">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2" t="s">
+      <c r="A3" s="43"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2" t="s">
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="43"/>
+      <c r="F4" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="38" t="s">
+      <c r="G4" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="2" t="s">
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="38"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2" t="s">
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="38"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" ht="72" spans="1:7">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="2" t="s">
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="38"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="43"/>
+      <c r="B8" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="38"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="s">
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="38"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="s">
+      <c r="A10" s="43"/>
+      <c r="B10" s="43"/>
+      <c r="C10" s="43"/>
+      <c r="D10" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="38"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" ht="57.6" spans="1:7">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="s">
+      <c r="A11" s="43"/>
+      <c r="B11" s="43"/>
+      <c r="C11" s="43"/>
+      <c r="D11" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="38"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="43"/>
+      <c r="B12" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="43" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="38"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="s">
+      <c r="A13" s="43"/>
+      <c r="B13" s="43"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="38"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="43"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" ht="43.2" spans="1:7">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="s">
+      <c r="A14" s="43"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="38"/>
+      <c r="F14" s="43"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" ht="57.6" spans="1:7">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
+      <c r="A15" s="43"/>
+      <c r="B15" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="39" t="s">
+      <c r="C15" s="43"/>
+      <c r="D15" s="45" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="38"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="38"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="s">
+      <c r="A17" s="43"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="38"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2" t="s">
+      <c r="A18" s="43"/>
+      <c r="B18" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="39"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="38"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2" t="s">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="38"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="43"/>
+      <c r="B20" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="38"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2" t="s">
+      <c r="A21" s="43"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="38"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" ht="72" spans="1:7">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2" t="s">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2" t="s">
+      <c r="D22" s="43"/>
+      <c r="E22" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="38"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="38"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2" t="s">
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="38"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" ht="43.2" spans="1:7">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="3" t="s">
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2" t="s">
+      <c r="D25" s="43"/>
+      <c r="E25" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="38"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2" t="s">
+      <c r="A26" s="43"/>
+      <c r="B26" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="38"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2" t="s">
+      <c r="A27" s="43"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="43" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="38"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="4"/>
     </row>
     <row r="28" ht="43.2" spans="1:7">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="3" t="s">
+      <c r="A28" s="43"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2" t="s">
+      <c r="D28" s="43"/>
+      <c r="E28" s="43" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="38"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="4"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2" t="s">
+      <c r="A29" s="43"/>
+      <c r="B29" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C29" s="44" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="43" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="38"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="44"/>
+      <c r="G29" s="4"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="3" t="s">
+      <c r="A30" s="43"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="38"/>
+      <c r="E30" s="43"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" ht="43.2" spans="1:7">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="3" t="s">
+      <c r="A31" s="43"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="44" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="39"/>
-      <c r="E31" s="2" t="s">
+      <c r="D31" s="45"/>
+      <c r="E31" s="43" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="38"/>
+      <c r="F31" s="44"/>
+      <c r="G31" s="4"/>
     </row>
     <row r="32" ht="57.6" spans="1:7">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3" t="s">
+      <c r="A32" s="43"/>
+      <c r="B32" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="2" t="s">
+      <c r="D32" s="45"/>
+      <c r="E32" s="43" t="s">
         <v>148</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="38"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="4"/>
     </row>
     <row r="33" ht="158.4" spans="1:7">
-      <c r="A33" s="39" t="s">
+      <c r="A33" s="45" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="26" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="40" t="s">
+      <c r="D33" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="40"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="38"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3727,7 +4082,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I214"/>
+  <dimension ref="A1:I215"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="42.2222222222222" customWidth="1"/>
@@ -3736,1832 +4091,1837 @@
     <col min="4" max="4" width="29.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.4" spans="1:4">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="8" t="s">
+    </row>
+    <row r="2" ht="20.4" spans="1:4">
+      <c r="A2" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="3" ht="28.8" spans="1:4">
-      <c r="A3" s="9" t="s">
+      <c r="D3" s="9" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" ht="28.8" spans="1:4">
+      <c r="A4" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" s="10">
+      <c r="B4" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="19">
         <v>0.35</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="4" ht="28.8" spans="1:4">
-      <c r="A4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="9" t="s">
+    </row>
+    <row r="5" ht="28.8" spans="1:4">
+      <c r="A5" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="10">
+      <c r="B5" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="19">
         <v>0.25</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="5" ht="28.8" spans="1:4">
-      <c r="A5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B5" s="9" t="s">
+    </row>
+    <row r="6" ht="28.8" spans="1:4">
+      <c r="A6" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="10">
+      <c r="B6" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C6" s="19">
         <v>0.15</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B6" s="9" t="s">
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C6" s="10">
+      <c r="B7" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="19">
         <v>0.15</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="9" t="s">
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="10">
+      <c r="B8" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="19">
         <v>0.1</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" ht="15.6" spans="1:4">
-      <c r="A9" s="11" t="s">
+      <c r="D8" s="10" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="10" ht="19.2" spans="1:4">
-      <c r="A10" s="12" t="s">
+    <row r="10" ht="15.6" spans="1:4">
+      <c r="A10" s="20" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="13" t="s">
+    <row r="11" ht="19.2" spans="1:4">
+      <c r="A11" s="21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="14" t="s">
+      <c r="B13" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="C13" s="7" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="13" ht="28.8" spans="1:4">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16" t="s">
+      <c r="D13" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C13" s="16" t="s">
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="23"/>
+      <c r="B14" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="C14" s="8" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="14" ht="28.8" spans="1:4">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16" t="s">
+      <c r="D14" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="C14" s="16" t="s">
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="23"/>
+      <c r="B15" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="C15" s="8" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="15" ht="28.8" spans="1:4">
-      <c r="A15" s="17"/>
-      <c r="B15" s="16" t="s">
+      <c r="D15" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C15" s="16" t="s">
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="24"/>
+      <c r="B16" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="C16" s="8" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C17" s="14" t="s">
+      <c r="D16" s="8" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="C18" s="7" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="15"/>
-      <c r="B18" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="D18" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="23"/>
+      <c r="B19" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="C19" s="8" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16" t="s">
+      <c r="D19" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C19" s="16" t="s">
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="23"/>
+      <c r="B20" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="C20" s="8" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="17"/>
-      <c r="B20" s="16" t="s">
+      <c r="D20" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="C20" s="16" t="s">
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="24"/>
+      <c r="B21" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="C21" s="8" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="C23" s="18" t="s">
+      <c r="D21" s="8" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="C24" s="25" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="15"/>
-      <c r="B24" s="19" t="s">
-        <v>195</v>
-      </c>
-      <c r="C24" s="19" t="s">
+      <c r="D24" s="25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="23"/>
+      <c r="B25" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="C25" s="26" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="15"/>
-      <c r="B25" s="19" t="s">
+      <c r="D25" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C25" s="19" t="s">
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="23"/>
+      <c r="B26" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="C26" s="26" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="17"/>
-      <c r="B26" s="19" t="s">
+      <c r="D26" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="C26" s="19" t="s">
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="24"/>
+      <c r="B27" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="C27" s="26" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" s="20" t="s">
+      <c r="D27" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="B28" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="C28" s="21" t="s">
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="B29" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="C29" s="28" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="20"/>
-      <c r="B29" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="C29" s="22" t="s">
+      <c r="D29" s="28" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="27"/>
+      <c r="B30" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="C30" s="26" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="20"/>
-      <c r="B30" s="22" t="s">
+      <c r="D30" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="C30" s="22" t="s">
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="27"/>
+      <c r="B31" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="C31" s="26" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="23" t="s">
+      <c r="D31" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="C32" s="14" t="s">
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="C33" s="7" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="23"/>
-      <c r="B33" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="C33" s="16" t="s">
+      <c r="D33" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="29"/>
+      <c r="B34" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="C34" s="8" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" s="23"/>
-      <c r="B34" s="16" t="s">
+      <c r="D34" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="C34" s="16" t="s">
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="29"/>
+      <c r="B35" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="D34" s="16" t="s">
+      <c r="C35" s="8" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="37" ht="20.4" spans="1:4">
-      <c r="A37" s="24" t="s">
+      <c r="D35" s="8" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
-      <c r="A39" s="14" t="s">
+    <row r="38" ht="20.4" spans="1:4">
+      <c r="A38" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="B39" s="14" t="s">
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="7" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="40" ht="28.8" spans="1:4">
-      <c r="A40" s="16" t="s">
+      <c r="B40" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="B40" s="16" t="s">
+    </row>
+    <row r="41" ht="28.8" spans="1:4">
+      <c r="A41" s="8" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="41" ht="28.8" spans="1:4">
-      <c r="A41" s="16" t="s">
+      <c r="B41" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="B41" s="16" t="s">
+    </row>
+    <row r="42" ht="28.8" spans="1:4">
+      <c r="A42" s="8" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="42" ht="28.8" spans="1:4">
-      <c r="A42" s="16" t="s">
+      <c r="B42" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="B42" s="16" t="s">
+    </row>
+    <row r="43" ht="28.8" spans="1:4">
+      <c r="A43" s="8" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" s="16" t="s">
+      <c r="B43" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="B43" s="16" t="s">
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44" s="8" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="46" ht="15.6" spans="1:4">
-      <c r="A46" s="11" t="s">
+      <c r="B44" s="8" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="14" t="s">
+    <row r="47" ht="15.6" spans="1:4">
+      <c r="A47" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="B48" s="14" t="s">
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="7" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="16" t="s">
+      <c r="B49" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B49" s="16" t="s">
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="8" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="16" t="s">
+      <c r="B50" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="B50" s="16" t="s">
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="8" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="16" t="s">
+      <c r="B51" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="B51" s="16" t="s">
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="8" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" s="16" t="s">
+      <c r="B52" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="B52" s="16" t="s">
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" s="8" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="55" ht="20.4" spans="1:3">
-      <c r="A55" s="24" t="s">
+      <c r="B53" s="8" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="14" t="s">
+    <row r="56" ht="20.4" spans="1:3">
+      <c r="A56" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="B57" s="14" t="s">
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="B58" s="7" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" s="16" t="s">
+      <c r="C58" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="B58" s="16" t="s">
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C58" s="16" t="s">
+      <c r="B59" s="8" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" s="16" t="s">
+      <c r="C59" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="B59" s="16" t="s">
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C59" s="16" t="s">
+      <c r="B60" s="8" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="16" t="s">
+      <c r="C60" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="B60" s="16" t="s">
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="B61" s="8" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="64" ht="37.8" spans="1:3">
-      <c r="A64" s="24" t="s">
+      <c r="C61" s="8" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="66" ht="28.8" spans="1:8">
-      <c r="A66" s="14" t="s">
+    <row r="65" ht="37.8" spans="1:8">
+      <c r="A65" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="B66" s="14" t="s">
+    </row>
+    <row r="67" ht="28.8" spans="1:8">
+      <c r="A67" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C66" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="D66" s="14" t="s">
+      <c r="B67" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="C67" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D67" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="E67" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="G66" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="H66" s="14" t="s">
+      <c r="F67" s="7" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="67" spans="1:8">
-      <c r="A67" s="16">
+      <c r="G67" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="8">
         <v>1</v>
       </c>
-      <c r="B67" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="C67" s="16">
+      <c r="B68" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C68" s="8">
         <v>91</v>
       </c>
-      <c r="D67" s="16">
+      <c r="D68" s="8">
         <v>6</v>
       </c>
-      <c r="E67" s="25">
+      <c r="E68" s="31">
         <v>0.082</v>
       </c>
-      <c r="F67" s="16">
+      <c r="F68" s="8">
         <v>4</v>
       </c>
-      <c r="G67" s="26">
+      <c r="G68" s="32">
         <v>0.4</v>
       </c>
-      <c r="H67" s="16" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="16">
+      <c r="H68" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="8">
         <v>2</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="C68" s="16">
+      <c r="B69" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C69" s="8">
         <v>88</v>
       </c>
-      <c r="D68" s="16">
+      <c r="D69" s="8">
         <v>8</v>
       </c>
-      <c r="E68" s="25">
+      <c r="E69" s="31">
         <v>0.075</v>
       </c>
-      <c r="F68" s="16">
+      <c r="F69" s="8">
         <v>3</v>
       </c>
-      <c r="G68" s="26">
+      <c r="G69" s="32">
         <v>0.25</v>
       </c>
-      <c r="H68" s="16" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" s="16">
+      <c r="H69" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="8">
         <v>3</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="C69" s="16">
+      <c r="B70" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C70" s="8">
         <v>82</v>
       </c>
-      <c r="D69" s="16">
+      <c r="D70" s="8">
         <v>4</v>
       </c>
-      <c r="E69" s="25">
+      <c r="E70" s="31">
         <v>0.051</v>
       </c>
-      <c r="F69" s="16">
+      <c r="F70" s="8">
         <v>6</v>
       </c>
-      <c r="G69" s="26">
+      <c r="G70" s="32">
         <v>-0.3</v>
       </c>
-      <c r="H69" s="16" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
-      <c r="A71" s="27"/>
-    </row>
-    <row r="72" ht="20.4" spans="1:8">
-      <c r="A72" s="28" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="75" ht="20.4" spans="1:8">
-      <c r="A75" s="24" t="s">
+      <c r="H70" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="33"/>
+    </row>
+    <row r="73" ht="20.4" spans="1:8">
+      <c r="A73" s="34" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
-      <c r="A76" s="8" t="s">
+    <row r="76" ht="20.4" spans="1:8">
+      <c r="A76" s="30" t="s">
         <v>265</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>266</v>
-      </c>
-      <c r="C76" s="8" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="B77" s="9" t="s">
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="B78" s="10" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" s="9" t="s">
+      <c r="C78" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B78" s="9" t="s">
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="B79" s="10" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="79" spans="1:8">
-      <c r="A79" s="9" t="s">
+      <c r="C79" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="B79" s="9" t="s">
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="B80" s="10" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" s="9" t="s">
+      <c r="C80" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="B80" s="9" t="s">
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="B81" s="10" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="9" t="s">
+      <c r="C81" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B81" s="9" t="s">
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C81" s="9" t="s">
+      <c r="B82" s="10" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="9" t="s">
+      <c r="C82" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="B82" s="9" t="s">
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="C82" s="9" t="s">
+      <c r="B83" s="10" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="9" t="s">
+      <c r="C83" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="B83" s="9" t="s">
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="C83" s="9" t="s">
+      <c r="B84" s="10" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="86" ht="37.8" spans="1:5">
-      <c r="A86" s="24" t="s">
+      <c r="C84" s="10" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="A88" s="14" t="s">
+    <row r="87" ht="37.8" spans="1:5">
+      <c r="A87" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="B88" s="14" t="s">
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="B89" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="D88" s="14" t="s">
+      <c r="C89" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E88" s="14" t="s">
+      <c r="D89" s="7" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
-      <c r="A89" s="16">
+      <c r="E89" s="7" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="8">
         <v>1</v>
       </c>
-      <c r="B89" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="D89" s="16" t="s">
+      <c r="B90" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="E89" s="16" t="s">
+      <c r="C90" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="D90" s="8" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
-      <c r="A90" s="16">
+      <c r="E90" s="8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="8">
         <v>2</v>
       </c>
-      <c r="B90" s="16" t="s">
+      <c r="B91" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="E91" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="C90" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="D90" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="E90" s="16" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
-      <c r="A91" s="16">
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="8">
         <v>3</v>
       </c>
-      <c r="B91" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="C91" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D91" s="16" t="s">
+      <c r="B92" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="E91" s="16" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" s="16">
+      <c r="C92" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="8">
         <v>4</v>
       </c>
-      <c r="B92" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D92" s="16" t="s">
+      <c r="B93" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="E92" s="16" t="s">
+      <c r="C93" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D93" s="8" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="16">
+      <c r="E93" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="8">
         <v>5</v>
       </c>
-      <c r="B93" s="16" t="s">
+      <c r="B94" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E94" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="C93" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="D93" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="E93" s="16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
-      <c r="A94" s="16">
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="8">
         <v>6</v>
       </c>
-      <c r="B94" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="C94" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="D94" s="16" t="s">
+      <c r="B95" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="E94" s="16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
-      <c r="A95" s="16">
+      <c r="C95" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="8">
         <v>7</v>
       </c>
-      <c r="B95" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="C95" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="D95" s="16" t="s">
+      <c r="B96" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="E95" s="16" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
-      <c r="A96" s="16">
+      <c r="C96" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="8">
         <v>8</v>
       </c>
-      <c r="B96" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="C96" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="D96" s="16" t="s">
+      <c r="B97" s="8" t="s">
         <v>312</v>
       </c>
-      <c r="E96" s="16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
-      <c r="A97" s="16">
+      <c r="C97" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="8">
         <v>9</v>
       </c>
-      <c r="B97" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="C97" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="D97" s="16" t="s">
+      <c r="B98" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="E97" s="16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
-      <c r="A98" s="16">
+      <c r="C98" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="8">
         <v>10</v>
       </c>
-      <c r="B98" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="C98" s="16" t="s">
+      <c r="B99" s="8" t="s">
         <v>316</v>
       </c>
-      <c r="D98" s="16" t="s">
+      <c r="C99" s="8" t="s">
         <v>317</v>
       </c>
-      <c r="E98" s="16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
-      <c r="A99" s="16">
+      <c r="D99" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="E99" s="8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="8">
         <v>11</v>
       </c>
-      <c r="B99" s="16" t="s">
-        <v>318</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>274</v>
-      </c>
-      <c r="D99" s="16" t="s">
+      <c r="B100" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="E99" s="16" t="s">
+      <c r="C100" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D100" s="8" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
-      <c r="A100" s="16">
+      <c r="E100" s="8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="8">
         <v>12</v>
       </c>
-      <c r="B100" s="16" t="s">
+      <c r="B101" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="E101" s="8" t="s">
         <v>321</v>
       </c>
-      <c r="C100" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="D100" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="E100" s="16" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="102" ht="20.4" spans="1:5">
-      <c r="A102" s="24" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="103" ht="19.2" spans="1:5">
-      <c r="A103" s="29" t="s">
+    </row>
+    <row r="103" ht="20.4" spans="1:5">
+      <c r="A103" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="B103" s="7"/>
-    </row>
-    <row r="104" spans="1:5">
-      <c r="A104" s="8" t="s">
+    </row>
+    <row r="104" ht="19.2" spans="1:5">
+      <c r="A104" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="B104" s="8" t="s">
-        <v>267</v>
-      </c>
+      <c r="B104" s="16"/>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="9" t="s">
         <v>326</v>
       </c>
       <c r="B105" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="10" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="106" spans="1:5">
-      <c r="A106" s="9" t="s">
+      <c r="B106" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B106" s="9" t="s">
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="10" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
-      <c r="A107" s="9" t="s">
+      <c r="B107" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="B107" s="9" t="s">
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="10" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="108" spans="1:5">
-      <c r="A108" s="9" t="s">
+      <c r="B108" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B108" s="9" t="s">
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="10" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="109" spans="1:5">
-      <c r="A109" s="9" t="s">
+      <c r="B109" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="B109" s="9" t="s">
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="10" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="110" spans="1:5">
-      <c r="A110" s="9" t="s">
+      <c r="B110" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B110" s="9" t="s">
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="10" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="111" spans="1:5">
-      <c r="A111" s="9" t="s">
+      <c r="B111" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="B111" s="9" t="s">
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="10" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="112" spans="1:5">
-      <c r="A112" s="9" t="s">
+      <c r="B112" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B112" s="9" t="s">
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="10" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" s="9" t="s">
+      <c r="B113" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="B113" s="9" t="s">
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="10" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="9" t="s">
+      <c r="B114" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="B114" s="9" t="s">
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="10" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="9" t="s">
+      <c r="B115" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="B115" s="9" t="s">
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="10" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" s="9" t="s">
+      <c r="B116" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B116" s="9" t="s">
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="10" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="118" ht="19.2" spans="1:2">
-      <c r="A118" s="30" t="s">
+      <c r="B117" s="10" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
-      <c r="A120" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B120" s="31" t="s">
-        <v>267</v>
+    <row r="119" ht="19.2" spans="1:2">
+      <c r="A119" s="36" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="32" t="s">
-        <v>351</v>
-      </c>
-      <c r="B121" s="32" t="s">
+      <c r="A121" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="B121" s="37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="10" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" s="32" t="s">
+      <c r="B122" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="B122" s="32" t="s">
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="10" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="32" t="s">
+      <c r="B123" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="B123" s="32" t="s">
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="10" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" s="32" t="s">
-        <v>338</v>
-      </c>
-      <c r="B124" s="32" t="s">
+      <c r="B124" s="10" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="10" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="B125" s="32" t="s">
+      <c r="B125" s="10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="10" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="32" t="s">
+      <c r="B126" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="B126" s="32" t="s">
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="10" t="s">
         <v>345</v>
       </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" s="32" t="s">
+      <c r="B127" s="10" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="131" ht="19.2" spans="1:2">
+      <c r="A131" s="36" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="B133" s="37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B134" s="10" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="B136" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B127" s="32" t="s">
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="10" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" s="32" t="s">
+      <c r="B140" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="B128" s="32" t="s">
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="10" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="130" ht="19.2" spans="1:2">
-      <c r="A130" s="30" t="s">
+      <c r="B141" s="10" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
-      <c r="A132" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B132" s="31" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" s="32" t="s">
-        <v>351</v>
-      </c>
-      <c r="B133" s="32" t="s">
+    <row r="143" ht="19.2" spans="1:2">
+      <c r="A143" s="36" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="B145" s="37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="10" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" s="32" t="s">
+      <c r="B146" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="B134" s="32" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="B135" s="32" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" s="32" t="s">
-        <v>338</v>
-      </c>
-      <c r="B136" s="32" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="B137" s="32" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" s="32" t="s">
-        <v>344</v>
-      </c>
-      <c r="B138" s="32" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" s="32" t="s">
-        <v>357</v>
-      </c>
-      <c r="B139" s="32" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" s="32" t="s">
-        <v>359</v>
-      </c>
-      <c r="B140" s="32" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="142" ht="19.2" spans="1:2">
-      <c r="A142" s="30" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B144" s="31" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" s="32" t="s">
-        <v>351</v>
-      </c>
-      <c r="B145" s="32" t="s">
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="154" ht="19.2" spans="1:2">
+      <c r="A154" s="36" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="B156" s="37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="38" t="s">
+        <v>329</v>
+      </c>
+      <c r="B157" s="38" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="38" t="s">
+        <v>377</v>
+      </c>
+      <c r="B158" s="38" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="38" t="s">
+        <v>379</v>
+      </c>
+      <c r="B159" s="38" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="38" t="s">
+        <v>381</v>
+      </c>
+      <c r="B160" s="38" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="B161" s="38" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" s="38" t="s">
+        <v>385</v>
+      </c>
+      <c r="B162" s="38" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="165" ht="19.2" spans="1:4">
+      <c r="A165" s="36" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" s="37" t="s">
+        <v>326</v>
+      </c>
+      <c r="B167" s="37" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" s="38" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="B146" s="32" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="B147" s="32" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" s="32" t="s">
-        <v>367</v>
-      </c>
-      <c r="B148" s="32" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" s="32" t="s">
-        <v>369</v>
-      </c>
-      <c r="B149" s="32" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="B150" s="32" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" s="32" t="s">
-        <v>373</v>
-      </c>
-      <c r="B151" s="32" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="153" ht="19.2" spans="1:2">
-      <c r="A153" s="30" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B155" s="31" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="B156" s="32" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" s="32" t="s">
-        <v>376</v>
-      </c>
-      <c r="B157" s="32" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" s="32" t="s">
-        <v>378</v>
-      </c>
-      <c r="B158" s="32" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="B159" s="32" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" s="32" t="s">
-        <v>382</v>
-      </c>
-      <c r="B160" s="32" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="B161" s="32" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="164" ht="19.2" spans="1:4">
-      <c r="A164" s="30" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
-      <c r="A166" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B166" s="31" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
-      <c r="A167" s="32" t="s">
-        <v>351</v>
-      </c>
-      <c r="B167" s="32" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="A168" s="32" t="s">
-        <v>387</v>
-      </c>
-      <c r="B168" s="32" t="s">
+      <c r="B168" s="38" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" s="38" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="169" spans="1:4">
-      <c r="A169" s="32" t="s">
+      <c r="B169" s="38" t="s">
         <v>389</v>
       </c>
-      <c r="B169" s="32" t="s">
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" s="38" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="170" spans="1:4">
-      <c r="A170" s="32" t="s">
+      <c r="B170" s="38" t="s">
         <v>391</v>
       </c>
-      <c r="B170" s="32" t="s">
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" s="38" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="171" spans="1:4">
-      <c r="A171" s="32" t="s">
+      <c r="B171" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="B171" s="32" t="s">
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" s="38" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="173" ht="20.4" spans="1:4">
-      <c r="A173" s="24" t="s">
+      <c r="B172" s="38" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
-      <c r="A175" s="14" t="s">
+    <row r="174" ht="20.4" spans="1:4">
+      <c r="A174" s="30" t="s">
         <v>396</v>
       </c>
-      <c r="B175" s="14" t="s">
+    </row>
+    <row r="176" spans="1:4">
+      <c r="A176" s="7" t="s">
         <v>397</v>
       </c>
-      <c r="C175" s="14" t="s">
+      <c r="B176" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="D175" s="14" t="s">
+      <c r="C176" s="7" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="176" spans="1:4">
-      <c r="A176" s="33" t="s">
+      <c r="D176" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="B176" s="16" t="s">
+    </row>
+    <row r="177" spans="1:4">
+      <c r="A177" s="39" t="s">
         <v>401</v>
       </c>
-      <c r="C176" s="16" t="s">
+      <c r="B177" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="D176" s="16" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="177" spans="1:9">
-      <c r="A177" s="34"/>
-      <c r="B177" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C177" s="16" t="s">
+      <c r="C177" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="D177" s="16" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9">
-      <c r="A178" s="35"/>
-      <c r="B178" s="16" t="s">
+      <c r="D177" s="8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4">
+      <c r="A178" s="40"/>
+      <c r="B178" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C178" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="C178" s="16" t="s">
+      <c r="D178" s="8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4">
+      <c r="A179" s="41"/>
+      <c r="B179" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="D178" s="16" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9">
-      <c r="A179" s="33" t="s">
+      <c r="C179" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="B179" s="16" t="s">
+      <c r="D179" s="8" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4">
+      <c r="A180" s="39" t="s">
         <v>407</v>
       </c>
-      <c r="C179" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="D179" s="16" t="s">
+      <c r="B180" s="8" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="180" spans="1:9">
-      <c r="A180" s="34"/>
-      <c r="B180" s="16" t="s">
+      <c r="C180" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D180" s="8" t="s">
         <v>409</v>
       </c>
-      <c r="C180" s="16" t="s">
+    </row>
+    <row r="181" spans="1:4">
+      <c r="A181" s="40"/>
+      <c r="B181" s="8" t="s">
         <v>410</v>
       </c>
-      <c r="D180" s="16" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9">
-      <c r="A181" s="34"/>
-      <c r="B181" s="16" t="s">
+      <c r="C181" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="C181" s="16" t="s">
+      <c r="D181" s="8" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4">
+      <c r="A182" s="40"/>
+      <c r="B182" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="D181" s="16" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9">
-      <c r="A182" s="35"/>
-      <c r="B182" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="C182" s="16" t="s">
+      <c r="C182" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="D182" s="16" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="183" ht="28.8" spans="1:9">
-      <c r="A183" s="33" t="s">
+      <c r="D182" s="8" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4">
+      <c r="A183" s="41"/>
+      <c r="B183" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C183" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="B183" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="C183" s="16" t="s">
+      <c r="D183" s="8" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="184" ht="28.8" spans="1:4">
+      <c r="A184" s="39" t="s">
         <v>415</v>
       </c>
-      <c r="D183" s="16" t="s">
+      <c r="B184" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C184" s="8" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="184" spans="1:9">
-      <c r="A184" s="34"/>
-      <c r="B184" s="16" t="s">
+      <c r="D184" s="8" t="s">
         <v>417</v>
       </c>
-      <c r="C184" s="16" t="s">
+    </row>
+    <row r="185" spans="1:4">
+      <c r="A185" s="40"/>
+      <c r="B185" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="D184" s="16" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9">
-      <c r="A185" s="35"/>
-      <c r="B185" s="16" t="s">
+      <c r="C185" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="C185" s="16" t="s">
+      <c r="D185" s="8" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4">
+      <c r="A186" s="41"/>
+      <c r="B186" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="D185" s="16" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9">
-      <c r="A186" s="33" t="s">
+      <c r="C186" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="B186" s="16" t="s">
+      <c r="D186" s="8" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4">
+      <c r="A187" s="39" t="s">
         <v>422</v>
       </c>
-      <c r="C186" s="16" t="s">
+      <c r="B187" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="D186" s="16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9">
-      <c r="A187" s="34"/>
-      <c r="B187" s="16" t="s">
+      <c r="C187" s="8" t="s">
         <v>424</v>
       </c>
-      <c r="C187" s="16" t="s">
+      <c r="D187" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4">
+      <c r="A188" s="40"/>
+      <c r="B188" s="8" t="s">
         <v>425</v>
       </c>
-      <c r="D187" s="16" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9">
-      <c r="A188" s="35"/>
-      <c r="B188" s="16" t="s">
+      <c r="C188" s="8" t="s">
         <v>426</v>
       </c>
-      <c r="C188" s="16" t="s">
+      <c r="D188" s="8" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4">
+      <c r="A189" s="41"/>
+      <c r="B189" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="D188" s="16" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="190" ht="20.4" spans="1:9">
-      <c r="A190" s="24" t="s">
+      <c r="C189" s="8" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="192" ht="43.2" spans="1:9">
-      <c r="A192" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B192" s="14" t="s">
+      <c r="D189" s="8" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="191" ht="20.4" spans="1:4">
+      <c r="A191" s="30" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="193" ht="43.2" spans="1:9">
+      <c r="A193" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="C192" s="14" t="s">
-        <v>429</v>
-      </c>
-      <c r="D192" s="14" t="s">
+      <c r="B193" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="C193" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="E192" s="14" t="s">
+      <c r="D193" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="F192" s="14" t="s">
+      <c r="E193" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="G192" s="14" t="s">
+      <c r="F193" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="H192" s="14" t="s">
+      <c r="G193" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="I192" s="14" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9">
-      <c r="A193" s="16">
+      <c r="H193" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="I193" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" s="8">
         <v>1</v>
       </c>
-      <c r="B193" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="C193" s="16">
+      <c r="B194" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="C194" s="8">
         <v>92</v>
       </c>
-      <c r="D193" s="16">
+      <c r="D194" s="8">
         <v>88</v>
       </c>
-      <c r="E193" s="16">
+      <c r="E194" s="8">
         <v>85</v>
       </c>
-      <c r="F193" s="16">
+      <c r="F194" s="8">
         <v>90</v>
       </c>
-      <c r="G193" s="16">
+      <c r="G194" s="8">
         <v>87</v>
       </c>
-      <c r="H193" s="16">
+      <c r="H194" s="8">
         <v>89</v>
       </c>
-      <c r="I193" s="16" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9">
-      <c r="A194" s="16">
+      <c r="I194" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" s="8">
         <v>2</v>
       </c>
-      <c r="B194" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="C194" s="16">
+      <c r="B195" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="C195" s="8">
         <v>90</v>
       </c>
-      <c r="D194" s="16">
+      <c r="D195" s="8">
         <v>91</v>
       </c>
-      <c r="E194" s="16">
+      <c r="E195" s="8">
         <v>82</v>
       </c>
-      <c r="F194" s="16">
+      <c r="F195" s="8">
         <v>86</v>
       </c>
-      <c r="G194" s="16">
+      <c r="G195" s="8">
         <v>85</v>
       </c>
-      <c r="H194" s="16">
+      <c r="H195" s="8">
         <v>88.1</v>
       </c>
-      <c r="I194" s="16" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9">
-      <c r="A195" s="16">
+      <c r="I195" s="8" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" s="8">
         <v>3</v>
       </c>
-      <c r="B195" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="C195" s="16">
+      <c r="B196" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="C196" s="8">
         <v>75</v>
       </c>
-      <c r="D195" s="16">
+      <c r="D196" s="8">
         <v>70</v>
       </c>
-      <c r="E195" s="16">
+      <c r="E196" s="8">
         <v>60</v>
       </c>
-      <c r="F195" s="16">
+      <c r="F196" s="8">
         <v>80</v>
       </c>
-      <c r="G195" s="16">
+      <c r="G196" s="8">
         <v>65</v>
       </c>
-      <c r="H195" s="16">
+      <c r="H196" s="8">
         <v>72</v>
       </c>
-      <c r="I195" s="16" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9">
-      <c r="A196" s="16">
+      <c r="I196" s="8" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" s="8">
         <v>4</v>
       </c>
-      <c r="B196" s="16" t="s">
-        <v>435</v>
-      </c>
-      <c r="C196" s="16">
+      <c r="B197" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="C197" s="8">
         <v>40</v>
       </c>
-      <c r="D196" s="16">
+      <c r="D197" s="8">
         <v>35</v>
       </c>
-      <c r="E196" s="16">
+      <c r="E197" s="8">
         <v>20</v>
       </c>
-      <c r="F196" s="16">
+      <c r="F197" s="8">
         <v>50</v>
       </c>
-      <c r="G196" s="16">
+      <c r="G197" s="8">
         <v>30</v>
       </c>
-      <c r="H196" s="16">
+      <c r="H197" s="8">
         <v>36.5</v>
       </c>
-      <c r="I196" s="16" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="199" ht="20.4" spans="1:9">
-      <c r="A199" s="24" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="201" ht="15.6" spans="1:9">
-      <c r="A201" s="36" t="s">
+      <c r="I197" s="8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="200" ht="20.4" spans="1:9">
+      <c r="A200" s="30" t="s">
         <v>437</v>
       </c>
-      <c r="B201" s="7"/>
-    </row>
-    <row r="202" spans="1:9">
-      <c r="A202" s="8" t="s">
-        <v>294</v>
-      </c>
-      <c r="B202" s="8" t="s">
-        <v>266</v>
-      </c>
+    </row>
+    <row r="202" ht="15.6" spans="1:9">
+      <c r="A202" s="35" t="s">
+        <v>438</v>
+      </c>
+      <c r="B202" s="16"/>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>438</v>
+        <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:9">
-      <c r="A204" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="B204" s="9" t="s">
+      <c r="A204" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B204" s="10" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="205" spans="1:9">
-      <c r="A205" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="B205" s="9" t="s">
+      <c r="A205" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B205" s="10" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="207" ht="15.6" spans="1:9">
-      <c r="A207" s="36" t="s">
+    <row r="206" spans="1:9">
+      <c r="A206" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="B206" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="B207" s="7"/>
-      <c r="C207" s="7"/>
-    </row>
-    <row r="208" spans="1:9">
-      <c r="A208" s="8" t="s">
+    </row>
+    <row r="208" ht="15.6" spans="1:9">
+      <c r="A208" s="35" t="s">
         <v>442</v>
       </c>
-      <c r="B208" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="C208" s="8" t="s">
-        <v>444</v>
-      </c>
+      <c r="B208" s="16"/>
+      <c r="C208" s="16"/>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="C209" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="B209" s="9" t="s">
+    </row>
+    <row r="210" spans="1:3">
+      <c r="A210" s="10" t="s">
         <v>446</v>
       </c>
-      <c r="C209" s="9" t="s">
+      <c r="B210" s="10" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="210" spans="1:3">
-      <c r="A210" s="9" t="s">
+      <c r="C210" s="10" t="s">
         <v>448</v>
       </c>
-      <c r="B210" s="9" t="s">
+    </row>
+    <row r="211" spans="1:3">
+      <c r="A211" s="10" t="s">
         <v>449</v>
       </c>
-      <c r="C210" s="9" t="s">
+      <c r="B211" s="10" t="s">
         <v>450</v>
       </c>
-    </row>
-    <row r="211" spans="1:3">
-      <c r="A211" s="9" t="s">
+      <c r="C211" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="B211" s="9" t="s">
+    </row>
+    <row r="212" spans="1:3">
+      <c r="A212" s="10" t="s">
         <v>452</v>
       </c>
-      <c r="C211" s="9" t="s">
+      <c r="B212" s="10" t="s">
         <v>453</v>
       </c>
-    </row>
-    <row r="212" spans="1:3">
-      <c r="A212" s="9" t="s">
+      <c r="C212" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="B212" s="9" t="s">
+    </row>
+    <row r="213" spans="1:3">
+      <c r="A213" s="10" t="s">
         <v>455</v>
       </c>
-      <c r="C212" s="9" t="s">
+      <c r="B213" s="10" t="s">
         <v>456</v>
       </c>
-    </row>
-    <row r="213" spans="1:3">
-      <c r="A213" s="9" t="s">
+      <c r="C213" s="10" t="s">
         <v>457</v>
       </c>
-      <c r="B213" s="9" t="s">
+    </row>
+    <row r="214" spans="1:3">
+      <c r="A214" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="C213" s="9" t="s">
+      <c r="B214" s="10" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="214" spans="1:3">
-      <c r="A214" s="9" t="s">
+      <c r="C214" s="10" t="s">
         <v>460</v>
       </c>
-      <c r="B214" s="9" t="s">
+    </row>
+    <row r="215" spans="1:3">
+      <c r="A215" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="C214" s="9" t="s">
+      <c r="B215" s="10" t="s">
         <v>462</v>
+      </c>
+      <c r="C215" s="10" t="s">
+        <v>463</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A32:A34"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A179:A182"/>
-    <mergeCell ref="A183:A185"/>
-    <mergeCell ref="A186:A188"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A18:A21"/>
+    <mergeCell ref="A24:A27"/>
+    <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A33:A35"/>
+    <mergeCell ref="A177:A179"/>
+    <mergeCell ref="A180:A183"/>
+    <mergeCell ref="A184:A186"/>
+    <mergeCell ref="A187:A189"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -5571,9 +5931,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A2:F2"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="5"/>
+  <cols>
+    <col min="5" max="5" width="14.7777777777778" customWidth="1"/>
+    <col min="6" max="6" width="15.6666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6">
+      <c r="A2" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>467</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5582,1072 +5967,453 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B4:O24"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:C86"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
-    <col min="3" max="3" width="26.4444444444444" customWidth="1"/>
-    <col min="13" max="13" width="17.7777777777778" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="63.6666666666667" customWidth="1"/>
+    <col min="3" max="3" width="33.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:15">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="2:15">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="2:15">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
-        <v>300000</v>
-      </c>
-      <c r="F6" s="1">
-        <v>108000</v>
-      </c>
-      <c r="G6" s="1">
-        <f>E6-F6</f>
-        <v>192000</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="2:15">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="2:15">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="N8" s="3">
-        <v>35000</v>
-      </c>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="2:15">
-      <c r="B9" s="1"/>
-      <c r="C9" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" ref="F9:F13" si="0">D9*E9</f>
-        <v>48000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>35000</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" ref="H9:H17" si="1">F9-G9</f>
-        <v>13000</v>
-      </c>
-      <c r="I9" s="1">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="1">
-        <v>7000</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="N9" s="3">
-        <v>26500</v>
-      </c>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="2:15">
-      <c r="B10" s="1"/>
-      <c r="C10" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E10" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F10" s="3">
-        <f t="shared" si="0"/>
-        <v>48000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>26500</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="1"/>
-        <v>21500</v>
-      </c>
-      <c r="I10" s="1">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="1">
-        <v>17000</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="N10" s="3">
-        <v>31000</v>
-      </c>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" spans="2:15">
-      <c r="B11" s="1"/>
-      <c r="C11" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E11" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="0"/>
-        <v>38400</v>
-      </c>
-      <c r="G11" s="3">
-        <v>31000</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="1"/>
-        <v>7400</v>
-      </c>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1">
-        <v>7000</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="N11" s="3">
-        <v>34000</v>
-      </c>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="2:15">
-      <c r="B12" s="1"/>
-      <c r="C12" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F12" s="3">
-        <f t="shared" si="0"/>
-        <v>38400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>34000</v>
-      </c>
-      <c r="H12" s="3">
-        <f t="shared" si="1"/>
-        <v>4400</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="N12" s="3">
-        <v>27000</v>
-      </c>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" spans="2:15">
-      <c r="B13" s="1"/>
-      <c r="C13" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F13" s="3">
-        <f t="shared" si="0"/>
-        <v>19200</v>
-      </c>
-      <c r="G13" s="3">
-        <v>27000</v>
-      </c>
-      <c r="H13" s="3">
-        <f t="shared" si="1"/>
-        <v>-7800</v>
-      </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="N13" s="5">
-        <v>31000</v>
-      </c>
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" spans="2:15">
-      <c r="B14" s="1"/>
-      <c r="C14" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5">
-        <v>31000</v>
-      </c>
-      <c r="H14" s="5">
-        <f t="shared" si="1"/>
-        <v>-31000</v>
-      </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" spans="2:15">
-      <c r="B15" s="1"/>
-      <c r="C15" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3">
-        <v>50000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>50000</v>
-      </c>
-      <c r="H15" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="3" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="N15" s="3">
-        <v>38000</v>
-      </c>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" spans="2:15">
-      <c r="B16" s="1"/>
-      <c r="C16" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3">
-        <v>38000</v>
-      </c>
-      <c r="G16" s="3">
-        <v>38000</v>
-      </c>
-      <c r="H16" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="5" t="s">
+      <c r="B1" s="2"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="N16" s="5">
-        <v>20000</v>
-      </c>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" spans="2:15">
-      <c r="B17" s="1"/>
-      <c r="C17" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5">
-        <v>20000</v>
-      </c>
-      <c r="G17" s="5">
-        <v>20000</v>
-      </c>
-      <c r="H17" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="N17" s="3">
-        <v>50000</v>
-      </c>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" spans="2:15">
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="2:15">
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" spans="2:15">
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-    </row>
-    <row r="21" spans="2:15">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-    </row>
-    <row r="22" spans="2:15">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1">
-        <v>31000</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="H22" s="1">
-        <f>F22*G22</f>
-        <v>40300</v>
-      </c>
-      <c r="I22" s="1">
-        <v>2</v>
-      </c>
-      <c r="J22" s="1">
-        <f>H22/I22</f>
-        <v>20150</v>
-      </c>
-      <c r="K22" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="L22" s="1">
-        <f>J22*K22</f>
-        <v>24180</v>
-      </c>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row r="23" spans="2:15">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1">
-        <f>H22-F22</f>
-        <v>9300</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1">
-        <f>L22-J22</f>
-        <v>4030</v>
-      </c>
-      <c r="M23" s="1">
-        <f>H23+L23</f>
-        <v>13330</v>
-      </c>
-      <c r="N23" s="1">
-        <f>M23/F22</f>
-        <v>0.43</v>
-      </c>
-      <c r="O23" s="1"/>
-    </row>
-    <row r="24" spans="2:15">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
+      <c r="B2" s="3" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="9" ht="27" spans="1:3">
+      <c r="A9" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11" ht="20.4" spans="1:3">
+      <c r="A11" s="6" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" s="8" t="s">
+        <v>488</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="16" ht="28.8" spans="1:3">
+      <c r="A16" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="19" ht="20.4" spans="1:3">
+      <c r="A19" s="6" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="24" ht="28.8" spans="1:3">
+      <c r="A24" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="27" ht="20.4" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="8" t="s">
+        <v>513</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="35" ht="20.4" spans="1:2">
+      <c r="A35" s="6" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="43" ht="20.4" spans="1:2">
+      <c r="A43" s="6" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="10" t="s">
+        <v>524</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="53" ht="16.8" spans="1:2">
+      <c r="A53" s="11" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="56" ht="27" spans="1:2">
+      <c r="A56" s="5" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="10"/>
+      <c r="B60" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="10"/>
+      <c r="B62" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="10"/>
+      <c r="B65" s="10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="10"/>
+      <c r="B66" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="10"/>
+      <c r="B67" s="10" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="70" ht="22.2" spans="1:2">
+      <c r="A70" s="12" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="72" ht="15.6" spans="1:2">
+      <c r="A72" s="13" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="74" ht="19.2" spans="1:2">
+      <c r="A74" s="14" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="75" ht="19.2" spans="1:2">
+      <c r="A75" s="14" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="76" ht="15.6" spans="1:2">
+      <c r="A76" s="14" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="15" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>561</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B4:O24"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="3" max="3" width="26.4444444444444" customWidth="1"/>
-    <col min="13" max="13" width="17.7777777777778" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" customFormat="1" spans="2:15">
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-    </row>
-    <row r="5" customFormat="1" spans="2:15">
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-    </row>
-    <row r="6" customFormat="1" spans="2:15">
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1">
-        <v>300000</v>
-      </c>
-      <c r="F6" s="1">
-        <v>108000</v>
-      </c>
-      <c r="G6" s="1">
-        <f>E6-F6</f>
-        <v>192000</v>
-      </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-    </row>
-    <row r="7" customFormat="1" spans="2:15">
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-    </row>
-    <row r="8" customFormat="1" spans="2:15">
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="N8" s="3">
-        <v>35000</v>
-      </c>
-      <c r="O8" s="1"/>
-    </row>
-    <row r="9" customFormat="1" spans="2:15">
-      <c r="B9" s="1"/>
-      <c r="C9" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D9" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E9" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F9" s="3">
-        <f t="shared" ref="F9:F13" si="0">D9*E9</f>
-        <v>48000</v>
-      </c>
-      <c r="G9" s="3">
-        <v>35000</v>
-      </c>
-      <c r="H9" s="3">
-        <f t="shared" ref="H9:H17" si="1">F9-G9</f>
-        <v>13000</v>
-      </c>
-      <c r="I9" s="1">
-        <v>10000</v>
-      </c>
-      <c r="J9" s="1">
-        <v>7000</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="N9" s="3">
-        <v>26500</v>
-      </c>
-      <c r="O9" s="1"/>
-    </row>
-    <row r="10" customFormat="1" spans="2:15">
-      <c r="B10" s="1"/>
-      <c r="C10" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D10" s="4">
-        <v>0.25</v>
-      </c>
-      <c r="E10" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F10" s="3">
-        <f t="shared" si="0"/>
-        <v>48000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>26500</v>
-      </c>
-      <c r="H10" s="3">
-        <f t="shared" si="1"/>
-        <v>21500</v>
-      </c>
-      <c r="I10" s="1">
-        <v>10000</v>
-      </c>
-      <c r="J10" s="1">
-        <v>17000</v>
-      </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="N10" s="3">
-        <v>31000</v>
-      </c>
-      <c r="O10" s="1"/>
-    </row>
-    <row r="11" customFormat="1" spans="2:15">
-      <c r="B11" s="1"/>
-      <c r="C11" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D11" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E11" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F11" s="3">
-        <f t="shared" si="0"/>
-        <v>38400</v>
-      </c>
-      <c r="G11" s="3">
-        <v>31000</v>
-      </c>
-      <c r="H11" s="3">
-        <f t="shared" si="1"/>
-        <v>7400</v>
-      </c>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1">
-        <v>7000</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="N11" s="3">
-        <v>34000</v>
-      </c>
-      <c r="O11" s="1"/>
-    </row>
-    <row r="12" customFormat="1" spans="2:15">
-      <c r="B12" s="1"/>
-      <c r="C12" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="D12" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="E12" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F12" s="3">
-        <f t="shared" si="0"/>
-        <v>38400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>34000</v>
-      </c>
-      <c r="H12" s="3">
-        <f t="shared" si="1"/>
-        <v>4400</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="N12" s="3">
-        <v>27000</v>
-      </c>
-      <c r="O12" s="1"/>
-    </row>
-    <row r="13" customFormat="1" spans="2:15">
-      <c r="B13" s="1"/>
-      <c r="C13" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="D13" s="4">
-        <v>0.1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>192000</v>
-      </c>
-      <c r="F13" s="3">
-        <f t="shared" si="0"/>
-        <v>19200</v>
-      </c>
-      <c r="G13" s="3">
-        <v>27000</v>
-      </c>
-      <c r="H13" s="3">
-        <f t="shared" si="1"/>
-        <v>-7800</v>
-      </c>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="N13" s="5">
-        <v>31000</v>
-      </c>
-      <c r="O13" s="1"/>
-    </row>
-    <row r="14" customFormat="1" spans="2:15">
-      <c r="B14" s="1"/>
-      <c r="C14" s="5" t="s">
-        <v>466</v>
-      </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5">
-        <v>31000</v>
-      </c>
-      <c r="H14" s="5">
-        <f t="shared" si="1"/>
-        <v>-31000</v>
-      </c>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="O14" s="1"/>
-    </row>
-    <row r="15" customFormat="1" spans="2:15">
-      <c r="B15" s="1"/>
-      <c r="C15" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3">
-        <v>50000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>50000</v>
-      </c>
-      <c r="H15" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="N15" s="3">
-        <v>38000</v>
-      </c>
-      <c r="O15" s="1"/>
-    </row>
-    <row r="16" customFormat="1" spans="2:15">
-      <c r="B16" s="1"/>
-      <c r="C16" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3">
-        <v>38000</v>
-      </c>
-      <c r="G16" s="3">
-        <v>38000</v>
-      </c>
-      <c r="H16" s="3">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="N16" s="5">
-        <v>20000</v>
-      </c>
-      <c r="O16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" spans="2:15">
-      <c r="B17" s="1"/>
-      <c r="C17" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5">
-        <v>20000</v>
-      </c>
-      <c r="G17" s="5">
-        <v>20000</v>
-      </c>
-      <c r="H17" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="N17" s="3">
-        <v>50000</v>
-      </c>
-      <c r="O17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" spans="2:15">
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-    </row>
-    <row r="19" customFormat="1" spans="2:15">
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-    </row>
-    <row r="20" customFormat="1" spans="2:15">
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-    </row>
-    <row r="21" customFormat="1" spans="2:15">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-    </row>
-    <row r="22" customFormat="1" spans="2:15">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1">
-        <v>31000</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1.3</v>
-      </c>
-      <c r="H22" s="1">
-        <f>F22*G22</f>
-        <v>40300</v>
-      </c>
-      <c r="I22" s="1">
-        <v>2</v>
-      </c>
-      <c r="J22" s="1">
-        <f>H22/I22</f>
-        <v>20150</v>
-      </c>
-      <c r="K22" s="1">
-        <v>1.2</v>
-      </c>
-      <c r="L22" s="1">
-        <f>J22*K22</f>
-        <v>24180</v>
-      </c>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-    </row>
-    <row r="23" customFormat="1" spans="2:15">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1">
-        <f>H22-F22</f>
-        <v>9300</v>
-      </c>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1">
-        <f>L22-J22</f>
-        <v>4030</v>
-      </c>
-      <c r="M23" s="1">
-        <f>H23+L23</f>
-        <v>13330</v>
-      </c>
-      <c r="N23" s="1">
-        <f>M23/F22</f>
-        <v>0.43</v>
-      </c>
-      <c r="O23" s="1"/>
-    </row>
-    <row r="24" customFormat="1" spans="2:15">
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-    </row>
-  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A59:A63"/>
+    <mergeCell ref="A64:A67"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/需求整理/industry_indicator_system.xlsx
+++ b/需求整理/industry_indicator_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="4"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Industry Indicators" sheetId="1" r:id="rId1"/>

--- a/需求整理/industry_indicator_system.xlsx
+++ b/需求整理/industry_indicator_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Industry Indicators" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="需求1—主线板块确认" sheetId="5" r:id="rId3"/>
     <sheet name="报表2—主线板块龙头" sheetId="4" r:id="rId4"/>
     <sheet name="需求3—量化主线板块" sheetId="6" r:id="rId5"/>
+    <sheet name="产业链分析" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="580">
   <si>
     <t>指标名称</t>
   </si>
@@ -2064,6 +2065,83 @@
   </si>
   <si>
     <t>如果无Wind，可用“过去4季度净利润增速”替代</t>
+  </si>
+  <si>
+    <r>
+      <t>半导体材料可以分成</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>上游原材料 → 半导体材料 → 设备 → 晶圆制造 → 封装测试 → 芯片设计 → 下游应用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <t>半导体产业链</t>
+  </si>
+  <si>
+    <t>矿产资源</t>
+  </si>
+  <si>
+    <t>化工材料</t>
+  </si>
+  <si>
+    <t>硫酸</t>
+  </si>
+  <si>
+    <t>双氧水</t>
+  </si>
+  <si>
+    <t>盐酸</t>
+  </si>
+  <si>
+    <t>氨水</t>
+  </si>
+  <si>
+    <t>氢氟酸（HF）</t>
+  </si>
+  <si>
+    <t>磷酸</t>
+  </si>
+  <si>
+    <t>电子化学品</t>
+  </si>
+  <si>
+    <t>│</t>
+  </si>
+  <si>
+    <t>半导体材料</t>
+  </si>
+  <si>
+    <t>半导体设备</t>
+  </si>
+  <si>
+    <t>晶圆制造</t>
+  </si>
+  <si>
+    <t>封装测试</t>
+  </si>
+  <si>
+    <t>芯片设计</t>
+  </si>
+  <si>
+    <t>AI服务器、手机、汽车</t>
   </si>
 </sst>
 </file>
@@ -2815,8 +2893,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3294,273 +3376,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="16" t="s">
+      <c r="D3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="18" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="18" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:6">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="18" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="18" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="18" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="18" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="18" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="18" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="18" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="18" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" ht="100.8" spans="1:6">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="40" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3585,473 +3667,473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="44" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="C1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="D1" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="42" t="s">
+      <c r="F1" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="4"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" ht="115.2" spans="1:7">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="45"/>
+      <c r="F2" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" ht="273.6" spans="1:7">
-      <c r="A3" s="43"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="43" t="s">
+      <c r="A3" s="45"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="43" t="s">
+      <c r="A4" s="45"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43" t="s">
+      <c r="E4" s="45"/>
+      <c r="F4" s="45" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="43"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="43" t="s">
+      <c r="A5" s="45"/>
+      <c r="B5" s="45"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="4"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="43" t="s">
+      <c r="A6" s="45"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="46"/>
+      <c r="D6" s="45" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="4"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" ht="72" spans="1:7">
-      <c r="A7" s="43"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="43" t="s">
+      <c r="A7" s="45"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="46"/>
+      <c r="D7" s="45" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="45" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="43"/>
-      <c r="G7" s="4"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43" t="s">
+      <c r="A8" s="45"/>
+      <c r="B8" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="4"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="6"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="43"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43" t="s">
+      <c r="A9" s="45"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="4"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="43"/>
-      <c r="B10" s="43"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43" t="s">
+      <c r="A10" s="45"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="4"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" ht="57.6" spans="1:7">
-      <c r="A11" s="43"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43" t="s">
+      <c r="A11" s="45"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="4"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="43"/>
-      <c r="B12" s="43" t="s">
+      <c r="A12" s="45"/>
+      <c r="B12" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="C12" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="45" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="4"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="43"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43" t="s">
+      <c r="A13" s="45"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="4"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" ht="43.2" spans="1:7">
-      <c r="A14" s="43"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43" t="s">
+      <c r="A14" s="45"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="45" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="43"/>
-      <c r="G14" s="4"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" ht="57.6" spans="1:7">
-      <c r="A15" s="43"/>
-      <c r="B15" s="43" t="s">
+      <c r="A15" s="45"/>
+      <c r="B15" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="43"/>
-      <c r="D15" s="45" t="s">
+      <c r="C15" s="45"/>
+      <c r="D15" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="E15" s="45" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="43"/>
-      <c r="G15" s="4"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="45" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="45" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="45" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="45" t="s">
         <v>110</v>
       </c>
-      <c r="F16" s="43"/>
-      <c r="G16" s="4"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="43"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43" t="s">
+      <c r="A17" s="45"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="43"/>
-      <c r="G17" s="4"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43" t="s">
+      <c r="A18" s="45"/>
+      <c r="B18" s="45" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="43" t="s">
+      <c r="C18" s="45" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D18" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="45"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="4"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="43"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43" t="s">
+      <c r="A19" s="45"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="4"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="43"/>
-      <c r="B20" s="43" t="s">
+      <c r="A20" s="45"/>
+      <c r="B20" s="45" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C20" s="45" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="45" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="43"/>
-      <c r="G20" s="4"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="43"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43" t="s">
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="43" t="s">
+      <c r="E21" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="43"/>
-      <c r="G21" s="4"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" ht="72" spans="1:7">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43" t="s">
+      <c r="A22" s="45"/>
+      <c r="B22" s="45" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="43" t="s">
+      <c r="C22" s="45" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43" t="s">
+      <c r="D22" s="45"/>
+      <c r="E22" s="45" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="43"/>
-      <c r="G22" s="4"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="45" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="45" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="45" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="43" t="s">
+      <c r="D23" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="4"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="43"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43" t="s">
+      <c r="A24" s="45"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="43" t="s">
+      <c r="D24" s="45" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="4"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" ht="43.2" spans="1:7">
-      <c r="A25" s="43"/>
-      <c r="B25" s="43"/>
-      <c r="C25" s="44" t="s">
+      <c r="A25" s="45"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="46" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43" t="s">
+      <c r="D25" s="45"/>
+      <c r="E25" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="44"/>
-      <c r="G25" s="4"/>
+      <c r="F25" s="46"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="43"/>
-      <c r="B26" s="43" t="s">
+      <c r="A26" s="45"/>
+      <c r="B26" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="4"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="43"/>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43" t="s">
+      <c r="A27" s="45"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="4"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="6"/>
     </row>
     <row r="28" ht="43.2" spans="1:7">
-      <c r="A28" s="43"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="44" t="s">
+      <c r="A28" s="45"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43" t="s">
+      <c r="D28" s="45"/>
+      <c r="E28" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="43"/>
-      <c r="G28" s="4"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="6"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="43"/>
-      <c r="B29" s="43" t="s">
+      <c r="A29" s="45"/>
+      <c r="B29" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="C29" s="44" t="s">
+      <c r="C29" s="46" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="43" t="s">
+      <c r="D29" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="43"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="4"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="6"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="43"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="44" t="s">
+      <c r="A30" s="45"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="46" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="43" t="s">
+      <c r="D30" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="E30" s="43"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="4"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="6"/>
     </row>
     <row r="31" ht="43.2" spans="1:7">
-      <c r="A31" s="43"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="44" t="s">
+      <c r="A31" s="45"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="45"/>
-      <c r="E31" s="43" t="s">
+      <c r="D31" s="47"/>
+      <c r="E31" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="44"/>
-      <c r="G31" s="4"/>
+      <c r="F31" s="46"/>
+      <c r="G31" s="6"/>
     </row>
     <row r="32" ht="57.6" spans="1:7">
-      <c r="A32" s="43"/>
-      <c r="B32" s="44" t="s">
+      <c r="A32" s="45"/>
+      <c r="B32" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="44" t="s">
+      <c r="C32" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="45"/>
-      <c r="E32" s="43" t="s">
+      <c r="D32" s="47"/>
+      <c r="E32" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="F32" s="44"/>
-      <c r="G32" s="4"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="6"/>
     </row>
     <row r="33" ht="158.4" spans="1:7">
-      <c r="A33" s="45" t="s">
+      <c r="A33" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="4"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="47"/>
+      <c r="G33" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4092,1822 +4174,1822 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" ht="20.4" spans="1:4">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="11" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="4" ht="28.8" spans="1:4">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="21">
         <v>0.35</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="12" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="5" ht="28.8" spans="1:4">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="21">
         <v>0.25</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="12" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="6" ht="28.8" spans="1:4">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="12" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="21">
         <v>0.15</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="12" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="12" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="21">
         <v>0.15</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="12" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="21">
         <v>0.1</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="12" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:4">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="22" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" ht="19.2" spans="1:4">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="23" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="23"/>
-      <c r="B14" s="8" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="10" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="23"/>
-      <c r="B15" s="8" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="24"/>
-      <c r="B16" s="8" t="s">
+      <c r="A16" s="26"/>
+      <c r="B16" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="9" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="23"/>
-      <c r="B19" s="8" t="s">
+      <c r="A19" s="25"/>
+      <c r="B19" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="10" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="23"/>
-      <c r="B20" s="8" t="s">
+      <c r="A20" s="25"/>
+      <c r="B20" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="10" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="24"/>
-      <c r="B21" s="8" t="s">
+      <c r="A21" s="26"/>
+      <c r="B21" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="10" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="27" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="27" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="27" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="23"/>
-      <c r="B25" s="26" t="s">
+      <c r="A25" s="25"/>
+      <c r="B25" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="28" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="23"/>
-      <c r="B26" s="26" t="s">
+      <c r="A26" s="25"/>
+      <c r="B26" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="28" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="24"/>
-      <c r="B27" s="26" t="s">
+      <c r="A27" s="26"/>
+      <c r="B27" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="28" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="28" t="s">
+      <c r="D29" s="30" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="27"/>
-      <c r="B30" s="26" t="s">
+      <c r="A30" s="29"/>
+      <c r="B30" s="28" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="28" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="27"/>
-      <c r="B31" s="26" t="s">
+      <c r="A31" s="29"/>
+      <c r="B31" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="28" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="9" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="29"/>
-      <c r="B34" s="8" t="s">
+      <c r="A34" s="31"/>
+      <c r="B34" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="8" t="s">
+      <c r="C34" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D34" s="8" t="s">
+      <c r="D34" s="10" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="29"/>
-      <c r="B35" s="8" t="s">
+      <c r="A35" s="31"/>
+      <c r="B35" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="10" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="38" ht="20.4" spans="1:4">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="32" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="7" t="s">
+      <c r="B40" s="9" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="41" ht="28.8" spans="1:4">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="10" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="42" ht="28.8" spans="1:4">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="10" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="43" ht="28.8" spans="1:4">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="10" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="10" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="47" ht="15.6" spans="1:4">
-      <c r="A47" s="20" t="s">
+      <c r="A47" s="22" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="7" t="s">
+      <c r="A49" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="9" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="10" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="10" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="10" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="10" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="56" ht="20.4" spans="1:3">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="32" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="9" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C59" s="8" t="s">
+      <c r="C59" s="10" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="8" t="s">
+      <c r="C60" s="10" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="C61" s="8" t="s">
+      <c r="C61" s="10" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="65" ht="37.8" spans="1:8">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="32" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="67" ht="28.8" spans="1:8">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B67" s="7" t="s">
+      <c r="B67" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C67" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="D67" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="F67" s="7" t="s">
+      <c r="F67" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="G67" s="7" t="s">
+      <c r="G67" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="H67" s="7" t="s">
+      <c r="H67" s="9" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="8">
+      <c r="A68" s="10">
         <v>1</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="C68" s="8">
+      <c r="C68" s="10">
         <v>91</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="10">
         <v>6</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="33">
         <v>0.082</v>
       </c>
-      <c r="F68" s="8">
+      <c r="F68" s="10">
         <v>4</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="34">
         <v>0.4</v>
       </c>
-      <c r="H68" s="8" t="s">
+      <c r="H68" s="10" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="8">
+      <c r="A69" s="10">
         <v>2</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C69" s="8">
+      <c r="C69" s="10">
         <v>88</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="10">
         <v>8</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="33">
         <v>0.075</v>
       </c>
-      <c r="F69" s="8">
+      <c r="F69" s="10">
         <v>3</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="34">
         <v>0.25</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="H69" s="10" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="8">
+      <c r="A70" s="10">
         <v>3</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="C70" s="8">
+      <c r="C70" s="10">
         <v>82</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="10">
         <v>4</v>
       </c>
-      <c r="E70" s="31">
+      <c r="E70" s="33">
         <v>0.051</v>
       </c>
-      <c r="F70" s="8">
+      <c r="F70" s="10">
         <v>6</v>
       </c>
-      <c r="G70" s="32">
+      <c r="G70" s="34">
         <v>-0.3</v>
       </c>
-      <c r="H70" s="8" t="s">
+      <c r="H70" s="10" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="33"/>
+      <c r="A72" s="35"/>
     </row>
     <row r="73" ht="20.4" spans="1:8">
-      <c r="A73" s="34" t="s">
+      <c r="A73" s="36" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="76" ht="20.4" spans="1:8">
-      <c r="A76" s="30" t="s">
+      <c r="A76" s="32" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="11" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" s="12" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="12" t="s">
         <v>272</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="12" t="s">
         <v>273</v>
       </c>
-      <c r="C79" s="10" t="s">
+      <c r="C79" s="12" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="C80" s="10" t="s">
+      <c r="C80" s="12" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="C81" s="10" t="s">
+      <c r="C81" s="12" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="12" t="s">
         <v>282</v>
       </c>
-      <c r="C82" s="10" t="s">
+      <c r="C82" s="12" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="12" t="s">
         <v>284</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="C83" s="10" t="s">
+      <c r="C83" s="12" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="12" t="s">
         <v>288</v>
       </c>
-      <c r="C84" s="10" t="s">
+      <c r="C84" s="12" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="87" ht="37.8" spans="1:5">
-      <c r="A87" s="30" t="s">
+      <c r="A87" s="32" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="7" t="s">
+      <c r="A89" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C89" s="9" t="s">
         <v>293</v>
       </c>
-      <c r="D89" s="7" t="s">
+      <c r="D89" s="9" t="s">
         <v>294</v>
       </c>
-      <c r="E89" s="7" t="s">
+      <c r="E89" s="9" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="8">
+      <c r="A90" s="10">
         <v>1</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="C90" s="8" t="s">
+      <c r="C90" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="D90" s="8" t="s">
+      <c r="D90" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="10" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="8">
+      <c r="A91" s="10">
         <v>2</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="C91" s="8" t="s">
+      <c r="C91" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="D91" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="E91" s="10" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="8">
+      <c r="A92" s="10">
         <v>3</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D92" s="8" t="s">
+      <c r="D92" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="E92" s="8" t="s">
+      <c r="E92" s="10" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="8">
+      <c r="A93" s="10">
         <v>4</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C93" s="8" t="s">
+      <c r="C93" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D93" s="8" t="s">
+      <c r="D93" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="E93" s="8" t="s">
+      <c r="E93" s="10" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="8">
+      <c r="A94" s="10">
         <v>5</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="C94" s="8" t="s">
+      <c r="C94" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D94" s="8" t="s">
+      <c r="D94" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" s="10" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="8">
+      <c r="A95" s="10">
         <v>6</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C95" s="8" t="s">
+      <c r="C95" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D95" s="8" t="s">
+      <c r="D95" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="E95" s="8" t="s">
+      <c r="E95" s="10" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="8">
+      <c r="A96" s="10">
         <v>7</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="C96" s="8" t="s">
+      <c r="C96" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="D96" s="8" t="s">
+      <c r="D96" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="E96" s="8" t="s">
+      <c r="E96" s="10" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="8">
+      <c r="A97" s="10">
         <v>8</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="C97" s="8" t="s">
+      <c r="C97" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D97" s="8" t="s">
+      <c r="D97" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="E97" s="8" t="s">
+      <c r="E97" s="10" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="8">
+      <c r="A98" s="10">
         <v>9</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="C98" s="8" t="s">
+      <c r="C98" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="D98" s="8" t="s">
+      <c r="D98" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="10" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="8">
+      <c r="A99" s="10">
         <v>10</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="C99" s="8" t="s">
+      <c r="C99" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="D99" s="8" t="s">
+      <c r="D99" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="E99" s="8" t="s">
+      <c r="E99" s="10" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="8">
+      <c r="A100" s="10">
         <v>11</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="C100" s="8" t="s">
+      <c r="C100" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="D100" s="8" t="s">
+      <c r="D100" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="E100" s="8" t="s">
+      <c r="E100" s="10" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="8">
+      <c r="A101" s="10">
         <v>12</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C101" s="8" t="s">
+      <c r="C101" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="D101" s="8" t="s">
+      <c r="D101" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="E101" s="8" t="s">
+      <c r="E101" s="10" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="103" ht="20.4" spans="1:5">
-      <c r="A103" s="30" t="s">
+      <c r="A103" s="32" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="104" ht="19.2" spans="1:5">
-      <c r="A104" s="35" t="s">
+      <c r="A104" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="B104" s="16"/>
+      <c r="B104" s="18"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" s="11" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="10" t="s">
+      <c r="A106" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B106" s="12" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="10" t="s">
+      <c r="A107" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="B107" s="10" t="s">
+      <c r="B107" s="12" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="B108" s="10" t="s">
+      <c r="B108" s="12" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="10" t="s">
+      <c r="A109" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="B109" s="10" t="s">
+      <c r="B109" s="12" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="B110" s="10" t="s">
+      <c r="B110" s="12" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="B111" s="10" t="s">
+      <c r="B111" s="12" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="10" t="s">
+      <c r="A112" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B112" s="10" t="s">
+      <c r="B112" s="12" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="B113" s="10" t="s">
+      <c r="B113" s="12" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="B114" s="10" t="s">
+      <c r="B114" s="12" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="B115" s="10" t="s">
+      <c r="B115" s="12" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="10" t="s">
+      <c r="A116" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="B116" s="10" t="s">
+      <c r="B116" s="12" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B117" s="10" t="s">
+      <c r="B117" s="12" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="119" ht="19.2" spans="1:2">
-      <c r="A119" s="36" t="s">
+      <c r="A119" s="38" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="37" t="s">
+      <c r="A121" s="39" t="s">
         <v>326</v>
       </c>
-      <c r="B121" s="37" t="s">
+      <c r="B121" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="10" t="s">
+      <c r="A122" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B122" s="12" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B123" s="12" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="10" t="s">
+      <c r="A124" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B124" s="12" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="10" t="s">
+      <c r="A125" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B125" s="10" t="s">
+      <c r="B125" s="12" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="10" t="s">
+      <c r="A126" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="B126" s="10" t="s">
+      <c r="B126" s="12" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="10" t="s">
+      <c r="A127" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="B127" s="10" t="s">
+      <c r="B127" s="12" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="10" t="s">
+      <c r="A128" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="B128" s="10" t="s">
+      <c r="B128" s="12" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="10" t="s">
+      <c r="A129" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B129" s="10" t="s">
+      <c r="B129" s="12" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="131" ht="19.2" spans="1:2">
-      <c r="A131" s="36" t="s">
+      <c r="A131" s="38" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="37" t="s">
+      <c r="A133" s="39" t="s">
         <v>326</v>
       </c>
-      <c r="B133" s="37" t="s">
+      <c r="B133" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="10" t="s">
+      <c r="A134" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B134" s="10" t="s">
+      <c r="B134" s="12" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="10" t="s">
+      <c r="A135" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="B135" s="10" t="s">
+      <c r="B135" s="12" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="10" t="s">
+      <c r="A136" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="B136" s="10" t="s">
+      <c r="B136" s="12" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="10" t="s">
+      <c r="A137" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="B137" s="10" t="s">
+      <c r="B137" s="12" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="10" t="s">
+      <c r="A138" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="B138" s="10" t="s">
+      <c r="B138" s="12" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="10" t="s">
+      <c r="A139" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="B139" s="10" t="s">
+      <c r="B139" s="12" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="10" t="s">
+      <c r="A140" s="12" t="s">
         <v>358</v>
       </c>
-      <c r="B140" s="10" t="s">
+      <c r="B140" s="12" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="10" t="s">
+      <c r="A141" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="B141" s="10" t="s">
+      <c r="B141" s="12" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="143" ht="19.2" spans="1:2">
-      <c r="A143" s="36" t="s">
+      <c r="A143" s="38" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="37" t="s">
+      <c r="A145" s="39" t="s">
         <v>326</v>
       </c>
-      <c r="B145" s="37" t="s">
+      <c r="B145" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="10" t="s">
+      <c r="A146" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="B146" s="10" t="s">
+      <c r="B146" s="12" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="10" t="s">
+      <c r="A147" s="12" t="s">
         <v>364</v>
       </c>
-      <c r="B147" s="10" t="s">
+      <c r="B147" s="12" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="10" t="s">
+      <c r="A148" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="B148" s="10" t="s">
+      <c r="B148" s="12" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="10" t="s">
+      <c r="A149" s="12" t="s">
         <v>368</v>
       </c>
-      <c r="B149" s="10" t="s">
+      <c r="B149" s="12" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="10" t="s">
+      <c r="A150" s="12" t="s">
         <v>370</v>
       </c>
-      <c r="B150" s="10" t="s">
+      <c r="B150" s="12" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="10" t="s">
+      <c r="A151" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="B151" s="10" t="s">
+      <c r="B151" s="12" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="10" t="s">
+      <c r="A152" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="B152" s="10" t="s">
+      <c r="B152" s="12" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="154" ht="19.2" spans="1:2">
-      <c r="A154" s="36" t="s">
+      <c r="A154" s="38" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="37" t="s">
+      <c r="A156" s="39" t="s">
         <v>326</v>
       </c>
-      <c r="B156" s="37" t="s">
+      <c r="B156" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="38" t="s">
+      <c r="A157" s="40" t="s">
         <v>329</v>
       </c>
-      <c r="B157" s="38" t="s">
+      <c r="B157" s="40" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="38" t="s">
+      <c r="A158" s="40" t="s">
         <v>377</v>
       </c>
-      <c r="B158" s="38" t="s">
+      <c r="B158" s="40" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="38" t="s">
+      <c r="A159" s="40" t="s">
         <v>379</v>
       </c>
-      <c r="B159" s="38" t="s">
+      <c r="B159" s="40" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="38" t="s">
+      <c r="A160" s="40" t="s">
         <v>381</v>
       </c>
-      <c r="B160" s="38" t="s">
+      <c r="B160" s="40" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="38" t="s">
+      <c r="A161" s="40" t="s">
         <v>383</v>
       </c>
-      <c r="B161" s="38" t="s">
+      <c r="B161" s="40" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="38" t="s">
+      <c r="A162" s="40" t="s">
         <v>385</v>
       </c>
-      <c r="B162" s="38" t="s">
+      <c r="B162" s="40" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="165" ht="19.2" spans="1:4">
-      <c r="A165" s="36" t="s">
+      <c r="A165" s="38" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="37" t="s">
+      <c r="A167" s="39" t="s">
         <v>326</v>
       </c>
-      <c r="B167" s="37" t="s">
+      <c r="B167" s="39" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="38" t="s">
+      <c r="A168" s="40" t="s">
         <v>352</v>
       </c>
-      <c r="B168" s="38" t="s">
+      <c r="B168" s="40" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="38" t="s">
+      <c r="A169" s="40" t="s">
         <v>388</v>
       </c>
-      <c r="B169" s="38" t="s">
+      <c r="B169" s="40" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="38" t="s">
+      <c r="A170" s="40" t="s">
         <v>390</v>
       </c>
-      <c r="B170" s="38" t="s">
+      <c r="B170" s="40" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="38" t="s">
+      <c r="A171" s="40" t="s">
         <v>392</v>
       </c>
-      <c r="B171" s="38" t="s">
+      <c r="B171" s="40" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="38" t="s">
+      <c r="A172" s="40" t="s">
         <v>394</v>
       </c>
-      <c r="B172" s="38" t="s">
+      <c r="B172" s="40" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="174" ht="20.4" spans="1:4">
-      <c r="A174" s="30" t="s">
+      <c r="A174" s="32" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="7" t="s">
+      <c r="A176" s="9" t="s">
         <v>397</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B176" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="C176" s="7" t="s">
+      <c r="C176" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="D176" s="7" t="s">
+      <c r="D176" s="9" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="39" t="s">
+      <c r="A177" s="41" t="s">
         <v>401</v>
       </c>
-      <c r="B177" s="8" t="s">
+      <c r="B177" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="C177" s="8" t="s">
+      <c r="C177" s="10" t="s">
         <v>403</v>
       </c>
-      <c r="D177" s="8" t="s">
+      <c r="D177" s="10" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="40"/>
-      <c r="B178" s="8" t="s">
+      <c r="A178" s="42"/>
+      <c r="B178" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="8" t="s">
+      <c r="C178" s="10" t="s">
         <v>404</v>
       </c>
-      <c r="D178" s="8" t="s">
+      <c r="D178" s="10" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="41"/>
-      <c r="B179" s="8" t="s">
+      <c r="A179" s="43"/>
+      <c r="B179" s="10" t="s">
         <v>405</v>
       </c>
-      <c r="C179" s="8" t="s">
+      <c r="C179" s="10" t="s">
         <v>406</v>
       </c>
-      <c r="D179" s="8" t="s">
+      <c r="D179" s="10" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="39" t="s">
+      <c r="A180" s="41" t="s">
         <v>407</v>
       </c>
-      <c r="B180" s="8" t="s">
+      <c r="B180" s="10" t="s">
         <v>408</v>
       </c>
-      <c r="C180" s="8" t="s">
+      <c r="C180" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D180" s="8" t="s">
+      <c r="D180" s="10" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="40"/>
-      <c r="B181" s="8" t="s">
+      <c r="A181" s="42"/>
+      <c r="B181" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="C181" s="8" t="s">
+      <c r="C181" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="D181" s="8" t="s">
+      <c r="D181" s="10" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="40"/>
-      <c r="B182" s="8" t="s">
+      <c r="A182" s="42"/>
+      <c r="B182" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="C182" s="8" t="s">
+      <c r="C182" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="D182" s="8" t="s">
+      <c r="D182" s="10" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="41"/>
-      <c r="B183" s="8" t="s">
+      <c r="A183" s="43"/>
+      <c r="B183" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C183" s="8" t="s">
+      <c r="C183" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="D183" s="8" t="s">
+      <c r="D183" s="10" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="184" ht="28.8" spans="1:4">
-      <c r="A184" s="39" t="s">
+      <c r="A184" s="41" t="s">
         <v>415</v>
       </c>
-      <c r="B184" s="8" t="s">
+      <c r="B184" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C184" s="8" t="s">
+      <c r="C184" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="D184" s="8" t="s">
+      <c r="D184" s="10" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="40"/>
-      <c r="B185" s="8" t="s">
+      <c r="A185" s="42"/>
+      <c r="B185" s="10" t="s">
         <v>418</v>
       </c>
-      <c r="C185" s="8" t="s">
+      <c r="C185" s="10" t="s">
         <v>419</v>
       </c>
-      <c r="D185" s="8" t="s">
+      <c r="D185" s="10" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="41"/>
-      <c r="B186" s="8" t="s">
+      <c r="A186" s="43"/>
+      <c r="B186" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="C186" s="8" t="s">
+      <c r="C186" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="D186" s="8" t="s">
+      <c r="D186" s="10" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="39" t="s">
+      <c r="A187" s="41" t="s">
         <v>422</v>
       </c>
-      <c r="B187" s="8" t="s">
+      <c r="B187" s="10" t="s">
         <v>423</v>
       </c>
-      <c r="C187" s="8" t="s">
+      <c r="C187" s="10" t="s">
         <v>424</v>
       </c>
-      <c r="D187" s="8" t="s">
+      <c r="D187" s="10" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="40"/>
-      <c r="B188" s="8" t="s">
+      <c r="A188" s="42"/>
+      <c r="B188" s="10" t="s">
         <v>425</v>
       </c>
-      <c r="C188" s="8" t="s">
+      <c r="C188" s="10" t="s">
         <v>426</v>
       </c>
-      <c r="D188" s="8" t="s">
+      <c r="D188" s="10" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="41"/>
-      <c r="B189" s="8" t="s">
+      <c r="A189" s="43"/>
+      <c r="B189" s="10" t="s">
         <v>427</v>
       </c>
-      <c r="C189" s="8" t="s">
+      <c r="C189" s="10" t="s">
         <v>428</v>
       </c>
-      <c r="D189" s="8" t="s">
+      <c r="D189" s="10" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="191" ht="20.4" spans="1:4">
-      <c r="A191" s="30" t="s">
+      <c r="A191" s="32" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="193" ht="43.2" spans="1:9">
-      <c r="A193" s="7" t="s">
+      <c r="A193" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B193" s="7" t="s">
+      <c r="B193" s="9" t="s">
         <v>256</v>
       </c>
-      <c r="C193" s="7" t="s">
+      <c r="C193" s="9" t="s">
         <v>430</v>
       </c>
-      <c r="D193" s="7" t="s">
+      <c r="D193" s="9" t="s">
         <v>431</v>
       </c>
-      <c r="E193" s="7" t="s">
+      <c r="E193" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="F193" s="7" t="s">
+      <c r="F193" s="9" t="s">
         <v>433</v>
       </c>
-      <c r="G193" s="7" t="s">
+      <c r="G193" s="9" t="s">
         <v>434</v>
       </c>
-      <c r="H193" s="7" t="s">
+      <c r="H193" s="9" t="s">
         <v>435</v>
       </c>
-      <c r="I193" s="7" t="s">
+      <c r="I193" s="9" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194" s="8">
+      <c r="A194" s="10">
         <v>1</v>
       </c>
-      <c r="B194" s="8" t="s">
+      <c r="B194" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="C194" s="8">
+      <c r="C194" s="10">
         <v>92</v>
       </c>
-      <c r="D194" s="8">
+      <c r="D194" s="10">
         <v>88</v>
       </c>
-      <c r="E194" s="8">
+      <c r="E194" s="10">
         <v>85</v>
       </c>
-      <c r="F194" s="8">
+      <c r="F194" s="10">
         <v>90</v>
       </c>
-      <c r="G194" s="8">
+      <c r="G194" s="10">
         <v>87</v>
       </c>
-      <c r="H194" s="8">
+      <c r="H194" s="10">
         <v>89</v>
       </c>
-      <c r="I194" s="8" t="s">
+      <c r="I194" s="10" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="195" spans="1:9">
-      <c r="A195" s="8">
+      <c r="A195" s="10">
         <v>2</v>
       </c>
-      <c r="B195" s="8" t="s">
+      <c r="B195" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C195" s="8">
+      <c r="C195" s="10">
         <v>90</v>
       </c>
-      <c r="D195" s="8">
+      <c r="D195" s="10">
         <v>91</v>
       </c>
-      <c r="E195" s="8">
+      <c r="E195" s="10">
         <v>82</v>
       </c>
-      <c r="F195" s="8">
+      <c r="F195" s="10">
         <v>86</v>
       </c>
-      <c r="G195" s="8">
+      <c r="G195" s="10">
         <v>85</v>
       </c>
-      <c r="H195" s="8">
+      <c r="H195" s="10">
         <v>88.1</v>
       </c>
-      <c r="I195" s="8" t="s">
+      <c r="I195" s="10" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="196" spans="1:9">
-      <c r="A196" s="8">
+      <c r="A196" s="10">
         <v>3</v>
       </c>
-      <c r="B196" s="8" t="s">
+      <c r="B196" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="C196" s="8">
+      <c r="C196" s="10">
         <v>75</v>
       </c>
-      <c r="D196" s="8">
+      <c r="D196" s="10">
         <v>70</v>
       </c>
-      <c r="E196" s="8">
+      <c r="E196" s="10">
         <v>60</v>
       </c>
-      <c r="F196" s="8">
+      <c r="F196" s="10">
         <v>80</v>
       </c>
-      <c r="G196" s="8">
+      <c r="G196" s="10">
         <v>65</v>
       </c>
-      <c r="H196" s="8">
+      <c r="H196" s="10">
         <v>72</v>
       </c>
-      <c r="I196" s="8" t="s">
+      <c r="I196" s="10" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="197" spans="1:9">
-      <c r="A197" s="8">
+      <c r="A197" s="10">
         <v>4</v>
       </c>
-      <c r="B197" s="8" t="s">
+      <c r="B197" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="C197" s="8">
+      <c r="C197" s="10">
         <v>40</v>
       </c>
-      <c r="D197" s="8">
+      <c r="D197" s="10">
         <v>35</v>
       </c>
-      <c r="E197" s="8">
+      <c r="E197" s="10">
         <v>20</v>
       </c>
-      <c r="F197" s="8">
+      <c r="F197" s="10">
         <v>50</v>
       </c>
-      <c r="G197" s="8">
+      <c r="G197" s="10">
         <v>30</v>
       </c>
-      <c r="H197" s="8">
+      <c r="H197" s="10">
         <v>36.5</v>
       </c>
-      <c r="I197" s="8" t="s">
+      <c r="I197" s="10" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="200" ht="20.4" spans="1:9">
-      <c r="A200" s="30" t="s">
+      <c r="A200" s="32" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="202" ht="15.6" spans="1:9">
-      <c r="A202" s="35" t="s">
+      <c r="A202" s="37" t="s">
         <v>438</v>
       </c>
-      <c r="B202" s="16"/>
+      <c r="B202" s="18"/>
     </row>
     <row r="203" spans="1:9">
-      <c r="A203" s="9" t="s">
+      <c r="A203" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="B203" s="9" t="s">
+      <c r="B203" s="11" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:9">
-      <c r="A204" s="10" t="s">
+      <c r="A204" s="12" t="s">
         <v>298</v>
       </c>
-      <c r="B204" s="10" t="s">
+      <c r="B204" s="12" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="205" spans="1:9">
-      <c r="A205" s="10" t="s">
+      <c r="A205" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="B205" s="10" t="s">
+      <c r="B205" s="12" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="206" spans="1:9">
-      <c r="A206" s="10" t="s">
+      <c r="A206" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="B206" s="10" t="s">
+      <c r="B206" s="12" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="208" ht="15.6" spans="1:9">
-      <c r="A208" s="35" t="s">
+      <c r="A208" s="37" t="s">
         <v>442</v>
       </c>
-      <c r="B208" s="16"/>
-      <c r="C208" s="16"/>
+      <c r="B208" s="18"/>
+      <c r="C208" s="18"/>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="9" t="s">
+      <c r="A209" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="B209" s="9" t="s">
+      <c r="B209" s="11" t="s">
         <v>444</v>
       </c>
-      <c r="C209" s="9" t="s">
+      <c r="C209" s="11" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="10" t="s">
+      <c r="A210" s="12" t="s">
         <v>446</v>
       </c>
-      <c r="B210" s="10" t="s">
+      <c r="B210" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="C210" s="10" t="s">
+      <c r="C210" s="12" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="10" t="s">
+      <c r="A211" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="B211" s="10" t="s">
+      <c r="B211" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="C211" s="10" t="s">
+      <c r="C211" s="12" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="10" t="s">
+      <c r="A212" s="12" t="s">
         <v>452</v>
       </c>
-      <c r="B212" s="10" t="s">
+      <c r="B212" s="12" t="s">
         <v>453</v>
       </c>
-      <c r="C212" s="10" t="s">
+      <c r="C212" s="12" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="10" t="s">
+      <c r="A213" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="B213" s="10" t="s">
+      <c r="B213" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="C213" s="10" t="s">
+      <c r="C213" s="12" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="10" t="s">
+      <c r="A214" s="12" t="s">
         <v>458</v>
       </c>
-      <c r="B214" s="10" t="s">
+      <c r="B214" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="C214" s="10" t="s">
+      <c r="C214" s="12" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="10" t="s">
+      <c r="A215" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="B215" s="10" t="s">
+      <c r="B215" s="12" t="s">
         <v>462</v>
       </c>
-      <c r="C215" s="10" t="s">
+      <c r="C215" s="12" t="s">
         <v>463</v>
       </c>
     </row>
@@ -5939,22 +6021,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="18" t="s">
         <v>465</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="18" t="s">
         <v>466</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="18" t="s">
         <v>467</v>
       </c>
     </row>
@@ -5976,285 +6058,285 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="4"/>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>469</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="6" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>475</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="7" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="11" ht="20.4" spans="1:3">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="8" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="10" t="s">
         <v>485</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="10" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="10" t="s">
         <v>488</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="10" t="s">
         <v>489</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="10" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="10" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="10" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="10" t="s">
         <v>494</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="10" t="s">
         <v>495</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="10" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="19" ht="20.4" spans="1:3">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="8" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="11" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="12" t="s">
         <v>498</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="12" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="12" t="s">
         <v>500</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="12" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="24" ht="28.8" spans="1:3">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="12" t="s">
         <v>502</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="12" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="12" t="s">
         <v>504</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="12" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="27" ht="20.4" spans="1:3">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="8" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="9" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="10" t="s">
         <v>507</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="10" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="10" t="s">
         <v>509</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="10" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="10" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="10" t="s">
         <v>513</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="10" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="35" ht="20.4" spans="1:2">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="8" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="11" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="12" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="12" t="s">
         <v>518</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="12" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="12" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="43" ht="20.4" spans="1:2">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="8" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B45" s="9" t="s">
+      <c r="B45" s="11" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="10" t="s">
+      <c r="A46" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="12" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="12" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="12" t="s">
         <v>528</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="12" t="s">
         <v>529</v>
       </c>
     </row>
@@ -6264,148 +6346,148 @@
       </c>
     </row>
     <row r="53" ht="16.8" spans="1:2">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="13" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="56" ht="27" spans="1:2">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="7" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="11" t="s">
         <v>533</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="11" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="12" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="10"/>
-      <c r="B60" s="10" t="s">
+      <c r="A60" s="12"/>
+      <c r="B60" s="12" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="10"/>
-      <c r="B61" s="10" t="s">
+      <c r="A61" s="12"/>
+      <c r="B61" s="12" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="10"/>
-      <c r="B62" s="10" t="s">
+      <c r="A62" s="12"/>
+      <c r="B62" s="12" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="10"/>
-      <c r="B63" s="10" t="s">
+      <c r="A63" s="12"/>
+      <c r="B63" s="12" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="10" t="s">
+      <c r="A64" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="12" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="10"/>
-      <c r="B65" s="10" t="s">
+      <c r="A65" s="12"/>
+      <c r="B65" s="12" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10" t="s">
+      <c r="A66" s="12"/>
+      <c r="B66" s="12" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="10"/>
-      <c r="B67" s="10" t="s">
+      <c r="A67" s="12"/>
+      <c r="B67" s="12" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="70" ht="22.2" spans="1:2">
-      <c r="A70" s="12" t="s">
+      <c r="A70" s="14" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="72" ht="15.6" spans="1:2">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="15" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="74" ht="19.2" spans="1:2">
-      <c r="A74" s="14" t="s">
+      <c r="A74" s="16" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="75" ht="19.2" spans="1:2">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="16" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="76" ht="15.6" spans="1:2">
-      <c r="A76" s="14" t="s">
+      <c r="A76" s="16" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="15" t="s">
+      <c r="A80" s="17" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="7" t="s">
+      <c r="A82" s="9" t="s">
         <v>552</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="9" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="10" t="s">
         <v>554</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="10" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="8" t="s">
+      <c r="A84" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="10" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="10" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="10" t="s">
         <v>560</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="10" t="s">
         <v>561</v>
       </c>
     </row>
@@ -6417,4 +6499,142 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B1:F25"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="2" width="14.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="19.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="14.1111111111111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6">
+      <c r="F1" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="2" spans="2:6">
+      <c r="B2" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="C3" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="C5" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="C6" s="2"/>
+      <c r="D6" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="C7" s="2"/>
+      <c r="D7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="C8" s="2"/>
+      <c r="D8" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="C9" s="2"/>
+      <c r="D9" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="C10" s="2"/>
+      <c r="D10" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="C13" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="C14" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="C15" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="C16" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" t="s">
+        <v>579</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C5:C10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/需求整理/industry_indicator_system.xlsx
+++ b/需求整理/industry_indicator_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="5"/>
+    <workbookView windowWidth="30720" windowHeight="13500" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Industry Indicators" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="报表2—主线板块龙头" sheetId="4" r:id="rId4"/>
     <sheet name="需求3—量化主线板块" sheetId="6" r:id="rId5"/>
     <sheet name="产业链分析" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,8 +32,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="719" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="754">
   <si>
     <t>指标名称</t>
   </si>
@@ -2067,19 +2090,11 @@
     <t>如果无Wind，可用“过去4季度净利润增速”替代</t>
   </si>
   <si>
+    <t>最终可以规划成四大能力：</t>
+  </si>
+  <si>
     <r>
-      <t>半导体材料可以分成</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>上游原材料 → 半导体材料 → 设备 → 晶圆制造 → 封装测试 → 芯片设计 → 下游应用</t>
+      <t>产业链图谱</t>
     </r>
     <r>
       <rPr>
@@ -2089,59 +2104,614 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>。</t>
+      <t>：完整展示上下游、替代关系、技术路线。</t>
     </r>
   </si>
   <si>
-    <t>半导体产业链</t>
-  </si>
-  <si>
-    <t>矿产资源</t>
-  </si>
-  <si>
-    <t>化工材料</t>
-  </si>
-  <si>
-    <t>硫酸</t>
-  </si>
-  <si>
-    <t>双氧水</t>
-  </si>
-  <si>
-    <t>盐酸</t>
-  </si>
-  <si>
-    <t>氨水</t>
-  </si>
-  <si>
-    <t>氢氟酸（HF）</t>
-  </si>
-  <si>
-    <t>磷酸</t>
-  </si>
-  <si>
-    <t>电子化学品</t>
-  </si>
-  <si>
-    <t>│</t>
-  </si>
-  <si>
-    <t>半导体材料</t>
-  </si>
-  <si>
-    <t>半导体设备</t>
-  </si>
-  <si>
-    <t>晶圆制造</t>
-  </si>
-  <si>
-    <t>封装测试</t>
-  </si>
-  <si>
-    <t>芯片设计</t>
-  </si>
-  <si>
-    <t>AI服务器、手机、汽车</t>
+    <r>
+      <t>产业数据库</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：景气度、估值、供需、价格、库存、资本开支等指标形成统一指标库。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>公司知识图谱</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：公司与产品、客户、供应商、细分赛道、产业链节点的关联关系。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI研究引擎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>：自动生成行业分析、龙头比较、轮动分析、风险提示，并支持自然语言提问，例如“AI服务器需求增加，哪些上游最受益？”或“半导体设备和电子特气哪个估值更有优势？”</t>
+    </r>
+  </si>
+  <si>
+    <t>📊 量价关系分析模块需求文档（PRD）</t>
+  </si>
+  <si>
+    <t>一、模块名称</t>
+  </si>
+  <si>
+    <t>量价关系分析系统（Volume-Price Analysis Engine）</t>
+  </si>
+  <si>
+    <t>二、背景与目标</t>
+  </si>
+  <si>
+    <t>1. 背景</t>
+  </si>
+  <si>
+    <t>A股市场中：</t>
+  </si>
+  <si>
+    <t>价格容易被短期资金推动</t>
+  </si>
+  <si>
+    <t>单纯看涨跌无法识别“真假趋势”</t>
+  </si>
+  <si>
+    <t>但成交量可以反映资金真实行为</t>
+  </si>
+  <si>
+    <t>因此需要构建一个系统：</t>
+  </si>
+  <si>
+    <t>用“量价关系 + 时间结构 + 行业维度”判断资金行为与趋势强度</t>
+  </si>
+  <si>
+    <t>2. 核心目标</t>
+  </si>
+  <si>
+    <t>构建一个可以回答以下问题的系统：</t>
+  </si>
+  <si>
+    <t>当前行业/股票是启动、加速还是派发？</t>
+  </si>
+  <si>
+    <t>是否存在主力持续流入？</t>
+  </si>
+  <si>
+    <t>当前上涨是否“有量支撑”？</t>
+  </si>
+  <si>
+    <t>是否进入主升浪 or 反弹结束？</t>
+  </si>
+  <si>
+    <t>哪些行业正在成为主线？</t>
+  </si>
+  <si>
+    <t>三、适用范围</t>
+  </si>
+  <si>
+    <t>数据对象</t>
+  </si>
+  <si>
+    <t>股票（个股）</t>
+  </si>
+  <si>
+    <t>行业（申万/同花顺）</t>
+  </si>
+  <si>
+    <t>概念板块</t>
+  </si>
+  <si>
+    <t>四、核心指标体系</t>
+  </si>
+  <si>
+    <t>4.1 基础量价指标</t>
+  </si>
+  <si>
+    <t>Close</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Turnover</t>
+  </si>
+  <si>
+    <t>Turnover Rate</t>
+  </si>
+  <si>
+    <t>Return</t>
+  </si>
+  <si>
+    <t>4.2 核心量价关系指标</t>
+  </si>
+  <si>
+    <t>（1）量比（核心）</t>
+  </si>
+  <si>
+    <t>量比 = 当日成交量 / 过去20日平均成交量</t>
+  </si>
+  <si>
+    <t>分级：</t>
+  </si>
+  <si>
+    <t>区间</t>
+  </si>
+  <si>
+    <t>含义</t>
+  </si>
+  <si>
+    <t>&lt;0.8</t>
+  </si>
+  <si>
+    <t>缩量</t>
+  </si>
+  <si>
+    <t>0.8-1.2</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>1.2-2</t>
+  </si>
+  <si>
+    <t>放量</t>
+  </si>
+  <si>
+    <t>强放量</t>
+  </si>
+  <si>
+    <t>&gt;3</t>
+  </si>
+  <si>
+    <t>异常放量</t>
+  </si>
+  <si>
+    <t>（2）量价配合强度</t>
+  </si>
+  <si>
+    <t>Volume-Price Score = f(价格涨跌 + 成交量变化)</t>
+  </si>
+  <si>
+    <t>分类：</t>
+  </si>
+  <si>
+    <t>价格</t>
+  </si>
+  <si>
+    <t>解释</t>
+  </si>
+  <si>
+    <t>↑</t>
+  </si>
+  <si>
+    <t>趋势确认（最强）</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>逼空或衰竭</t>
+  </si>
+  <si>
+    <t>出货信号</t>
+  </si>
+  <si>
+    <t>低迷/筑底</t>
+  </si>
+  <si>
+    <t>（3）20日趋势强度（核心周期）</t>
+  </si>
+  <si>
+    <t>20日量均线比 = 今日成交量 / MA20(Volume)</t>
+  </si>
+  <si>
+    <t>20日价趋势 = MA20(Price slope)</t>
+  </si>
+  <si>
+    <t>（4）连续放量天数</t>
+  </si>
+  <si>
+    <t>连续 N 天：Volume &gt; MA20</t>
+  </si>
+  <si>
+    <t>含义：</t>
+  </si>
+  <si>
+    <t>天数</t>
+  </si>
+  <si>
+    <t>异动</t>
+  </si>
+  <si>
+    <t>初期趋势</t>
+  </si>
+  <si>
+    <t>主升确认</t>
+  </si>
+  <si>
+    <t>&gt;10</t>
+  </si>
+  <si>
+    <t>强趋势主线</t>
+  </si>
+  <si>
+    <t>（5）突破量价信号</t>
+  </si>
+  <si>
+    <t>定义：</t>
+  </si>
+  <si>
+    <t>价格突破60日新高 + 成交量 &gt; MA20 * 1.5</t>
+  </si>
+  <si>
+    <t>五、行业级量价分析（重点）</t>
+  </si>
+  <si>
+    <t>5.1 行业聚合指标</t>
+  </si>
+  <si>
+    <t>对行业内所有股票加权：</t>
+  </si>
+  <si>
+    <t>行业成交额</t>
+  </si>
+  <si>
+    <t>sum(volume * price)</t>
+  </si>
+  <si>
+    <t>行业涨跌幅</t>
+  </si>
+  <si>
+    <t>加权平均</t>
+  </si>
+  <si>
+    <t>行业量比</t>
+  </si>
+  <si>
+    <t>总成交额 / 20日均值</t>
+  </si>
+  <si>
+    <t>上涨股票数 / 总数</t>
+  </si>
+  <si>
+    <t>放量比例</t>
+  </si>
+  <si>
+    <t>放量股票数 / 总数</t>
+  </si>
+  <si>
+    <t>5.2 行业资金强度评分（核心输出）</t>
+  </si>
+  <si>
+    <t>Industry Volume-Price Score (0-100)</t>
+  </si>
+  <si>
+    <t>组成：</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>成交量变化</t>
+  </si>
+  <si>
+    <t>价格趋势</t>
+  </si>
+  <si>
+    <t>连续放量</t>
+  </si>
+  <si>
+    <t>突破信号</t>
+  </si>
+  <si>
+    <t>5.3 行业状态分类</t>
+  </si>
+  <si>
+    <t>分数</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>80-100</t>
+  </si>
+  <si>
+    <t>主线爆发</t>
+  </si>
+  <si>
+    <t>60-80</t>
+  </si>
+  <si>
+    <t>趋势上升</t>
+  </si>
+  <si>
+    <t>40-60</t>
+  </si>
+  <si>
+    <t>震荡</t>
+  </si>
+  <si>
+    <t>20-40</t>
+  </si>
+  <si>
+    <t>弱势</t>
+  </si>
+  <si>
+    <t>&lt;20</t>
+  </si>
+  <si>
+    <t>退潮</t>
+  </si>
+  <si>
+    <t>六、时间周期设计（必须）</t>
+  </si>
+  <si>
+    <t>系统必须支持多周期：</t>
+  </si>
+  <si>
+    <t>周期</t>
+  </si>
+  <si>
+    <t>3日</t>
+  </si>
+  <si>
+    <t>捕捉启动</t>
+  </si>
+  <si>
+    <t>5日</t>
+  </si>
+  <si>
+    <t>短线趋势</t>
+  </si>
+  <si>
+    <t>10日</t>
+  </si>
+  <si>
+    <t>短中趋势</t>
+  </si>
+  <si>
+    <t>20日</t>
+  </si>
+  <si>
+    <t>主力趋势（核心）</t>
+  </si>
+  <si>
+    <t>60日</t>
+  </si>
+  <si>
+    <t>中期趋势</t>
+  </si>
+  <si>
+    <t>120日</t>
+  </si>
+  <si>
+    <t>大趋势</t>
+  </si>
+  <si>
+    <t>👉 默认推荐分析周期：20日</t>
+  </si>
+  <si>
+    <t>七、数据结构设计（MySQL）</t>
+  </si>
+  <si>
+    <t>7.1 股票量价表</t>
+  </si>
+  <si>
+    <t>stock_price_volume_di</t>
+  </si>
+  <si>
+    <t>7.2 行业聚合表</t>
+  </si>
+  <si>
+    <t>industry_volume_di</t>
+  </si>
+  <si>
+    <t>7.3 量价评分表</t>
+  </si>
+  <si>
+    <t>industry_vp_score_di</t>
+  </si>
+  <si>
+    <t>八、核心算法逻辑</t>
+  </si>
+  <si>
+    <t>Step 1：基础指标计算</t>
+  </si>
+  <si>
+    <t>MA5 / MA10 / MA20 / MA60</t>
+  </si>
+  <si>
+    <t>Volume ratio</t>
+  </si>
+  <si>
+    <t>Price momentum</t>
+  </si>
+  <si>
+    <t>Step 2：量价关系判断</t>
+  </si>
+  <si>
+    <t>if price_up and volume_up:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    signal = "trend_confirm"</t>
+  </si>
+  <si>
+    <t>elif price_up and volume_down:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    signal = "weak_rise"</t>
+  </si>
+  <si>
+    <t>elif price_down and volume_up:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    signal = "distribution"</t>
+  </si>
+  <si>
+    <t>Step 3：行业聚合</t>
+  </si>
+  <si>
+    <t>行业指标 = Σ(个股指标 * 权重)</t>
+  </si>
+  <si>
+    <t>权重：</t>
+  </si>
+  <si>
+    <t>市值权重（推荐）</t>
+  </si>
+  <si>
+    <t>或等权</t>
+  </si>
+  <si>
+    <t>Step 4：生成评分</t>
+  </si>
+  <si>
+    <t>score = 30% volume + 25% trend + 15% continuity + 15% breadth + 15% breakout</t>
+  </si>
+  <si>
+    <t>九、输出能力（产品层）</t>
+  </si>
+  <si>
+    <t>1. 行业排行榜</t>
+  </si>
+  <si>
+    <t>今日最强行业（量价评分）</t>
+  </si>
+  <si>
+    <t>资金流入Top10行业</t>
+  </si>
+  <si>
+    <t>连续放量行业</t>
+  </si>
+  <si>
+    <t>2. 行业趋势卡片</t>
+  </si>
+  <si>
+    <t>展示：</t>
+  </si>
+  <si>
+    <t>20日量比</t>
+  </si>
+  <si>
+    <t>连续放量天数</t>
+  </si>
+  <si>
+    <t>上涨家数比例</t>
+  </si>
+  <si>
+    <t>3. 信号系统</t>
+  </si>
+  <si>
+    <t>主升浪信号</t>
+  </si>
+  <si>
+    <t>启动信号</t>
+  </si>
+  <si>
+    <t>派发信号</t>
+  </si>
+  <si>
+    <t>退潮信号</t>
+  </si>
+  <si>
+    <t>4. 个股辅助</t>
+  </si>
+  <si>
+    <t>是否跟随行业</t>
+  </si>
+  <si>
+    <t>是否补涨</t>
+  </si>
+  <si>
+    <t>十、核心价值（为什么这个模块重要）</t>
+  </si>
+  <si>
+    <t>这个模块解决的是：</t>
+  </si>
+  <si>
+    <t>从“看股票” → “看资金行为” → “看行业主线”</t>
+  </si>
+  <si>
+    <t>最终能回答：</t>
+  </si>
+  <si>
+    <t>AI是主线吗？</t>
+  </si>
+  <si>
+    <t>CPO是不是退潮？</t>
+  </si>
+  <si>
+    <t>半导体是不是新一轮启动？</t>
+  </si>
+  <si>
+    <t>哪些板块是资金在持续买？</t>
+  </si>
+  <si>
+    <t>十一、升级建议（非常重要）</t>
+  </si>
+  <si>
+    <t>如果你要做成产品竞争力强的版本，建议加三层：</t>
+  </si>
+  <si>
+    <t>① 资金层（北向 / ETF / 龙虎榜）</t>
+  </si>
+  <si>
+    <t>② 情绪层（涨停数 / 连板数）</t>
+  </si>
+  <si>
+    <t>③ 产业层（订单 / CapEx / 景气度）</t>
+  </si>
+  <si>
+    <t>十二、总结一句话</t>
+  </si>
+  <si>
+    <t>这个系统本质不是“量价分析工具”，而是：</t>
+  </si>
+  <si>
+    <t>用量价关系识别“主力在买哪个行业”</t>
+  </si>
+  <si>
+    <t>如果你下一步想做，我可以帮你继续细化：</t>
+  </si>
+  <si>
+    <t>✔ 技术架构（FastAPI + MySQL +调度）</t>
+  </si>
+  <si>
+    <t>✔ 行业评分SQL实现</t>
+  </si>
+  <si>
+    <t>✔ Python量价计算代码</t>
+  </si>
+  <si>
+    <t>✔ 小程序UI设计</t>
+  </si>
+  <si>
+    <t>✔ 或直接帮你做MVP版本设计</t>
+  </si>
+  <si>
+    <t>只要你说要做到哪一层就行。</t>
   </si>
 </sst>
 </file>
@@ -2163,15 +2733,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2893,15 +3463,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -2911,13 +3480,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2953,7 +3522,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2962,7 +3531,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2977,7 +3546,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -2985,7 +3554,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3376,273 +3945,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="19" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:6">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="19" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="19" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="19" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F9" s="19" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F10" s="19" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="18" t="s">
+      <c r="F11" s="19" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="F12" s="19" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="18" t="s">
+      <c r="F13" s="19" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" ht="100.8" spans="1:6">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="41" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="C15" s="41" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3667,473 +4236,473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="44" t="s">
+      <c r="F1" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="6"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" ht="115.2" spans="1:7">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="46" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="47" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="45" t="s">
+      <c r="D2" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" ht="273.6" spans="1:7">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="45" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="45" t="s">
+      <c r="E3" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="45" t="s">
+      <c r="F3" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="45"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="45" t="s">
+      <c r="A4" s="46"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="46" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="7" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="45"/>
-      <c r="B5" s="45"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="45" t="s">
+      <c r="A5" s="46"/>
+      <c r="B5" s="46"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="6"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="45"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="45" t="s">
+      <c r="A6" s="46"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="6"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="7"/>
     </row>
     <row r="7" ht="72" spans="1:7">
-      <c r="A7" s="45"/>
-      <c r="B7" s="45"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="45" t="s">
+      <c r="A7" s="46"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="45" t="s">
+      <c r="E7" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="45"/>
-      <c r="G7" s="6"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="7"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="45"/>
-      <c r="B8" s="45" t="s">
+      <c r="A8" s="46"/>
+      <c r="B8" s="46" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C8" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="45" t="s">
+      <c r="D8" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="6"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="45"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45" t="s">
+      <c r="A9" s="46"/>
+      <c r="B9" s="46"/>
+      <c r="C9" s="46"/>
+      <c r="D9" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="6"/>
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="7"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="45"/>
-      <c r="D10" s="45" t="s">
+      <c r="A10" s="46"/>
+      <c r="B10" s="46"/>
+      <c r="C10" s="46"/>
+      <c r="D10" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="6"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" ht="57.6" spans="1:7">
-      <c r="A11" s="45"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="45"/>
-      <c r="D11" s="45" t="s">
+      <c r="A11" s="46"/>
+      <c r="B11" s="46"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="45" t="s">
+      <c r="E11" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="45"/>
-      <c r="G11" s="6"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="45"/>
-      <c r="B12" s="45" t="s">
+      <c r="A12" s="46"/>
+      <c r="B12" s="46" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C12" s="46" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="45" t="s">
+      <c r="D12" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="6"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="45"/>
-      <c r="B13" s="45"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45" t="s">
+      <c r="A13" s="46"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="6"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="7"/>
     </row>
     <row r="14" ht="43.2" spans="1:7">
-      <c r="A14" s="45"/>
-      <c r="B14" s="45"/>
-      <c r="C14" s="45"/>
-      <c r="D14" s="45" t="s">
+      <c r="A14" s="46"/>
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="45"/>
-      <c r="G14" s="6"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="7"/>
     </row>
     <row r="15" ht="57.6" spans="1:7">
-      <c r="A15" s="45"/>
-      <c r="B15" s="45" t="s">
+      <c r="A15" s="46"/>
+      <c r="B15" s="46" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="47" t="s">
+      <c r="C15" s="46"/>
+      <c r="D15" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="45" t="s">
+      <c r="E15" s="46" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="6"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="7"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="46" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="46" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="46" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D16" s="46" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="E16" s="46" t="s">
         <v>110</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="6"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="45"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45" t="s">
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="45" t="s">
+      <c r="E17" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="6"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="7"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="45"/>
-      <c r="B18" s="45" t="s">
+      <c r="A18" s="46"/>
+      <c r="B18" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C18" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="47" t="s">
+      <c r="D18" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="6"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="45"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="45"/>
-      <c r="D19" s="45" t="s">
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="45"/>
-      <c r="F19" s="45"/>
-      <c r="G19" s="6"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="45"/>
-      <c r="B20" s="45" t="s">
+      <c r="A20" s="46"/>
+      <c r="B20" s="46" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C20" s="46" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D20" s="46" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="6"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="45"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="45" t="s">
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="6"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="7"/>
     </row>
     <row r="22" ht="72" spans="1:7">
-      <c r="A22" s="45"/>
-      <c r="B22" s="45" t="s">
+      <c r="A22" s="46"/>
+      <c r="B22" s="46" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C22" s="46" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45" t="s">
+      <c r="D22" s="46"/>
+      <c r="E22" s="46" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="45"/>
-      <c r="G22" s="6"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="45" t="s">
+      <c r="A23" s="46" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C23" s="46" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="46" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="6"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="46"/>
+      <c r="G23" s="7"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="45"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45" t="s">
+      <c r="A24" s="46"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="46" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="6"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="7"/>
     </row>
     <row r="25" ht="43.2" spans="1:7">
-      <c r="A25" s="45"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="46" t="s">
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
+      <c r="C25" s="47" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45" t="s">
+      <c r="D25" s="46"/>
+      <c r="E25" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="46"/>
-      <c r="G25" s="6"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45" t="s">
+      <c r="A26" s="46"/>
+      <c r="B26" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="45" t="s">
+      <c r="C26" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="6"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="45"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45" t="s">
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="6"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" ht="43.2" spans="1:7">
-      <c r="A28" s="45"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="46" t="s">
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="47" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="45"/>
-      <c r="E28" s="45" t="s">
+      <c r="D28" s="46"/>
+      <c r="E28" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="45"/>
-      <c r="G28" s="6"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="7"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45" t="s">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46" t="s">
         <v>139</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="47" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D29" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="6"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="47"/>
+      <c r="G29" s="7"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="46" t="s">
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="45" t="s">
+      <c r="D30" s="46" t="s">
         <v>143</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="6"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="47"/>
+      <c r="G30" s="7"/>
     </row>
     <row r="31" ht="43.2" spans="1:7">
-      <c r="A31" s="45"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="46" t="s">
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="47" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="47"/>
-      <c r="E31" s="45" t="s">
+      <c r="D31" s="48"/>
+      <c r="E31" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="46"/>
-      <c r="G31" s="6"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="7"/>
     </row>
     <row r="32" ht="57.6" spans="1:7">
-      <c r="A32" s="45"/>
-      <c r="B32" s="46" t="s">
+      <c r="A32" s="46"/>
+      <c r="B32" s="47" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="47"/>
-      <c r="E32" s="45" t="s">
+      <c r="D32" s="48"/>
+      <c r="E32" s="46" t="s">
         <v>148</v>
       </c>
-      <c r="F32" s="46"/>
-      <c r="G32" s="6"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="7"/>
     </row>
     <row r="33" ht="158.4" spans="1:7">
-      <c r="A33" s="47" t="s">
+      <c r="A33" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="28" t="s">
+      <c r="D33" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="28"/>
-      <c r="F33" s="47"/>
-      <c r="G33" s="6"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4174,1822 +4743,1822 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" ht="20.4" spans="1:4">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="4" ht="28.8" spans="1:4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="22">
         <v>0.35</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="5" ht="28.8" spans="1:4">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="22">
         <v>0.25</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="6" ht="28.8" spans="1:4">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="22">
         <v>0.15</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <v>0.15</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="13" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <v>0.1</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="13" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:4">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="23" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" ht="19.2" spans="1:4">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="24" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="10" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="25"/>
-      <c r="B14" s="10" t="s">
+      <c r="A14" s="26"/>
+      <c r="B14" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="11" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="25"/>
-      <c r="B15" s="10" t="s">
+      <c r="A15" s="26"/>
+      <c r="B15" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="11" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="26"/>
-      <c r="B16" s="10" t="s">
+      <c r="A16" s="27"/>
+      <c r="B16" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="10" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="25"/>
-      <c r="B19" s="10" t="s">
+      <c r="A19" s="26"/>
+      <c r="B19" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="25"/>
-      <c r="B20" s="10" t="s">
+      <c r="A20" s="26"/>
+      <c r="B20" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="11" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="26"/>
-      <c r="B21" s="10" t="s">
+      <c r="A21" s="27"/>
+      <c r="B21" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="11" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="24" t="s">
+      <c r="A24" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="28" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="25"/>
-      <c r="B25" s="28" t="s">
+      <c r="A25" s="26"/>
+      <c r="B25" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="28" t="s">
+      <c r="D25" s="29" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="25"/>
-      <c r="B26" s="28" t="s">
+      <c r="A26" s="26"/>
+      <c r="B26" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="29" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="28" t="s">
+      <c r="D26" s="29" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="26"/>
-      <c r="B27" s="28" t="s">
+      <c r="A27" s="27"/>
+      <c r="B27" s="29" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="29" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="30" t="s">
+      <c r="C29" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="30" t="s">
+      <c r="D29" s="31" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="29"/>
-      <c r="B30" s="28" t="s">
+      <c r="A30" s="30"/>
+      <c r="B30" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="D30" s="29" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="29"/>
-      <c r="B31" s="28" t="s">
+      <c r="A31" s="30"/>
+      <c r="B31" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="D31" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="31" t="s">
+      <c r="A33" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="9" t="s">
+      <c r="D33" s="10" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="31"/>
-      <c r="B34" s="10" t="s">
+      <c r="A34" s="32"/>
+      <c r="B34" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C34" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="11" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="31"/>
-      <c r="B35" s="10" t="s">
+      <c r="A35" s="32"/>
+      <c r="B35" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="C35" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="11" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="38" ht="20.4" spans="1:4">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="33" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="10" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="41" ht="28.8" spans="1:4">
-      <c r="A41" s="10" t="s">
+      <c r="A41" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="11" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="42" ht="28.8" spans="1:4">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="11" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="43" ht="28.8" spans="1:4">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="11" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="11" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="47" ht="15.6" spans="1:4">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="23" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B49" s="9" t="s">
+      <c r="B49" s="10" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="11" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="10" t="s">
+      <c r="A51" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="11" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="10" t="s">
+      <c r="A52" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="11" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="10" t="s">
+      <c r="A53" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="11" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="56" ht="20.4" spans="1:3">
-      <c r="A56" s="32" t="s">
+      <c r="A56" s="33" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="9" t="s">
+      <c r="A58" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B58" s="9" t="s">
+      <c r="B58" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="9" t="s">
+      <c r="C58" s="10" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="10" t="s">
+      <c r="A59" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="C59" s="10" t="s">
+      <c r="C59" s="11" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="10" t="s">
+      <c r="A60" s="11" t="s">
         <v>248</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="11" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="10" t="s">
+      <c r="C60" s="11" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="10" t="s">
+      <c r="A61" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" s="11" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="65" ht="37.8" spans="1:8">
-      <c r="A65" s="32" t="s">
+      <c r="A65" s="33" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="67" ht="28.8" spans="1:8">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="C67" s="9" t="s">
+      <c r="C67" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="D67" s="9" t="s">
+      <c r="D67" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="E67" s="9" t="s">
+      <c r="E67" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="F67" s="9" t="s">
+      <c r="F67" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="G67" s="9" t="s">
+      <c r="G67" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="H67" s="9" t="s">
+      <c r="H67" s="10" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="10">
+      <c r="A68" s="11">
         <v>1</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C68" s="10">
+      <c r="C68" s="11">
         <v>91</v>
       </c>
-      <c r="D68" s="10">
+      <c r="D68" s="11">
         <v>6</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <v>0.082</v>
       </c>
-      <c r="F68" s="10">
+      <c r="F68" s="11">
         <v>4</v>
       </c>
-      <c r="G68" s="34">
+      <c r="G68" s="35">
         <v>0.4</v>
       </c>
-      <c r="H68" s="10" t="s">
+      <c r="H68" s="11" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="10">
+      <c r="A69" s="11">
         <v>2</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="C69" s="10">
+      <c r="C69" s="11">
         <v>88</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69" s="11">
         <v>8</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>0.075</v>
       </c>
-      <c r="F69" s="10">
+      <c r="F69" s="11">
         <v>3</v>
       </c>
-      <c r="G69" s="34">
+      <c r="G69" s="35">
         <v>0.25</v>
       </c>
-      <c r="H69" s="10" t="s">
+      <c r="H69" s="11" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="10">
+      <c r="A70" s="11">
         <v>3</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C70" s="10">
+      <c r="C70" s="11">
         <v>82</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70" s="11">
         <v>4</v>
       </c>
-      <c r="E70" s="33">
+      <c r="E70" s="34">
         <v>0.051</v>
       </c>
-      <c r="F70" s="10">
+      <c r="F70" s="11">
         <v>6</v>
       </c>
-      <c r="G70" s="34">
+      <c r="G70" s="35">
         <v>-0.3</v>
       </c>
-      <c r="H70" s="10" t="s">
+      <c r="H70" s="11" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="35"/>
+      <c r="A72" s="36"/>
     </row>
     <row r="73" ht="20.4" spans="1:8">
-      <c r="A73" s="36" t="s">
+      <c r="A73" s="37" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="76" ht="20.4" spans="1:8">
-      <c r="A76" s="32" t="s">
+      <c r="A76" s="33" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="12" t="s">
         <v>267</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="12" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="12" t="s">
+      <c r="A78" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="C78" s="13" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="12" t="s">
+      <c r="A79" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="C79" s="12" t="s">
+      <c r="C79" s="13" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="C80" s="12" t="s">
+      <c r="C80" s="13" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="C81" s="12" t="s">
+      <c r="C81" s="13" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="12" t="s">
+      <c r="A82" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="13" t="s">
         <v>282</v>
       </c>
-      <c r="C82" s="12" t="s">
+      <c r="C82" s="13" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="12" t="s">
+      <c r="A83" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="C83" s="12" t="s">
+      <c r="C83" s="13" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="12" t="s">
+      <c r="A84" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="13" t="s">
         <v>288</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="13" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="87" ht="37.8" spans="1:5">
-      <c r="A87" s="32" t="s">
+      <c r="A87" s="33" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="C89" s="9" t="s">
+      <c r="C89" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="D89" s="9" t="s">
+      <c r="D89" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="E89" s="9" t="s">
+      <c r="E89" s="10" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="10">
+      <c r="A90" s="11">
         <v>1</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="C90" s="10" t="s">
+      <c r="C90" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="D90" s="10" t="s">
+      <c r="D90" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="E90" s="10" t="s">
+      <c r="E90" s="11" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="10">
+      <c r="A91" s="11">
         <v>2</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="11" t="s">
         <v>299</v>
       </c>
-      <c r="C91" s="10" t="s">
+      <c r="C91" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D91" s="10" t="s">
+      <c r="D91" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="E91" s="10" t="s">
+      <c r="E91" s="11" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="10">
+      <c r="A92" s="11">
         <v>3</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="C92" s="10" t="s">
+      <c r="C92" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="D92" s="10" t="s">
+      <c r="D92" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="E92" s="10" t="s">
+      <c r="E92" s="11" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="10">
+      <c r="A93" s="11">
         <v>4</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="11" t="s">
         <v>303</v>
       </c>
-      <c r="C93" s="10" t="s">
+      <c r="C93" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="D93" s="10" t="s">
+      <c r="D93" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="E93" s="10" t="s">
+      <c r="E93" s="11" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="10">
+      <c r="A94" s="11">
         <v>5</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B94" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="C94" s="10" t="s">
+      <c r="C94" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D94" s="10" t="s">
+      <c r="D94" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="E94" s="10" t="s">
+      <c r="E94" s="11" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="10">
+      <c r="A95" s="11">
         <v>6</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="C95" s="10" t="s">
+      <c r="C95" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D95" s="10" t="s">
+      <c r="D95" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="E95" s="10" t="s">
+      <c r="E95" s="11" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="10">
+      <c r="A96" s="11">
         <v>7</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="C96" s="10" t="s">
+      <c r="C96" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="D96" s="10" t="s">
+      <c r="D96" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="E96" s="10" t="s">
+      <c r="E96" s="11" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="10">
+      <c r="A97" s="11">
         <v>8</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B97" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="C97" s="10" t="s">
+      <c r="C97" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="D97" s="10" t="s">
+      <c r="D97" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="E97" s="10" t="s">
+      <c r="E97" s="11" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="10">
+      <c r="A98" s="11">
         <v>9</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="C98" s="10" t="s">
+      <c r="C98" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="D98" s="10" t="s">
+      <c r="D98" s="11" t="s">
         <v>315</v>
       </c>
-      <c r="E98" s="10" t="s">
+      <c r="E98" s="11" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="10">
+      <c r="A99" s="11">
         <v>10</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="11" t="s">
         <v>316</v>
       </c>
-      <c r="C99" s="10" t="s">
+      <c r="C99" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="D99" s="10" t="s">
+      <c r="D99" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="E99" s="10" t="s">
+      <c r="E99" s="11" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="10">
+      <c r="A100" s="11">
         <v>11</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B100" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="C100" s="10" t="s">
+      <c r="C100" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D100" s="11" t="s">
         <v>320</v>
       </c>
-      <c r="E100" s="10" t="s">
+      <c r="E100" s="11" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="10">
+      <c r="A101" s="11">
         <v>12</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B101" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="C101" s="10" t="s">
+      <c r="C101" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="D101" s="10" t="s">
+      <c r="D101" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E101" s="11" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="103" ht="20.4" spans="1:5">
-      <c r="A103" s="32" t="s">
+      <c r="A103" s="33" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="104" ht="19.2" spans="1:5">
-      <c r="A104" s="37" t="s">
+      <c r="A104" s="38" t="s">
         <v>325</v>
       </c>
-      <c r="B104" s="18"/>
+      <c r="B104" s="19"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="11" t="s">
+      <c r="A105" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="12" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="13" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="12" t="s">
+      <c r="A107" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="13" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="12" t="s">
+      <c r="A108" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="13" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="13" t="s">
         <v>333</v>
       </c>
-      <c r="B109" s="12" t="s">
+      <c r="B109" s="13" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="12" t="s">
+      <c r="A110" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="13" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="12" t="s">
+      <c r="A111" s="13" t="s">
         <v>337</v>
       </c>
-      <c r="B111" s="12" t="s">
+      <c r="B111" s="13" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="12" t="s">
+      <c r="A112" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="13" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="12" t="s">
+      <c r="A113" s="13" t="s">
         <v>341</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="13" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="12" t="s">
+      <c r="A114" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="B114" s="12" t="s">
+      <c r="B114" s="13" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="12" t="s">
+      <c r="A115" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="13" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="12" t="s">
+      <c r="A116" s="13" t="s">
         <v>347</v>
       </c>
-      <c r="B116" s="12" t="s">
+      <c r="B116" s="13" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="12" t="s">
+      <c r="A117" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="B117" s="12" t="s">
+      <c r="B117" s="13" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="119" ht="19.2" spans="1:2">
-      <c r="A119" s="38" t="s">
+      <c r="A119" s="39" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="39" t="s">
+      <c r="A121" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="B121" s="39" t="s">
+      <c r="B121" s="40" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="12" t="s">
+      <c r="A122" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="B122" s="12" t="s">
+      <c r="B122" s="13" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="12" t="s">
+      <c r="A123" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="B123" s="12" t="s">
+      <c r="B123" s="13" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="12" t="s">
+      <c r="A124" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="B124" s="12" t="s">
+      <c r="B124" s="13" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="12" t="s">
+      <c r="A125" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="B125" s="12" t="s">
+      <c r="B125" s="13" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="12" t="s">
+      <c r="A126" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="B126" s="12" t="s">
+      <c r="B126" s="13" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="12" t="s">
+      <c r="A127" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="13" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="12" t="s">
+      <c r="A128" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="B128" s="12" t="s">
+      <c r="B128" s="13" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="12" t="s">
+      <c r="A129" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="B129" s="13" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="131" ht="19.2" spans="1:2">
-      <c r="A131" s="38" t="s">
+      <c r="A131" s="39" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="39" t="s">
+      <c r="A133" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="B133" s="39" t="s">
+      <c r="B133" s="40" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="12" t="s">
+      <c r="A134" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="13" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="12" t="s">
+      <c r="A135" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="B135" s="12" t="s">
+      <c r="B135" s="13" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="12" t="s">
+      <c r="A136" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="B136" s="12" t="s">
+      <c r="B136" s="13" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="12" t="s">
+      <c r="A137" s="13" t="s">
         <v>339</v>
       </c>
-      <c r="B137" s="12" t="s">
+      <c r="B137" s="13" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="12" t="s">
+      <c r="A138" s="13" t="s">
         <v>343</v>
       </c>
-      <c r="B138" s="12" t="s">
+      <c r="B138" s="13" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="12" t="s">
+      <c r="A139" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="13" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="12" t="s">
+      <c r="A140" s="13" t="s">
         <v>358</v>
       </c>
-      <c r="B140" s="12" t="s">
+      <c r="B140" s="13" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="12" t="s">
+      <c r="A141" s="13" t="s">
         <v>360</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="B141" s="13" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="143" ht="19.2" spans="1:2">
-      <c r="A143" s="38" t="s">
+      <c r="A143" s="39" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="39" t="s">
+      <c r="A145" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="B145" s="39" t="s">
+      <c r="B145" s="40" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="12" t="s">
+      <c r="A146" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="B146" s="12" t="s">
+      <c r="B146" s="13" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="12" t="s">
+      <c r="A147" s="13" t="s">
         <v>364</v>
       </c>
-      <c r="B147" s="12" t="s">
+      <c r="B147" s="13" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="12" t="s">
+      <c r="A148" s="13" t="s">
         <v>366</v>
       </c>
-      <c r="B148" s="12" t="s">
+      <c r="B148" s="13" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="12" t="s">
+      <c r="A149" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="B149" s="12" t="s">
+      <c r="B149" s="13" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="12" t="s">
+      <c r="A150" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="B150" s="12" t="s">
+      <c r="B150" s="13" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="12" t="s">
+      <c r="A151" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="B151" s="12" t="s">
+      <c r="B151" s="13" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="12" t="s">
+      <c r="A152" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="B152" s="12" t="s">
+      <c r="B152" s="13" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="154" ht="19.2" spans="1:2">
-      <c r="A154" s="38" t="s">
+      <c r="A154" s="39" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="39" t="s">
+      <c r="A156" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="B156" s="39" t="s">
+      <c r="B156" s="40" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="40" t="s">
+      <c r="A157" s="41" t="s">
         <v>329</v>
       </c>
-      <c r="B157" s="40" t="s">
+      <c r="B157" s="41" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="40" t="s">
+      <c r="A158" s="41" t="s">
         <v>377</v>
       </c>
-      <c r="B158" s="40" t="s">
+      <c r="B158" s="41" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="40" t="s">
+      <c r="A159" s="41" t="s">
         <v>379</v>
       </c>
-      <c r="B159" s="40" t="s">
+      <c r="B159" s="41" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="40" t="s">
+      <c r="A160" s="41" t="s">
         <v>381</v>
       </c>
-      <c r="B160" s="40" t="s">
+      <c r="B160" s="41" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="40" t="s">
+      <c r="A161" s="41" t="s">
         <v>383</v>
       </c>
-      <c r="B161" s="40" t="s">
+      <c r="B161" s="41" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="40" t="s">
+      <c r="A162" s="41" t="s">
         <v>385</v>
       </c>
-      <c r="B162" s="40" t="s">
+      <c r="B162" s="41" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="165" ht="19.2" spans="1:4">
-      <c r="A165" s="38" t="s">
+      <c r="A165" s="39" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="39" t="s">
+      <c r="A167" s="40" t="s">
         <v>326</v>
       </c>
-      <c r="B167" s="39" t="s">
+      <c r="B167" s="40" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="40" t="s">
+      <c r="A168" s="41" t="s">
         <v>352</v>
       </c>
-      <c r="B168" s="40" t="s">
+      <c r="B168" s="41" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="40" t="s">
+      <c r="A169" s="41" t="s">
         <v>388</v>
       </c>
-      <c r="B169" s="40" t="s">
+      <c r="B169" s="41" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="40" t="s">
+      <c r="A170" s="41" t="s">
         <v>390</v>
       </c>
-      <c r="B170" s="40" t="s">
+      <c r="B170" s="41" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="40" t="s">
+      <c r="A171" s="41" t="s">
         <v>392</v>
       </c>
-      <c r="B171" s="40" t="s">
+      <c r="B171" s="41" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="40" t="s">
+      <c r="A172" s="41" t="s">
         <v>394</v>
       </c>
-      <c r="B172" s="40" t="s">
+      <c r="B172" s="41" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="174" ht="20.4" spans="1:4">
-      <c r="A174" s="32" t="s">
+      <c r="A174" s="33" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="9" t="s">
+      <c r="A176" s="10" t="s">
         <v>397</v>
       </c>
-      <c r="B176" s="9" t="s">
+      <c r="B176" s="10" t="s">
         <v>398</v>
       </c>
-      <c r="C176" s="9" t="s">
+      <c r="C176" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="D176" s="9" t="s">
+      <c r="D176" s="10" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="41" t="s">
+      <c r="A177" s="42" t="s">
         <v>401</v>
       </c>
-      <c r="B177" s="10" t="s">
+      <c r="B177" s="11" t="s">
         <v>402</v>
       </c>
-      <c r="C177" s="10" t="s">
+      <c r="C177" s="11" t="s">
         <v>403</v>
       </c>
-      <c r="D177" s="10" t="s">
+      <c r="D177" s="11" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="42"/>
-      <c r="B178" s="10" t="s">
+      <c r="A178" s="43"/>
+      <c r="B178" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="10" t="s">
+      <c r="C178" s="11" t="s">
         <v>404</v>
       </c>
-      <c r="D178" s="10" t="s">
+      <c r="D178" s="11" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="43"/>
-      <c r="B179" s="10" t="s">
+      <c r="A179" s="44"/>
+      <c r="B179" s="11" t="s">
         <v>405</v>
       </c>
-      <c r="C179" s="10" t="s">
+      <c r="C179" s="11" t="s">
         <v>406</v>
       </c>
-      <c r="D179" s="10" t="s">
+      <c r="D179" s="11" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="41" t="s">
+      <c r="A180" s="42" t="s">
         <v>407</v>
       </c>
-      <c r="B180" s="10" t="s">
+      <c r="B180" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="C180" s="10" t="s">
+      <c r="C180" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="D180" s="10" t="s">
+      <c r="D180" s="11" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="42"/>
-      <c r="B181" s="10" t="s">
+      <c r="A181" s="43"/>
+      <c r="B181" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="C181" s="10" t="s">
+      <c r="C181" s="11" t="s">
         <v>411</v>
       </c>
-      <c r="D181" s="10" t="s">
+      <c r="D181" s="11" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="42"/>
-      <c r="B182" s="10" t="s">
+      <c r="A182" s="43"/>
+      <c r="B182" s="11" t="s">
         <v>412</v>
       </c>
-      <c r="C182" s="10" t="s">
+      <c r="C182" s="11" t="s">
         <v>413</v>
       </c>
-      <c r="D182" s="10" t="s">
+      <c r="D182" s="11" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="43"/>
-      <c r="B183" s="10" t="s">
+      <c r="A183" s="44"/>
+      <c r="B183" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C183" s="10" t="s">
+      <c r="C183" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="D183" s="10" t="s">
+      <c r="D183" s="11" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="184" ht="28.8" spans="1:4">
-      <c r="A184" s="41" t="s">
+      <c r="A184" s="42" t="s">
         <v>415</v>
       </c>
-      <c r="B184" s="10" t="s">
+      <c r="B184" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="C184" s="10" t="s">
+      <c r="C184" s="11" t="s">
         <v>416</v>
       </c>
-      <c r="D184" s="10" t="s">
+      <c r="D184" s="11" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="42"/>
-      <c r="B185" s="10" t="s">
+      <c r="A185" s="43"/>
+      <c r="B185" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="C185" s="10" t="s">
+      <c r="C185" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="D185" s="10" t="s">
+      <c r="D185" s="11" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="43"/>
-      <c r="B186" s="10" t="s">
+      <c r="A186" s="44"/>
+      <c r="B186" s="11" t="s">
         <v>420</v>
       </c>
-      <c r="C186" s="10" t="s">
+      <c r="C186" s="11" t="s">
         <v>421</v>
       </c>
-      <c r="D186" s="10" t="s">
+      <c r="D186" s="11" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="41" t="s">
+      <c r="A187" s="42" t="s">
         <v>422</v>
       </c>
-      <c r="B187" s="10" t="s">
+      <c r="B187" s="11" t="s">
         <v>423</v>
       </c>
-      <c r="C187" s="10" t="s">
+      <c r="C187" s="11" t="s">
         <v>424</v>
       </c>
-      <c r="D187" s="10" t="s">
+      <c r="D187" s="11" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="42"/>
-      <c r="B188" s="10" t="s">
+      <c r="A188" s="43"/>
+      <c r="B188" s="11" t="s">
         <v>425</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C188" s="11" t="s">
         <v>426</v>
       </c>
-      <c r="D188" s="10" t="s">
+      <c r="D188" s="11" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="43"/>
-      <c r="B189" s="10" t="s">
+      <c r="A189" s="44"/>
+      <c r="B189" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="C189" s="10" t="s">
+      <c r="C189" s="11" t="s">
         <v>428</v>
       </c>
-      <c r="D189" s="10" t="s">
+      <c r="D189" s="11" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="191" ht="20.4" spans="1:4">
-      <c r="A191" s="32" t="s">
+      <c r="A191" s="33" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="193" ht="43.2" spans="1:9">
-      <c r="A193" s="9" t="s">
+      <c r="A193" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="B193" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="C193" s="9" t="s">
+      <c r="C193" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="D193" s="9" t="s">
+      <c r="D193" s="10" t="s">
         <v>431</v>
       </c>
-      <c r="E193" s="9" t="s">
+      <c r="E193" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="F193" s="9" t="s">
+      <c r="F193" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="G193" s="9" t="s">
+      <c r="G193" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="H193" s="9" t="s">
+      <c r="H193" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="I193" s="9" t="s">
+      <c r="I193" s="10" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194" s="10">
+      <c r="A194" s="11">
         <v>1</v>
       </c>
-      <c r="B194" s="10" t="s">
+      <c r="B194" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="C194" s="10">
+      <c r="C194" s="11">
         <v>92</v>
       </c>
-      <c r="D194" s="10">
+      <c r="D194" s="11">
         <v>88</v>
       </c>
-      <c r="E194" s="10">
+      <c r="E194" s="11">
         <v>85</v>
       </c>
-      <c r="F194" s="10">
+      <c r="F194" s="11">
         <v>90</v>
       </c>
-      <c r="G194" s="10">
+      <c r="G194" s="11">
         <v>87</v>
       </c>
-      <c r="H194" s="10">
+      <c r="H194" s="11">
         <v>89</v>
       </c>
-      <c r="I194" s="10" t="s">
+      <c r="I194" s="11" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="195" spans="1:9">
-      <c r="A195" s="10">
+      <c r="A195" s="11">
         <v>2</v>
       </c>
-      <c r="B195" s="10" t="s">
+      <c r="B195" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="C195" s="10">
+      <c r="C195" s="11">
         <v>90</v>
       </c>
-      <c r="D195" s="10">
+      <c r="D195" s="11">
         <v>91</v>
       </c>
-      <c r="E195" s="10">
+      <c r="E195" s="11">
         <v>82</v>
       </c>
-      <c r="F195" s="10">
+      <c r="F195" s="11">
         <v>86</v>
       </c>
-      <c r="G195" s="10">
+      <c r="G195" s="11">
         <v>85</v>
       </c>
-      <c r="H195" s="10">
+      <c r="H195" s="11">
         <v>88.1</v>
       </c>
-      <c r="I195" s="10" t="s">
+      <c r="I195" s="11" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="196" spans="1:9">
-      <c r="A196" s="10">
+      <c r="A196" s="11">
         <v>3</v>
       </c>
-      <c r="B196" s="10" t="s">
+      <c r="B196" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="C196" s="10">
+      <c r="C196" s="11">
         <v>75</v>
       </c>
-      <c r="D196" s="10">
+      <c r="D196" s="11">
         <v>70</v>
       </c>
-      <c r="E196" s="10">
+      <c r="E196" s="11">
         <v>60</v>
       </c>
-      <c r="F196" s="10">
+      <c r="F196" s="11">
         <v>80</v>
       </c>
-      <c r="G196" s="10">
+      <c r="G196" s="11">
         <v>65</v>
       </c>
-      <c r="H196" s="10">
+      <c r="H196" s="11">
         <v>72</v>
       </c>
-      <c r="I196" s="10" t="s">
+      <c r="I196" s="11" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="197" spans="1:9">
-      <c r="A197" s="10">
+      <c r="A197" s="11">
         <v>4</v>
       </c>
-      <c r="B197" s="10" t="s">
+      <c r="B197" s="11" t="s">
         <v>436</v>
       </c>
-      <c r="C197" s="10">
+      <c r="C197" s="11">
         <v>40</v>
       </c>
-      <c r="D197" s="10">
+      <c r="D197" s="11">
         <v>35</v>
       </c>
-      <c r="E197" s="10">
+      <c r="E197" s="11">
         <v>20</v>
       </c>
-      <c r="F197" s="10">
+      <c r="F197" s="11">
         <v>50</v>
       </c>
-      <c r="G197" s="10">
+      <c r="G197" s="11">
         <v>30</v>
       </c>
-      <c r="H197" s="10">
+      <c r="H197" s="11">
         <v>36.5</v>
       </c>
-      <c r="I197" s="10" t="s">
+      <c r="I197" s="11" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="200" ht="20.4" spans="1:9">
-      <c r="A200" s="32" t="s">
+      <c r="A200" s="33" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="202" ht="15.6" spans="1:9">
-      <c r="A202" s="37" t="s">
+      <c r="A202" s="38" t="s">
         <v>438</v>
       </c>
-      <c r="B202" s="18"/>
+      <c r="B202" s="19"/>
     </row>
     <row r="203" spans="1:9">
-      <c r="A203" s="11" t="s">
+      <c r="A203" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="B203" s="11" t="s">
+      <c r="B203" s="12" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:9">
-      <c r="A204" s="12" t="s">
+      <c r="A204" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="B204" s="12" t="s">
+      <c r="B204" s="13" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="205" spans="1:9">
-      <c r="A205" s="12" t="s">
+      <c r="A205" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="B205" s="12" t="s">
+      <c r="B205" s="13" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="206" spans="1:9">
-      <c r="A206" s="12" t="s">
+      <c r="A206" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="B206" s="12" t="s">
+      <c r="B206" s="13" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="208" ht="15.6" spans="1:9">
-      <c r="A208" s="37" t="s">
+      <c r="A208" s="38" t="s">
         <v>442</v>
       </c>
-      <c r="B208" s="18"/>
-      <c r="C208" s="18"/>
+      <c r="B208" s="19"/>
+      <c r="C208" s="19"/>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="11" t="s">
+      <c r="A209" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="B209" s="11" t="s">
+      <c r="B209" s="12" t="s">
         <v>444</v>
       </c>
-      <c r="C209" s="11" t="s">
+      <c r="C209" s="12" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="12" t="s">
+      <c r="A210" s="13" t="s">
         <v>446</v>
       </c>
-      <c r="B210" s="12" t="s">
+      <c r="B210" s="13" t="s">
         <v>447</v>
       </c>
-      <c r="C210" s="12" t="s">
+      <c r="C210" s="13" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="12" t="s">
+      <c r="A211" s="13" t="s">
         <v>449</v>
       </c>
-      <c r="B211" s="12" t="s">
+      <c r="B211" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="C211" s="12" t="s">
+      <c r="C211" s="13" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="12" t="s">
+      <c r="A212" s="13" t="s">
         <v>452</v>
       </c>
-      <c r="B212" s="12" t="s">
+      <c r="B212" s="13" t="s">
         <v>453</v>
       </c>
-      <c r="C212" s="12" t="s">
+      <c r="C212" s="13" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="12" t="s">
+      <c r="A213" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="B213" s="12" t="s">
+      <c r="B213" s="13" t="s">
         <v>456</v>
       </c>
-      <c r="C213" s="12" t="s">
+      <c r="C213" s="13" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="12" t="s">
+      <c r="A214" s="13" t="s">
         <v>458</v>
       </c>
-      <c r="B214" s="12" t="s">
+      <c r="B214" s="13" t="s">
         <v>459</v>
       </c>
-      <c r="C214" s="12" t="s">
+      <c r="C214" s="13" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="12" t="s">
+      <c r="A215" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="B215" s="12" t="s">
+      <c r="B215" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="C215" s="12" t="s">
+      <c r="C215" s="13" t="s">
         <v>463</v>
       </c>
     </row>
@@ -6021,22 +6590,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>464</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="19" t="s">
         <v>465</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="19" t="s">
         <v>466</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F2" s="19" t="s">
         <v>467</v>
       </c>
     </row>
@@ -6058,285 +6627,285 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="5"/>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="8" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="11" ht="20.4" spans="1:3">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>483</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="11" t="s">
         <v>485</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="11" t="s">
         <v>486</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="11" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="11" t="s">
         <v>489</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:3">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="11" t="s">
         <v>491</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="11" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="11" t="s">
         <v>494</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="11" t="s">
         <v>495</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="19" ht="20.4" spans="1:3">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="9" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="13" t="s">
         <v>498</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="13" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>500</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="13" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="24" ht="28.8" spans="1:3">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="13" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="12" t="s">
+      <c r="A25" s="13" t="s">
         <v>504</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="13" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="27" ht="20.4" spans="1:3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" s="10" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="11" t="s">
         <v>507</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="11" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="11" t="s">
         <v>509</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="11" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="11" t="s">
         <v>511</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="11" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="11" t="s">
         <v>513</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="11" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="35" ht="20.4" spans="1:2">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="9" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="12" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="13" t="s">
         <v>516</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="13" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="12" t="s">
+      <c r="A39" s="13" t="s">
         <v>518</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="13" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="13" t="s">
         <v>520</v>
       </c>
-      <c r="B40" s="12" t="s">
+      <c r="B40" s="13" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="43" ht="20.4" spans="1:2">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="9" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="12" t="s">
         <v>326</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="12" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="12" t="s">
+      <c r="A46" s="13" t="s">
         <v>524</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="13" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="12" t="s">
+      <c r="A47" s="13" t="s">
         <v>526</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B47" s="13" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="13" t="s">
         <v>528</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="B48" s="13" t="s">
         <v>529</v>
       </c>
     </row>
@@ -6346,148 +6915,148 @@
       </c>
     </row>
     <row r="53" ht="16.8" spans="1:2">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="14" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="56" ht="27" spans="1:2">
-      <c r="A56" s="7" t="s">
+      <c r="A56" s="8" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="12" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="13" t="s">
         <v>535</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="13" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12" t="s">
+      <c r="A60" s="13"/>
+      <c r="B60" s="13" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12" t="s">
+      <c r="A61" s="13"/>
+      <c r="B61" s="13" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12" t="s">
+      <c r="A62" s="13"/>
+      <c r="B62" s="13" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12" t="s">
+      <c r="A63" s="13"/>
+      <c r="B63" s="13" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="12" t="s">
+      <c r="A64" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="13" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12" t="s">
+      <c r="A65" s="13"/>
+      <c r="B65" s="13" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12" t="s">
+      <c r="A66" s="13"/>
+      <c r="B66" s="13" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12" t="s">
+      <c r="A67" s="13"/>
+      <c r="B67" s="13" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="70" ht="22.2" spans="1:2">
-      <c r="A70" s="14" t="s">
+      <c r="A70" s="15" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="72" ht="15.6" spans="1:2">
-      <c r="A72" s="15" t="s">
+      <c r="A72" s="16" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="74" ht="19.2" spans="1:2">
-      <c r="A74" s="16" t="s">
+      <c r="A74" s="17" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="75" ht="19.2" spans="1:2">
-      <c r="A75" s="16" t="s">
+      <c r="A75" s="17" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="76" ht="15.6" spans="1:2">
-      <c r="A76" s="16" t="s">
+      <c r="A76" s="17" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="17" t="s">
+      <c r="A80" s="18" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="10" t="s">
         <v>552</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="10" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="11" t="s">
         <v>554</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="11" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="11" t="s">
         <v>556</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="11" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="11" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="11" t="s">
         <v>560</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="11" t="s">
         <v>561</v>
       </c>
     </row>
@@ -6504,136 +7073,1163 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B1:F25"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="5"/>
-  <cols>
-    <col min="2" max="2" width="14.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="19.8888888888889" customWidth="1"/>
-    <col min="4" max="4" width="14.1111111111111" customWidth="1"/>
-  </cols>
+  <dimension ref="A2:A9"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="2:6">
-      <c r="F1" s="1" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="2" spans="2:6">
-      <c r="B2" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" s="3" t="s">
         <v>563</v>
       </c>
     </row>
-    <row r="3" spans="2:6">
-      <c r="C3" t="s">
+    <row r="5" spans="1:1">
+      <c r="A5" s="3" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="5" spans="2:6">
-      <c r="C5" s="2" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="D5" t="s">
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="3" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="6" spans="2:6">
-      <c r="C6" s="2"/>
-      <c r="D6" t="s">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C230"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="7" spans="2:6">
-      <c r="C7" s="2"/>
-      <c r="D7" t="s">
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
         <v>568</v>
       </c>
     </row>
-    <row r="8" spans="2:6">
-      <c r="C8" s="2"/>
-      <c r="D8" t="s">
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
         <v>569</v>
       </c>
     </row>
-    <row r="9" spans="2:6">
-      <c r="C9" s="2"/>
-      <c r="D9" t="s">
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="10" spans="2:6">
-      <c r="C10" s="2"/>
-      <c r="D10" t="s">
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="13" spans="2:6">
-      <c r="C13" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="14" spans="2:6">
-      <c r="C14" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
         <v>573</v>
       </c>
     </row>
-    <row r="15" spans="2:6">
-      <c r="C15" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="16" spans="2:6">
-      <c r="C16" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3">
-      <c r="C17" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="18" spans="3:3">
-      <c r="C18" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3">
-      <c r="C19" t="s">
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="20" spans="3:3">
-      <c r="C20" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" t="s">
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
         <v>577</v>
       </c>
     </row>
-    <row r="22" spans="3:3">
-      <c r="C22" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="23" spans="3:3">
-      <c r="C23" t="s">
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
         <v>578</v>
       </c>
     </row>
-    <row r="24" spans="3:3">
-      <c r="C24" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="25" spans="3:3">
-      <c r="C25" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
         <v>579</v>
       </c>
     </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B36" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>332</v>
+      </c>
+      <c r="B37" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>342</v>
+      </c>
+      <c r="B38" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>344</v>
+      </c>
+      <c r="B39" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>346</v>
+      </c>
+      <c r="B40" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>340</v>
+      </c>
+      <c r="B41" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>601</v>
+      </c>
+      <c r="B48" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>603</v>
+      </c>
+      <c r="B49" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>605</v>
+      </c>
+      <c r="B50" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" t="s">
+        <v>607</v>
+      </c>
+      <c r="B51" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B52" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53" t="s">
+        <v>610</v>
+      </c>
+      <c r="B53" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" t="s">
+        <v>615</v>
+      </c>
+      <c r="B59" t="s">
+        <v>342</v>
+      </c>
+      <c r="C59" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" t="s">
+        <v>617</v>
+      </c>
+      <c r="B60" t="s">
+        <v>617</v>
+      </c>
+      <c r="C60" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" t="s">
+        <v>617</v>
+      </c>
+      <c r="B61" t="s">
+        <v>619</v>
+      </c>
+      <c r="C61" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62" t="s">
+        <v>619</v>
+      </c>
+      <c r="B62" t="s">
+        <v>617</v>
+      </c>
+      <c r="C62" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
+        <v>619</v>
+      </c>
+      <c r="B63" t="s">
+        <v>619</v>
+      </c>
+      <c r="C63" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>629</v>
+      </c>
+      <c r="B72" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="1">
+        <v>46024</v>
+      </c>
+      <c r="B73" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B74" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B75" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>633</v>
+      </c>
+      <c r="B76" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="e" cm="1">
+        <f t="array" ref="A83">强趋势启动信号</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>175</v>
+      </c>
+      <c r="B90" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>641</v>
+      </c>
+      <c r="B91" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>643</v>
+      </c>
+      <c r="B92" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>645</v>
+      </c>
+      <c r="B93" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>213</v>
+      </c>
+      <c r="B94" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>648</v>
+      </c>
+      <c r="B95" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>155</v>
+      </c>
+      <c r="B101" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>654</v>
+      </c>
+      <c r="B102" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>655</v>
+      </c>
+      <c r="B103" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>656</v>
+      </c>
+      <c r="B104" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>213</v>
+      </c>
+      <c r="B105" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>657</v>
+      </c>
+      <c r="B106" s="2">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>659</v>
+      </c>
+      <c r="B108" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>661</v>
+      </c>
+      <c r="B109" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>663</v>
+      </c>
+      <c r="B110" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>665</v>
+      </c>
+      <c r="B111" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>667</v>
+      </c>
+      <c r="B112" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>669</v>
+      </c>
+      <c r="B113" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>673</v>
+      </c>
+      <c r="B118" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>674</v>
+      </c>
+      <c r="B119" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>676</v>
+      </c>
+      <c r="B120" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>678</v>
+      </c>
+      <c r="B121" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>680</v>
+      </c>
+      <c r="B122" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>682</v>
+      </c>
+      <c r="B123" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>684</v>
+      </c>
+      <c r="B124" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" t="e" cm="1">
+        <f t="array" ref="A131">-ts_code</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" t="e" cm="1">
+        <f t="array" ref="A132">-trade_date</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" t="e" cm="1">
+        <f t="array" ref="A133">-close</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" t="e" cm="1">
+        <f t="array" ref="A134">-volume</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" t="e" cm="1">
+        <f t="array" ref="A135">-turnover</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" t="e" cm="1">
+        <f t="array" ref="A136">-change_pct</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137" t="e" cm="1">
+        <f t="array" ref="A137">-turnover_rate</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" t="e" cm="1">
+        <f t="array" ref="A140">-industry_code</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" t="e" cm="1">
+        <f t="array" ref="A141">-trade_date</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" t="e" cm="1">
+        <f t="array" ref="A142">-total_volume</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" t="e" cm="1">
+        <f t="array" ref="A143">-total_turnover</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" t="e" cm="1">
+        <f t="array" ref="A144">-avg_change_pct</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" t="e" cm="1">
+        <f t="array" ref="A145">-rising_ratio</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" t="e" cm="1">
+        <f t="array" ref="A146">-volume_ratio_20d</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" t="e" cm="1">
+        <f t="array" ref="A149">-industry_code</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" t="e" cm="1">
+        <f t="array" ref="A150">-trade_date</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" t="e" cm="1">
+        <f t="array" ref="A151">-score</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" t="e" cm="1">
+        <f t="array" ref="A152">-status</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" t="e" cm="1">
+        <f t="array" ref="A153">-signal_type</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230" t="s">
+        <v>753</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C5:C10"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/需求整理/industry_indicator_system.xlsx
+++ b/需求整理/industry_indicator_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13500" activeTab="6"/>
+    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Industry Indicators" sheetId="1" r:id="rId1"/>
@@ -12,8 +12,8 @@
     <sheet name="需求1—主线板块确认" sheetId="5" r:id="rId3"/>
     <sheet name="报表2—主线板块龙头" sheetId="4" r:id="rId4"/>
     <sheet name="需求3—量化主线板块" sheetId="6" r:id="rId5"/>
-    <sheet name="产业链分析" sheetId="7" r:id="rId6"/>
-    <sheet name="Sheet2" sheetId="8" r:id="rId7"/>
+    <sheet name="AI产业数据库" sheetId="7" r:id="rId6"/>
+    <sheet name="板块量价关系" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="754">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="838">
   <si>
     <t>指标名称</t>
   </si>
@@ -2090,67 +2090,458 @@
     <t>如果无Wind，可用“过去4季度净利润增速”替代</t>
   </si>
   <si>
-    <t>最终可以规划成四大能力：</t>
+    <t>产业线</t>
+  </si>
+  <si>
+    <t>板块</t>
+  </si>
+  <si>
+    <t>细分板块</t>
+  </si>
+  <si>
+    <t>产品</t>
+  </si>
+  <si>
+    <t>板块景气度</t>
+  </si>
+  <si>
+    <t>板块订单情况</t>
+  </si>
+  <si>
+    <t>产品对应龙头前3，毛利、收入、利润</t>
+  </si>
+  <si>
+    <t>客户</t>
+  </si>
+  <si>
+    <t>风险点</t>
+  </si>
+  <si>
+    <t>AI产业线</t>
+  </si>
+  <si>
+    <t>上游基础层</t>
+  </si>
+  <si>
+    <t>AI芯片</t>
+  </si>
+  <si>
+    <t>GPU/AI训练芯片</t>
+  </si>
+  <si>
+    <t>AI推理芯片</t>
+  </si>
+  <si>
+    <t>HBM（高带宽存储）</t>
+  </si>
+  <si>
+    <t>存算一体芯片</t>
+  </si>
+  <si>
+    <t>服务器与设备</t>
+  </si>
+  <si>
+    <t>AI服务器</t>
+  </si>
+  <si>
+    <t xml:space="preserve">液冷服务器 </t>
+  </si>
+  <si>
+    <t>存储设备</t>
+  </si>
+  <si>
+    <t>网络通信硬件</t>
+  </si>
+  <si>
+    <t>CPO光模块</t>
+  </si>
+  <si>
+    <t>光器件</t>
+  </si>
+  <si>
+    <t>高速铜连接</t>
+  </si>
+  <si>
+    <t>光纤光缆</t>
+  </si>
+  <si>
+    <t>PCB</t>
+  </si>
+  <si>
+    <t>数据中心与基础设施</t>
+  </si>
+  <si>
+    <t>IDC（互联网数据中心</t>
+  </si>
+  <si>
+    <t>AIDC（智算中心）</t>
+  </si>
+  <si>
+    <t>超节点技术</t>
+  </si>
+  <si>
+    <t>供配电/制冷系统</t>
+  </si>
+  <si>
+    <t>数据服务</t>
+  </si>
+  <si>
+    <t>数据标注/脱敏</t>
+  </si>
+  <si>
+    <t>合成数据</t>
+  </si>
+  <si>
+    <t>中游技术层：算法、模型与平台</t>
+  </si>
+  <si>
+    <t>大模型</t>
+  </si>
+  <si>
+    <t>语言大模型</t>
+  </si>
+  <si>
+    <t>多模态大模型</t>
+  </si>
+  <si>
+    <t>推理模型</t>
+  </si>
+  <si>
+    <t>AI算法与技术</t>
+  </si>
+  <si>
+    <t>AIGC（生成式AI）</t>
+  </si>
+  <si>
+    <t>机器视觉</t>
+  </si>
+  <si>
+    <t>虚拟人/数字人</t>
+  </si>
+  <si>
+    <t>智能体（Agent）</t>
+  </si>
+  <si>
+    <t>软件与服务</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基础及通用软件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">行业应用软件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">操作系统 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">办公软件 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">网络安全 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">物联网 </t>
+  </si>
+  <si>
+    <t>云计算与平台服务</t>
   </si>
   <si>
     <r>
-      <t>产业链图谱</t>
+      <t>云计算</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>：完整展示上下游、替代关系、技术路线。</t>
+      <t> </t>
     </r>
   </si>
   <si>
     <r>
-      <t>产业数据库</t>
+      <t>SaaS（软件即服务）</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>：景气度、估值、供需、价格、库存、资本开支等指标形成统一指标库。</t>
+      <t> </t>
     </r>
   </si>
   <si>
+    <t>MaaS（模型即服务）</t>
+  </si>
+  <si>
+    <t>边缘计算</t>
+  </si>
+  <si>
+    <t>下游应用层</t>
+  </si>
+  <si>
+    <t>端侧AI（AI硬件）</t>
+  </si>
+  <si>
+    <t>AI手机</t>
+  </si>
+  <si>
     <r>
-      <t>公司知识图谱</t>
+      <t>AI PC</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>：公司与产品、客户、供应商、细分赛道、产业链节点的关联关系。</t>
+      <t> </t>
     </r>
   </si>
   <si>
+    <t>AI眼镜</t>
+  </si>
+  <si>
+    <t>AI穿戴设备</t>
+  </si>
+  <si>
+    <t>智能家居</t>
+  </si>
+  <si>
+    <t>AIoT设备</t>
+  </si>
+  <si>
+    <t>智能驾驶</t>
+  </si>
+  <si>
     <r>
-      <t>AI研究引擎</t>
+      <t>L2+/L3智能驾驶</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
         <charset val="134"/>
-        <scheme val="minor"/>
       </rPr>
-      <t>：自动生成行业分析、龙头比较、轮动分析、风险提示，并支持自然语言提问，例如“AI服务器需求增加，哪些上游最受益？”或“半导体设备和电子特气哪个估值更有优势？”</t>
+      <t> </t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>Robotaxi（自动驾驶出租车）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>智驾芯片</t>
+  </si>
+  <si>
+    <t>激光雷达</t>
+  </si>
+  <si>
+    <t>人形机器人/具身智能</t>
+  </si>
+  <si>
+    <r>
+      <t>人形机器人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>具身智能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（进入实训阶段）</t>
+    </r>
+  </si>
+  <si>
+    <t>企业级AI应用</t>
+  </si>
+  <si>
+    <r>
+      <t>企业级AI Agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI办公</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI编程</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>消费级AI应用</t>
+  </si>
+  <si>
+    <r>
+      <t>AI搜索引擎</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI综合助手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（如DeepSeek、腾讯元宝）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI创作</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>AI生活娱乐</t>
+  </si>
+  <si>
+    <t>AI原生社交与陪伴</t>
+  </si>
+  <si>
+    <t>垂直行业AI应用</t>
+  </si>
+  <si>
+    <r>
+      <t>AI+工业制造</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（研发设计、生产调度等全环节）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI+医疗健康</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（病理诊断等）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI+金融</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（金融风控等）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AI+教育</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Segoe UI"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+  </si>
+  <si>
+    <t>AI+科学研究</t>
+  </si>
+  <si>
+    <t>数字营销/电子政务/在线教育/智慧医疗/游戏</t>
   </si>
   <si>
     <t>📊 量价关系分析模块需求文档（PRD）</t>
@@ -2724,7 +3115,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2733,15 +3124,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2929,6 +3320,12 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0F1115"/>
+      <name val="Segoe UI"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -3463,14 +3860,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -3480,13 +3886,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3522,7 +3928,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3531,7 +3937,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3546,7 +3952,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3554,7 +3960,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3945,273 +4351,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="22" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="22" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="22" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="22" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:6">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="22" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="22" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="22" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="22" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="22" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="22" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="22" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" ht="100.8" spans="1:6">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="44" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="44" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4236,473 +4642,473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="45" t="s">
+      <c r="B1" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="45" t="s">
+      <c r="D1" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="48" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="F1" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="7"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" ht="115.2" spans="1:7">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="46" t="s">
+      <c r="D2" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="10" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" ht="273.6" spans="1:7">
-      <c r="A3" s="46"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="46" t="s">
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="49" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="49" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="49" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="46"/>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="46" t="s">
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46" t="s">
+      <c r="E4" s="49"/>
+      <c r="F4" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="10" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="46"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="47"/>
-      <c r="D5" s="46" t="s">
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="7"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="46"/>
-      <c r="B6" s="46"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="46" t="s">
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="7"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" ht="72" spans="1:7">
-      <c r="A7" s="46"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="46" t="s">
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="46"/>
-      <c r="G7" s="7"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="46"/>
-      <c r="B8" s="46" t="s">
+      <c r="A8" s="49"/>
+      <c r="B8" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="46"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46" t="s">
+      <c r="A9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="7"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="46"/>
-      <c r="B10" s="46"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="46" t="s">
+      <c r="A10" s="49"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="7"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" ht="57.6" spans="1:7">
-      <c r="A11" s="46"/>
-      <c r="B11" s="46"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="46" t="s">
+      <c r="A11" s="49"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="49"/>
+      <c r="D11" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="46" t="s">
+      <c r="E11" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="46"/>
-      <c r="G11" s="7"/>
+      <c r="F11" s="49"/>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="46"/>
-      <c r="B12" s="46" t="s">
+      <c r="A12" s="49"/>
+      <c r="B12" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="49" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="7"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="46"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46" t="s">
+      <c r="A13" s="49"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="7"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" ht="43.2" spans="1:7">
-      <c r="A14" s="46"/>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46" t="s">
+      <c r="A14" s="49"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="46" t="s">
+      <c r="E14" s="49" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="46"/>
-      <c r="G14" s="7"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="10"/>
     </row>
     <row r="15" ht="57.6" spans="1:7">
-      <c r="A15" s="46"/>
-      <c r="B15" s="46" t="s">
+      <c r="A15" s="49"/>
+      <c r="B15" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="48" t="s">
+      <c r="C15" s="49"/>
+      <c r="D15" s="51" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="46" t="s">
+      <c r="E15" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="7"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="46" t="s">
+      <c r="A16" s="49" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="49" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="49" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="46" t="s">
+      <c r="E16" s="49" t="s">
         <v>110</v>
       </c>
-      <c r="F16" s="46"/>
-      <c r="G16" s="7"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="10"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="46"/>
-      <c r="B17" s="46"/>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46" t="s">
+      <c r="A17" s="49"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="46" t="s">
+      <c r="E17" s="49" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="46"/>
-      <c r="G17" s="7"/>
+      <c r="F17" s="49"/>
+      <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="46"/>
-      <c r="B18" s="46" t="s">
+      <c r="A18" s="49"/>
+      <c r="B18" s="49" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="46" t="s">
+      <c r="C18" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="48" t="s">
+      <c r="D18" s="51" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="48"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="7"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="46"/>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46" t="s">
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="7"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="46"/>
-      <c r="B20" s="46" t="s">
+      <c r="A20" s="49"/>
+      <c r="B20" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="D20" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="46" t="s">
+      <c r="E20" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="46"/>
-      <c r="G20" s="7"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="46"/>
-      <c r="B21" s="46"/>
-      <c r="C21" s="46"/>
-      <c r="D21" s="46" t="s">
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="49"/>
+      <c r="D21" s="49" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="46" t="s">
+      <c r="E21" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="46"/>
-      <c r="G21" s="7"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="10"/>
     </row>
     <row r="22" ht="72" spans="1:7">
-      <c r="A22" s="46"/>
-      <c r="B22" s="46" t="s">
+      <c r="A22" s="49"/>
+      <c r="B22" s="49" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="46"/>
-      <c r="E22" s="46" t="s">
+      <c r="D22" s="49"/>
+      <c r="E22" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="46"/>
-      <c r="G22" s="7"/>
+      <c r="F22" s="49"/>
+      <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="46" t="s">
+      <c r="A23" s="49" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="46"/>
-      <c r="G23" s="7"/>
+      <c r="E23" s="49"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="46"/>
-      <c r="B24" s="46"/>
-      <c r="C24" s="46" t="s">
+      <c r="A24" s="49"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="49" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="46"/>
-      <c r="F24" s="46"/>
-      <c r="G24" s="7"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="49"/>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" ht="43.2" spans="1:7">
-      <c r="A25" s="46"/>
-      <c r="B25" s="46"/>
-      <c r="C25" s="47" t="s">
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46" t="s">
+      <c r="D25" s="49"/>
+      <c r="E25" s="49" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="47"/>
-      <c r="G25" s="7"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="46"/>
-      <c r="B26" s="46" t="s">
+      <c r="A26" s="49"/>
+      <c r="B26" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="46"/>
-      <c r="E26" s="46"/>
-      <c r="F26" s="46"/>
-      <c r="G26" s="7"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="46"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46" t="s">
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="7"/>
+      <c r="D27" s="49"/>
+      <c r="E27" s="49"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="10"/>
     </row>
     <row r="28" ht="43.2" spans="1:7">
-      <c r="A28" s="46"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="47" t="s">
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="46"/>
-      <c r="E28" s="46" t="s">
+      <c r="D28" s="49"/>
+      <c r="E28" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="46"/>
-      <c r="G28" s="7"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="46"/>
-      <c r="B29" s="46" t="s">
+      <c r="A29" s="49"/>
+      <c r="B29" s="49" t="s">
         <v>139</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="46" t="s">
+      <c r="D29" s="49" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="46"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="7"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="46"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="47" t="s">
+      <c r="A30" s="49"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="46" t="s">
+      <c r="D30" s="49" t="s">
         <v>143</v>
       </c>
-      <c r="E30" s="46"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="7"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="10"/>
     </row>
     <row r="31" ht="43.2" spans="1:7">
-      <c r="A31" s="46"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="47" t="s">
+      <c r="A31" s="49"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="48"/>
-      <c r="E31" s="46" t="s">
+      <c r="D31" s="51"/>
+      <c r="E31" s="49" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="47"/>
-      <c r="G31" s="7"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" ht="57.6" spans="1:7">
-      <c r="A32" s="46"/>
-      <c r="B32" s="47" t="s">
+      <c r="A32" s="49"/>
+      <c r="B32" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="48"/>
-      <c r="E32" s="46" t="s">
+      <c r="D32" s="51"/>
+      <c r="E32" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="F32" s="47"/>
-      <c r="G32" s="7"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="10"/>
     </row>
     <row r="33" ht="158.4" spans="1:7">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="51" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="32" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="29"/>
-      <c r="F33" s="48"/>
-      <c r="G33" s="7"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -4743,1822 +5149,1822 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="23" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" ht="20.4" spans="1:4">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="15" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="4" ht="28.8" spans="1:4">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="25">
         <v>0.35</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="16" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="5" ht="28.8" spans="1:4">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="25">
         <v>0.25</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="16" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="6" ht="28.8" spans="1:4">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="25">
         <v>0.15</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="16" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="25">
         <v>0.15</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="16" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="25">
         <v>0.1</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="16" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:4">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="26" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" ht="19.2" spans="1:4">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="27" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="26"/>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="29"/>
+      <c r="B14" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="14" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="26"/>
-      <c r="B15" s="11" t="s">
+      <c r="A15" s="29"/>
+      <c r="B15" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="14" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="27"/>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="30"/>
+      <c r="B16" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="14" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="26"/>
-      <c r="B19" s="11" t="s">
+      <c r="A19" s="29"/>
+      <c r="B19" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="14" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="26"/>
-      <c r="B20" s="11" t="s">
+      <c r="A20" s="29"/>
+      <c r="B20" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="14" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="27"/>
-      <c r="B21" s="11" t="s">
+      <c r="A21" s="30"/>
+      <c r="B21" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="14" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="28" t="s">
+      <c r="D24" s="31" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="26"/>
-      <c r="B25" s="29" t="s">
+      <c r="A25" s="29"/>
+      <c r="B25" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="32" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="29" t="s">
+      <c r="D25" s="32" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="26"/>
-      <c r="B26" s="29" t="s">
+      <c r="A26" s="29"/>
+      <c r="B26" s="32" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="32" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="29" t="s">
+      <c r="D26" s="32" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="27"/>
-      <c r="B27" s="29" t="s">
+      <c r="A27" s="30"/>
+      <c r="B27" s="32" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="32" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="32" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="33" t="s">
         <v>205</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="31" t="s">
+      <c r="D29" s="34" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="30"/>
-      <c r="B30" s="29" t="s">
+      <c r="A30" s="33"/>
+      <c r="B30" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="D30" s="29" t="s">
+      <c r="D30" s="32" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="30"/>
-      <c r="B31" s="29" t="s">
+      <c r="A31" s="33"/>
+      <c r="B31" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="D31" s="29" t="s">
+      <c r="D31" s="32" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="35" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="13" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="32"/>
-      <c r="B34" s="11" t="s">
+      <c r="A34" s="35"/>
+      <c r="B34" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="14" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="32"/>
-      <c r="B35" s="11" t="s">
+      <c r="A35" s="35"/>
+      <c r="B35" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="D35" s="14" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="38" ht="20.4" spans="1:4">
-      <c r="A38" s="33" t="s">
+      <c r="A38" s="36" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="13" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="13" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="41" ht="28.8" spans="1:4">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="14" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="42" ht="28.8" spans="1:4">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="14" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="43" ht="28.8" spans="1:4">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="14" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="14" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="47" ht="15.6" spans="1:4">
-      <c r="A47" s="23" t="s">
+      <c r="A47" s="26" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="10" t="s">
+      <c r="A49" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="13" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="14" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="14" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="14" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="56" ht="20.4" spans="1:3">
-      <c r="A56" s="33" t="s">
+      <c r="A56" s="36" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="10" t="s">
+      <c r="A58" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="10" t="s">
+      <c r="C58" s="13" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="14" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="14" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="65" ht="37.8" spans="1:8">
-      <c r="A65" s="33" t="s">
+      <c r="A65" s="36" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="67" ht="28.8" spans="1:8">
-      <c r="A67" s="10" t="s">
+      <c r="A67" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="13" t="s">
         <v>258</v>
       </c>
-      <c r="F67" s="10" t="s">
+      <c r="F67" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="G67" s="10" t="s">
+      <c r="G67" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="H67" s="10" t="s">
+      <c r="H67" s="13" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="11">
+      <c r="A68" s="14">
         <v>1</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C68" s="11">
+      <c r="C68" s="14">
         <v>91</v>
       </c>
-      <c r="D68" s="11">
+      <c r="D68" s="14">
         <v>6</v>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="37">
         <v>0.082</v>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="14">
         <v>4</v>
       </c>
-      <c r="G68" s="35">
+      <c r="G68" s="38">
         <v>0.4</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="14" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="11">
+      <c r="A69" s="14">
         <v>2</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="14">
         <v>88</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="14">
         <v>8</v>
       </c>
-      <c r="E69" s="34">
+      <c r="E69" s="37">
         <v>0.075</v>
       </c>
-      <c r="F69" s="11">
+      <c r="F69" s="14">
         <v>3</v>
       </c>
-      <c r="G69" s="35">
+      <c r="G69" s="38">
         <v>0.25</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="11">
+      <c r="A70" s="14">
         <v>3</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C70" s="11">
+      <c r="C70" s="14">
         <v>82</v>
       </c>
-      <c r="D70" s="11">
+      <c r="D70" s="14">
         <v>4</v>
       </c>
-      <c r="E70" s="34">
+      <c r="E70" s="37">
         <v>0.051</v>
       </c>
-      <c r="F70" s="11">
+      <c r="F70" s="14">
         <v>6</v>
       </c>
-      <c r="G70" s="35">
+      <c r="G70" s="38">
         <v>-0.3</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="36"/>
+      <c r="A72" s="39"/>
     </row>
     <row r="73" ht="20.4" spans="1:8">
-      <c r="A73" s="37" t="s">
+      <c r="A73" s="40" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="76" ht="20.4" spans="1:8">
-      <c r="A76" s="33" t="s">
+      <c r="A76" s="36" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="12" t="s">
+      <c r="A77" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C77" s="12" t="s">
+      <c r="C77" s="15" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="16" t="s">
         <v>270</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="16" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="16" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="16" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="16" t="s">
         <v>279</v>
       </c>
-      <c r="C81" s="13" t="s">
+      <c r="C81" s="16" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="16" t="s">
         <v>281</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="16" t="s">
         <v>282</v>
       </c>
-      <c r="C82" s="13" t="s">
+      <c r="C82" s="16" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="16" t="s">
         <v>284</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="16" t="s">
         <v>285</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="16" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="16" t="s">
         <v>288</v>
       </c>
-      <c r="C84" s="13" t="s">
+      <c r="C84" s="16" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="87" ht="37.8" spans="1:5">
-      <c r="A87" s="33" t="s">
+      <c r="A87" s="36" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="13" t="s">
         <v>291</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="C89" s="10" t="s">
+      <c r="C89" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="D89" s="10" t="s">
+      <c r="D89" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="E89" s="10" t="s">
+      <c r="E89" s="13" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="11">
+      <c r="A90" s="14">
         <v>1</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="14" t="s">
         <v>296</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="D90" s="11" t="s">
+      <c r="D90" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="E90" s="11" t="s">
+      <c r="E90" s="14" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="11">
+      <c r="A91" s="14">
         <v>2</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="D91" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="E91" s="11" t="s">
+      <c r="E91" s="14" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="11">
+      <c r="A92" s="14">
         <v>3</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="14" t="s">
         <v>302</v>
       </c>
-      <c r="E92" s="11" t="s">
+      <c r="E92" s="14" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="11">
+      <c r="A93" s="14">
         <v>4</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="E93" s="11" t="s">
+      <c r="E93" s="14" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="11">
+      <c r="A94" s="14">
         <v>5</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="E94" s="11" t="s">
+      <c r="E94" s="14" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="11">
+      <c r="A95" s="14">
         <v>6</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="D95" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="E95" s="11" t="s">
+      <c r="E95" s="14" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="11">
+      <c r="A96" s="14">
         <v>7</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="C96" s="11" t="s">
+      <c r="C96" s="14" t="s">
         <v>272</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="D96" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="E96" s="11" t="s">
+      <c r="E96" s="14" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="11">
+      <c r="A97" s="14">
         <v>8</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="14" t="s">
         <v>312</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D97" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="E97" s="11" t="s">
+      <c r="E97" s="14" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="11">
+      <c r="A98" s="14">
         <v>9</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C98" s="11" t="s">
+      <c r="C98" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="D98" s="11" t="s">
+      <c r="D98" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="E98" s="11" t="s">
+      <c r="E98" s="14" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="11">
+      <c r="A99" s="14">
         <v>10</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="14" t="s">
         <v>316</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C99" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="D99" s="11" t="s">
+      <c r="D99" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="E99" s="11" t="s">
+      <c r="E99" s="14" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="11">
+      <c r="A100" s="14">
         <v>11</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C100" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="D100" s="11" t="s">
+      <c r="D100" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="E100" s="11" t="s">
+      <c r="E100" s="14" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="11">
+      <c r="A101" s="14">
         <v>12</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C101" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="D101" s="11" t="s">
+      <c r="D101" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="E101" s="14" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="103" ht="20.4" spans="1:5">
-      <c r="A103" s="33" t="s">
+      <c r="A103" s="36" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="104" ht="19.2" spans="1:5">
-      <c r="A104" s="38" t="s">
+      <c r="A104" s="41" t="s">
         <v>325</v>
       </c>
-      <c r="B104" s="19"/>
+      <c r="B104" s="22"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="15" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="16" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" s="16" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="B108" s="13" t="s">
+      <c r="B108" s="16" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" s="16" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="13" t="s">
+      <c r="A110" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="16" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="13" t="s">
+      <c r="A111" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" s="16" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="B112" s="16" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="13" t="s">
+      <c r="A113" s="16" t="s">
         <v>341</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" s="16" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="13" t="s">
+      <c r="A114" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" s="16" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="13" t="s">
+      <c r="A115" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" s="16" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="13" t="s">
+      <c r="A116" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="B116" s="16" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="13" t="s">
+      <c r="A117" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="B117" s="13" t="s">
+      <c r="B117" s="16" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="119" ht="19.2" spans="1:2">
-      <c r="A119" s="39" t="s">
+      <c r="A119" s="42" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="40" t="s">
+      <c r="A121" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="B121" s="40" t="s">
+      <c r="B121" s="43" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="13" t="s">
+      <c r="A122" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B122" s="16" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="13" t="s">
+      <c r="A123" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="B123" s="16" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="13" t="s">
+      <c r="A124" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" s="16" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="16" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" s="16" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="13" t="s">
+      <c r="A127" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="B127" s="13" t="s">
+      <c r="B127" s="16" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="13" t="s">
+      <c r="A128" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="B128" s="13" t="s">
+      <c r="B128" s="16" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" s="16" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="131" ht="19.2" spans="1:2">
-      <c r="A131" s="39" t="s">
+      <c r="A131" s="42" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="40" t="s">
+      <c r="A133" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="B133" s="40" t="s">
+      <c r="B133" s="43" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="13" t="s">
+      <c r="A134" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="B134" s="13" t="s">
+      <c r="B134" s="16" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="13" t="s">
+      <c r="A135" s="16" t="s">
         <v>354</v>
       </c>
-      <c r="B135" s="13" t="s">
+      <c r="B135" s="16" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="13" t="s">
+      <c r="A136" s="16" t="s">
         <v>356</v>
       </c>
-      <c r="B136" s="13" t="s">
+      <c r="B136" s="16" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="13" t="s">
+      <c r="A137" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="B137" s="13" t="s">
+      <c r="B137" s="16" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="13" t="s">
+      <c r="A138" s="16" t="s">
         <v>343</v>
       </c>
-      <c r="B138" s="13" t="s">
+      <c r="B138" s="16" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="13" t="s">
+      <c r="A139" s="16" t="s">
         <v>345</v>
       </c>
-      <c r="B139" s="13" t="s">
+      <c r="B139" s="16" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="13" t="s">
+      <c r="A140" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="B140" s="13" t="s">
+      <c r="B140" s="16" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="13" t="s">
+      <c r="A141" s="16" t="s">
         <v>360</v>
       </c>
-      <c r="B141" s="13" t="s">
+      <c r="B141" s="16" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="143" ht="19.2" spans="1:2">
-      <c r="A143" s="39" t="s">
+      <c r="A143" s="42" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="40" t="s">
+      <c r="A145" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="B145" s="40" t="s">
+      <c r="B145" s="43" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="13" t="s">
+      <c r="A146" s="16" t="s">
         <v>352</v>
       </c>
-      <c r="B146" s="13" t="s">
+      <c r="B146" s="16" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="13" t="s">
+      <c r="A147" s="16" t="s">
         <v>364</v>
       </c>
-      <c r="B147" s="13" t="s">
+      <c r="B147" s="16" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="13" t="s">
+      <c r="A148" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="B148" s="13" t="s">
+      <c r="B148" s="16" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="13" t="s">
+      <c r="A149" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="B149" s="13" t="s">
+      <c r="B149" s="16" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="13" t="s">
+      <c r="A150" s="16" t="s">
         <v>370</v>
       </c>
-      <c r="B150" s="13" t="s">
+      <c r="B150" s="16" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="13" t="s">
+      <c r="A151" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="B151" s="13" t="s">
+      <c r="B151" s="16" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="13" t="s">
+      <c r="A152" s="16" t="s">
         <v>374</v>
       </c>
-      <c r="B152" s="13" t="s">
+      <c r="B152" s="16" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="154" ht="19.2" spans="1:2">
-      <c r="A154" s="39" t="s">
+      <c r="A154" s="42" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="40" t="s">
+      <c r="A156" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="B156" s="40" t="s">
+      <c r="B156" s="43" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="41" t="s">
+      <c r="A157" s="44" t="s">
         <v>329</v>
       </c>
-      <c r="B157" s="41" t="s">
+      <c r="B157" s="44" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="41" t="s">
+      <c r="A158" s="44" t="s">
         <v>377</v>
       </c>
-      <c r="B158" s="41" t="s">
+      <c r="B158" s="44" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="41" t="s">
+      <c r="A159" s="44" t="s">
         <v>379</v>
       </c>
-      <c r="B159" s="41" t="s">
+      <c r="B159" s="44" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="41" t="s">
+      <c r="A160" s="44" t="s">
         <v>381</v>
       </c>
-      <c r="B160" s="41" t="s">
+      <c r="B160" s="44" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="41" t="s">
+      <c r="A161" s="44" t="s">
         <v>383</v>
       </c>
-      <c r="B161" s="41" t="s">
+      <c r="B161" s="44" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="41" t="s">
+      <c r="A162" s="44" t="s">
         <v>385</v>
       </c>
-      <c r="B162" s="41" t="s">
+      <c r="B162" s="44" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="165" ht="19.2" spans="1:4">
-      <c r="A165" s="39" t="s">
+      <c r="A165" s="42" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="40" t="s">
+      <c r="A167" s="43" t="s">
         <v>326</v>
       </c>
-      <c r="B167" s="40" t="s">
+      <c r="B167" s="43" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="41" t="s">
+      <c r="A168" s="44" t="s">
         <v>352</v>
       </c>
-      <c r="B168" s="41" t="s">
+      <c r="B168" s="44" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="41" t="s">
+      <c r="A169" s="44" t="s">
         <v>388</v>
       </c>
-      <c r="B169" s="41" t="s">
+      <c r="B169" s="44" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="41" t="s">
+      <c r="A170" s="44" t="s">
         <v>390</v>
       </c>
-      <c r="B170" s="41" t="s">
+      <c r="B170" s="44" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="41" t="s">
+      <c r="A171" s="44" t="s">
         <v>392</v>
       </c>
-      <c r="B171" s="41" t="s">
+      <c r="B171" s="44" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="41" t="s">
+      <c r="A172" s="44" t="s">
         <v>394</v>
       </c>
-      <c r="B172" s="41" t="s">
+      <c r="B172" s="44" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="174" ht="20.4" spans="1:4">
-      <c r="A174" s="33" t="s">
+      <c r="A174" s="36" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="10" t="s">
+      <c r="A176" s="13" t="s">
         <v>397</v>
       </c>
-      <c r="B176" s="10" t="s">
+      <c r="B176" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="C176" s="10" t="s">
+      <c r="C176" s="13" t="s">
         <v>399</v>
       </c>
-      <c r="D176" s="10" t="s">
+      <c r="D176" s="13" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="42" t="s">
+      <c r="A177" s="45" t="s">
         <v>401</v>
       </c>
-      <c r="B177" s="11" t="s">
+      <c r="B177" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="C177" s="11" t="s">
+      <c r="C177" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="D177" s="11" t="s">
+      <c r="D177" s="14" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="43"/>
-      <c r="B178" s="11" t="s">
+      <c r="A178" s="46"/>
+      <c r="B178" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="11" t="s">
+      <c r="C178" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D178" s="11" t="s">
+      <c r="D178" s="14" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="44"/>
-      <c r="B179" s="11" t="s">
+      <c r="A179" s="47"/>
+      <c r="B179" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="C179" s="11" t="s">
+      <c r="C179" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="D179" s="11" t="s">
+      <c r="D179" s="14" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="42" t="s">
+      <c r="A180" s="45" t="s">
         <v>407</v>
       </c>
-      <c r="B180" s="11" t="s">
+      <c r="B180" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="C180" s="11" t="s">
+      <c r="C180" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="D180" s="11" t="s">
+      <c r="D180" s="14" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="43"/>
-      <c r="B181" s="11" t="s">
+      <c r="A181" s="46"/>
+      <c r="B181" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="C181" s="11" t="s">
+      <c r="C181" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="D181" s="11" t="s">
+      <c r="D181" s="14" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="43"/>
-      <c r="B182" s="11" t="s">
+      <c r="A182" s="46"/>
+      <c r="B182" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="C182" s="11" t="s">
+      <c r="C182" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="D182" s="11" t="s">
+      <c r="D182" s="14" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="44"/>
-      <c r="B183" s="11" t="s">
+      <c r="A183" s="47"/>
+      <c r="B183" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="C183" s="11" t="s">
+      <c r="C183" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="D183" s="11" t="s">
+      <c r="D183" s="14" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="184" ht="28.8" spans="1:4">
-      <c r="A184" s="42" t="s">
+      <c r="A184" s="45" t="s">
         <v>415</v>
       </c>
-      <c r="B184" s="11" t="s">
+      <c r="B184" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="C184" s="11" t="s">
+      <c r="C184" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="D184" s="11" t="s">
+      <c r="D184" s="14" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="43"/>
-      <c r="B185" s="11" t="s">
+      <c r="A185" s="46"/>
+      <c r="B185" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="C185" s="11" t="s">
+      <c r="C185" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="D185" s="11" t="s">
+      <c r="D185" s="14" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="44"/>
-      <c r="B186" s="11" t="s">
+      <c r="A186" s="47"/>
+      <c r="B186" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="C186" s="11" t="s">
+      <c r="C186" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="D186" s="11" t="s">
+      <c r="D186" s="14" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="42" t="s">
+      <c r="A187" s="45" t="s">
         <v>422</v>
       </c>
-      <c r="B187" s="11" t="s">
+      <c r="B187" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="C187" s="11" t="s">
+      <c r="C187" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="D187" s="11" t="s">
+      <c r="D187" s="14" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="43"/>
-      <c r="B188" s="11" t="s">
+      <c r="A188" s="46"/>
+      <c r="B188" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="C188" s="11" t="s">
+      <c r="C188" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="D188" s="11" t="s">
+      <c r="D188" s="14" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="44"/>
-      <c r="B189" s="11" t="s">
+      <c r="A189" s="47"/>
+      <c r="B189" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="C189" s="11" t="s">
+      <c r="C189" s="14" t="s">
         <v>428</v>
       </c>
-      <c r="D189" s="11" t="s">
+      <c r="D189" s="14" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="191" ht="20.4" spans="1:4">
-      <c r="A191" s="33" t="s">
+      <c r="A191" s="36" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="193" ht="43.2" spans="1:9">
-      <c r="A193" s="10" t="s">
+      <c r="A193" s="13" t="s">
         <v>255</v>
       </c>
-      <c r="B193" s="10" t="s">
+      <c r="B193" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="C193" s="10" t="s">
+      <c r="C193" s="13" t="s">
         <v>430</v>
       </c>
-      <c r="D193" s="10" t="s">
+      <c r="D193" s="13" t="s">
         <v>431</v>
       </c>
-      <c r="E193" s="10" t="s">
+      <c r="E193" s="13" t="s">
         <v>432</v>
       </c>
-      <c r="F193" s="10" t="s">
+      <c r="F193" s="13" t="s">
         <v>433</v>
       </c>
-      <c r="G193" s="10" t="s">
+      <c r="G193" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="H193" s="10" t="s">
+      <c r="H193" s="13" t="s">
         <v>435</v>
       </c>
-      <c r="I193" s="10" t="s">
+      <c r="I193" s="13" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194" s="11">
+      <c r="A194" s="14">
         <v>1</v>
       </c>
-      <c r="B194" s="11" t="s">
+      <c r="B194" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C194" s="11">
+      <c r="C194" s="14">
         <v>92</v>
       </c>
-      <c r="D194" s="11">
+      <c r="D194" s="14">
         <v>88</v>
       </c>
-      <c r="E194" s="11">
+      <c r="E194" s="14">
         <v>85</v>
       </c>
-      <c r="F194" s="11">
+      <c r="F194" s="14">
         <v>90</v>
       </c>
-      <c r="G194" s="11">
+      <c r="G194" s="14">
         <v>87</v>
       </c>
-      <c r="H194" s="11">
+      <c r="H194" s="14">
         <v>89</v>
       </c>
-      <c r="I194" s="11" t="s">
+      <c r="I194" s="14" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="195" spans="1:9">
-      <c r="A195" s="11">
+      <c r="A195" s="14">
         <v>2</v>
       </c>
-      <c r="B195" s="11" t="s">
+      <c r="B195" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="C195" s="11">
+      <c r="C195" s="14">
         <v>90</v>
       </c>
-      <c r="D195" s="11">
+      <c r="D195" s="14">
         <v>91</v>
       </c>
-      <c r="E195" s="11">
+      <c r="E195" s="14">
         <v>82</v>
       </c>
-      <c r="F195" s="11">
+      <c r="F195" s="14">
         <v>86</v>
       </c>
-      <c r="G195" s="11">
+      <c r="G195" s="14">
         <v>85</v>
       </c>
-      <c r="H195" s="11">
+      <c r="H195" s="14">
         <v>88.1</v>
       </c>
-      <c r="I195" s="11" t="s">
+      <c r="I195" s="14" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="196" spans="1:9">
-      <c r="A196" s="11">
+      <c r="A196" s="14">
         <v>3</v>
       </c>
-      <c r="B196" s="11" t="s">
+      <c r="B196" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C196" s="11">
+      <c r="C196" s="14">
         <v>75</v>
       </c>
-      <c r="D196" s="11">
+      <c r="D196" s="14">
         <v>70</v>
       </c>
-      <c r="E196" s="11">
+      <c r="E196" s="14">
         <v>60</v>
       </c>
-      <c r="F196" s="11">
+      <c r="F196" s="14">
         <v>80</v>
       </c>
-      <c r="G196" s="11">
+      <c r="G196" s="14">
         <v>65</v>
       </c>
-      <c r="H196" s="11">
+      <c r="H196" s="14">
         <v>72</v>
       </c>
-      <c r="I196" s="11" t="s">
+      <c r="I196" s="14" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="197" spans="1:9">
-      <c r="A197" s="11">
+      <c r="A197" s="14">
         <v>4</v>
       </c>
-      <c r="B197" s="11" t="s">
+      <c r="B197" s="14" t="s">
         <v>436</v>
       </c>
-      <c r="C197" s="11">
+      <c r="C197" s="14">
         <v>40</v>
       </c>
-      <c r="D197" s="11">
+      <c r="D197" s="14">
         <v>35</v>
       </c>
-      <c r="E197" s="11">
+      <c r="E197" s="14">
         <v>20</v>
       </c>
-      <c r="F197" s="11">
+      <c r="F197" s="14">
         <v>50</v>
       </c>
-      <c r="G197" s="11">
+      <c r="G197" s="14">
         <v>30</v>
       </c>
-      <c r="H197" s="11">
+      <c r="H197" s="14">
         <v>36.5</v>
       </c>
-      <c r="I197" s="11" t="s">
+      <c r="I197" s="14" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="200" ht="20.4" spans="1:9">
-      <c r="A200" s="33" t="s">
+      <c r="A200" s="36" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="202" ht="15.6" spans="1:9">
-      <c r="A202" s="38" t="s">
+      <c r="A202" s="41" t="s">
         <v>438</v>
       </c>
-      <c r="B202" s="19"/>
+      <c r="B202" s="22"/>
     </row>
     <row r="203" spans="1:9">
-      <c r="A203" s="12" t="s">
+      <c r="A203" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B203" s="12" t="s">
+      <c r="B203" s="15" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:9">
-      <c r="A204" s="13" t="s">
+      <c r="A204" s="16" t="s">
         <v>298</v>
       </c>
-      <c r="B204" s="13" t="s">
+      <c r="B204" s="16" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="205" spans="1:9">
-      <c r="A205" s="13" t="s">
+      <c r="A205" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="B205" s="13" t="s">
+      <c r="B205" s="16" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="206" spans="1:9">
-      <c r="A206" s="13" t="s">
+      <c r="A206" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="B206" s="13" t="s">
+      <c r="B206" s="16" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="208" ht="15.6" spans="1:9">
-      <c r="A208" s="38" t="s">
+      <c r="A208" s="41" t="s">
         <v>442</v>
       </c>
-      <c r="B208" s="19"/>
-      <c r="C208" s="19"/>
+      <c r="B208" s="22"/>
+      <c r="C208" s="22"/>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="12" t="s">
+      <c r="A209" s="15" t="s">
         <v>443</v>
       </c>
-      <c r="B209" s="12" t="s">
+      <c r="B209" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="C209" s="12" t="s">
+      <c r="C209" s="15" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="13" t="s">
+      <c r="A210" s="16" t="s">
         <v>446</v>
       </c>
-      <c r="B210" s="13" t="s">
+      <c r="B210" s="16" t="s">
         <v>447</v>
       </c>
-      <c r="C210" s="13" t="s">
+      <c r="C210" s="16" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="13" t="s">
+      <c r="A211" s="16" t="s">
         <v>449</v>
       </c>
-      <c r="B211" s="13" t="s">
+      <c r="B211" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="C211" s="13" t="s">
+      <c r="C211" s="16" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="13" t="s">
+      <c r="A212" s="16" t="s">
         <v>452</v>
       </c>
-      <c r="B212" s="13" t="s">
+      <c r="B212" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="C212" s="13" t="s">
+      <c r="C212" s="16" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="13" t="s">
+      <c r="A213" s="16" t="s">
         <v>455</v>
       </c>
-      <c r="B213" s="13" t="s">
+      <c r="B213" s="16" t="s">
         <v>456</v>
       </c>
-      <c r="C213" s="13" t="s">
+      <c r="C213" s="16" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="13" t="s">
+      <c r="A214" s="16" t="s">
         <v>458</v>
       </c>
-      <c r="B214" s="13" t="s">
+      <c r="B214" s="16" t="s">
         <v>459</v>
       </c>
-      <c r="C214" s="13" t="s">
+      <c r="C214" s="16" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="13" t="s">
+      <c r="A215" s="16" t="s">
         <v>461</v>
       </c>
-      <c r="B215" s="13" t="s">
+      <c r="B215" s="16" t="s">
         <v>462</v>
       </c>
-      <c r="C215" s="13" t="s">
+      <c r="C215" s="16" t="s">
         <v>463</v>
       </c>
     </row>
@@ -6590,22 +6996,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="22" t="s">
         <v>464</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="22" t="s">
         <v>465</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="22" t="s">
         <v>466</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="22" t="s">
         <v>467</v>
       </c>
     </row>
@@ -6627,285 +7033,285 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>468</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="8"/>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="9" t="s">
         <v>469</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="9" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="10" t="s">
         <v>471</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="10" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="10" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="10" t="s">
         <v>475</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="10" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="10" t="s">
         <v>477</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="10" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="10" t="s">
         <v>479</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="10" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="11" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="11" ht="20.4" spans="1:3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="12" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="13" t="s">
         <v>483</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="13" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="14" t="s">
         <v>485</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="14" t="s">
         <v>486</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="14" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="14" t="s">
         <v>488</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="14" t="s">
         <v>489</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="14" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="14" t="s">
         <v>491</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="14" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="14" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="14" t="s">
         <v>494</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="14" t="s">
         <v>495</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="14" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="19" ht="20.4" spans="1:3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="12" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="15" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="16" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="16" t="s">
         <v>500</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="16" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="24" ht="28.8" spans="1:3">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="16" t="s">
         <v>502</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="16" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="16" t="s">
         <v>504</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="16" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="27" ht="20.4" spans="1:3">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="12" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="13" t="s">
         <v>326</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="13" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="14" t="s">
         <v>507</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="14" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="14" t="s">
         <v>509</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="14" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="14" t="s">
         <v>511</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="14" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="14" t="s">
         <v>513</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="14" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="35" ht="20.4" spans="1:2">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="12" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="12" t="s">
+      <c r="A37" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="15" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="16" t="s">
         <v>516</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="16" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="16" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="16" t="s">
         <v>520</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="16" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="43" ht="20.4" spans="1:2">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="12" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="12" t="s">
+      <c r="A45" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="B45" s="12" t="s">
+      <c r="B45" s="15" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="16" t="s">
         <v>524</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="16" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="16" t="s">
         <v>526</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="16" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="16" t="s">
         <v>528</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="16" t="s">
         <v>529</v>
       </c>
     </row>
@@ -6915,148 +7321,148 @@
       </c>
     </row>
     <row r="53" ht="16.8" spans="1:2">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="17" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="56" ht="27" spans="1:2">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="11" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="15" t="s">
         <v>533</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="15" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="16" t="s">
         <v>535</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="16" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="13"/>
-      <c r="B60" s="13" t="s">
+      <c r="A60" s="16"/>
+      <c r="B60" s="16" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="13"/>
-      <c r="B61" s="13" t="s">
+      <c r="A61" s="16"/>
+      <c r="B61" s="16" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="13"/>
-      <c r="B62" s="13" t="s">
+      <c r="A62" s="16"/>
+      <c r="B62" s="16" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="13"/>
-      <c r="B63" s="13" t="s">
+      <c r="A63" s="16"/>
+      <c r="B63" s="16" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="16" t="s">
         <v>541</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="16" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="13"/>
-      <c r="B65" s="13" t="s">
+      <c r="A65" s="16"/>
+      <c r="B65" s="16" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="13"/>
-      <c r="B66" s="13" t="s">
+      <c r="A66" s="16"/>
+      <c r="B66" s="16" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="13"/>
-      <c r="B67" s="13" t="s">
+      <c r="A67" s="16"/>
+      <c r="B67" s="16" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="70" ht="22.2" spans="1:2">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="18" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="72" ht="15.6" spans="1:2">
-      <c r="A72" s="16" t="s">
+      <c r="A72" s="19" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="74" ht="19.2" spans="1:2">
-      <c r="A74" s="17" t="s">
+      <c r="A74" s="20" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="75" ht="19.2" spans="1:2">
-      <c r="A75" s="17" t="s">
+      <c r="A75" s="20" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="76" ht="15.6" spans="1:2">
-      <c r="A76" s="17" t="s">
+      <c r="A76" s="20" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="18" t="s">
+      <c r="A80" s="21" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="13" t="s">
         <v>552</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="13" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="14" t="s">
         <v>554</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="14" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="14" t="s">
         <v>556</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="14" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="14" t="s">
         <v>558</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="14" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="14" t="s">
         <v>560</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="14" t="s">
         <v>561</v>
       </c>
     </row>
@@ -7073,35 +7479,899 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:A9"/>
+  <dimension ref="B2:J63"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="3" width="32.1111111111111" customWidth="1"/>
+    <col min="4" max="4" width="20.8888888888889" customWidth="1"/>
+    <col min="5" max="5" width="50.1111111111111" customWidth="1"/>
+    <col min="6" max="6" width="11.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="14.1111111111111" customWidth="1"/>
+    <col min="8" max="8" width="37.7777777777778" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
+    <row r="2" spans="2:10">
+      <c r="B2" s="3" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>564</v>
       </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>565</v>
       </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>566</v>
       </c>
+      <c r="G2" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="4"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="4"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="4"/>
+      <c r="C21" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26" s="4"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" s="4"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28" s="4"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="4"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="4"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="4"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="4"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" ht="19.2" spans="2:10">
+      <c r="B34" s="4"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" ht="19.2" spans="2:10">
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="4"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37" s="4"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38" s="4"/>
+      <c r="C38" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+    </row>
+    <row r="39" ht="19.2" spans="2:10">
+      <c r="B39" s="4"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="4"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="4"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="4"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="4"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" ht="19.2" spans="2:10">
+      <c r="B44" s="4"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+    </row>
+    <row r="45" ht="19.2" spans="2:10">
+      <c r="B45" s="4"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="4"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="4"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" ht="19.2" spans="2:10">
+      <c r="B48" s="4"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" ht="15.6" spans="2:10">
+      <c r="B49" s="4"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" ht="19.2" spans="2:10">
+      <c r="B50" s="4"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" ht="19.2" spans="2:10">
+      <c r="B51" s="4"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" ht="19.2" spans="2:10">
+      <c r="B52" s="4"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+    </row>
+    <row r="53" ht="19.2" spans="2:10">
+      <c r="B53" s="4"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" ht="19.2" spans="2:10">
+      <c r="B54" s="4"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" ht="19.2" spans="2:10">
+      <c r="B55" s="4"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="4"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="4"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" ht="15.6" spans="2:10">
+      <c r="B58" s="4"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+    </row>
+    <row r="59" ht="15.6" spans="2:10">
+      <c r="B59" s="4"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
+      <c r="J59" s="3"/>
+    </row>
+    <row r="60" ht="15.6" spans="2:10">
+      <c r="B60" s="4"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
+      <c r="J60" s="3"/>
+    </row>
+    <row r="61" ht="19.2" spans="2:10">
+      <c r="B61" s="4"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+    </row>
+    <row r="62" spans="2:10">
+      <c r="B62" s="4"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+    </row>
+    <row r="63" spans="2:10">
+      <c r="B63" s="4"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B3:B63"/>
+    <mergeCell ref="C3:C20"/>
+    <mergeCell ref="C21:C37"/>
+    <mergeCell ref="C38:C63"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="D10:D14"/>
+    <mergeCell ref="D15:D18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D23"/>
+    <mergeCell ref="D24:D27"/>
+    <mergeCell ref="D28:D33"/>
+    <mergeCell ref="D34:D37"/>
+    <mergeCell ref="D38:D43"/>
+    <mergeCell ref="D44:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="D53:D57"/>
+    <mergeCell ref="D58:D63"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -7115,117 +8385,117 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>567</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>568</v>
+        <v>652</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>569</v>
+        <v>653</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>570</v>
+        <v>654</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>571</v>
+        <v>655</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>572</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>573</v>
+        <v>657</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>574</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>575</v>
+        <v>659</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>576</v>
+        <v>660</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>577</v>
+        <v>661</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>578</v>
+        <v>662</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>579</v>
+        <v>663</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>580</v>
+        <v>664</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>581</v>
+        <v>665</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>582</v>
+        <v>666</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>583</v>
+        <v>667</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>584</v>
+        <v>668</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>585</v>
+        <v>669</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>586</v>
+        <v>670</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>587</v>
+        <v>671</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>588</v>
+        <v>672</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>589</v>
+        <v>673</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -7235,12 +8505,12 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>590</v>
+        <v>674</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>591</v>
+        <v>675</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -7256,7 +8526,7 @@
         <v>332</v>
       </c>
       <c r="B37" t="s">
-        <v>592</v>
+        <v>676</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -7264,7 +8534,7 @@
         <v>342</v>
       </c>
       <c r="B38" t="s">
-        <v>593</v>
+        <v>677</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -7272,7 +8542,7 @@
         <v>344</v>
       </c>
       <c r="B39" t="s">
-        <v>594</v>
+        <v>678</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -7280,7 +8550,7 @@
         <v>346</v>
       </c>
       <c r="B40" t="s">
-        <v>595</v>
+        <v>679</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -7288,59 +8558,59 @@
         <v>340</v>
       </c>
       <c r="B41" t="s">
-        <v>596</v>
+        <v>680</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>597</v>
+        <v>681</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>598</v>
+        <v>682</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>599</v>
+        <v>683</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>600</v>
+        <v>684</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>601</v>
+        <v>685</v>
       </c>
       <c r="B48" t="s">
-        <v>602</v>
+        <v>686</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>603</v>
+        <v>687</v>
       </c>
       <c r="B49" t="s">
-        <v>604</v>
+        <v>688</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>605</v>
+        <v>689</v>
       </c>
       <c r="B50" t="s">
-        <v>606</v>
+        <v>690</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>607</v>
+        <v>691</v>
       </c>
       <c r="B51" t="s">
-        <v>608</v>
+        <v>692</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -7348,123 +8618,123 @@
         <v>46056</v>
       </c>
       <c r="B52" t="s">
-        <v>609</v>
+        <v>693</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>610</v>
+        <v>694</v>
       </c>
       <c r="B53" t="s">
-        <v>611</v>
+        <v>695</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>612</v>
+        <v>696</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>613</v>
+        <v>697</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>614</v>
+        <v>698</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>615</v>
+        <v>699</v>
       </c>
       <c r="B59" t="s">
         <v>342</v>
       </c>
       <c r="C59" t="s">
-        <v>616</v>
+        <v>700</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>617</v>
+        <v>701</v>
       </c>
       <c r="B60" t="s">
-        <v>617</v>
+        <v>701</v>
       </c>
       <c r="C60" t="s">
-        <v>618</v>
+        <v>702</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>617</v>
+        <v>701</v>
       </c>
       <c r="B61" t="s">
-        <v>619</v>
+        <v>703</v>
       </c>
       <c r="C61" t="s">
-        <v>620</v>
+        <v>704</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>619</v>
+        <v>703</v>
       </c>
       <c r="B62" t="s">
-        <v>617</v>
+        <v>701</v>
       </c>
       <c r="C62" t="s">
-        <v>621</v>
+        <v>705</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>619</v>
+        <v>703</v>
       </c>
       <c r="B63" t="s">
-        <v>619</v>
+        <v>703</v>
       </c>
       <c r="C63" t="s">
-        <v>622</v>
+        <v>706</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>623</v>
+        <v>707</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>624</v>
+        <v>708</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>625</v>
+        <v>709</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>626</v>
+        <v>710</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>627</v>
+        <v>711</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>628</v>
+        <v>712</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>629</v>
+        <v>713</v>
       </c>
       <c r="B72" t="s">
-        <v>602</v>
+        <v>686</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -7472,7 +8742,7 @@
         <v>46024</v>
       </c>
       <c r="B73" t="s">
-        <v>630</v>
+        <v>714</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -7480,7 +8750,7 @@
         <v>46086</v>
       </c>
       <c r="B74" t="s">
-        <v>631</v>
+        <v>715</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -7488,30 +8758,30 @@
         <v>46183</v>
       </c>
       <c r="B75" t="s">
-        <v>632</v>
+        <v>716</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>633</v>
+        <v>717</v>
       </c>
       <c r="B76" t="s">
-        <v>634</v>
+        <v>718</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>635</v>
+        <v>719</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>636</v>
+        <v>720</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>637</v>
+        <v>721</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -7522,17 +8792,17 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>638</v>
+        <v>722</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>639</v>
+        <v>723</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>640</v>
+        <v>724</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -7545,26 +8815,26 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>641</v>
+        <v>725</v>
       </c>
       <c r="B91" t="s">
-        <v>642</v>
+        <v>726</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>643</v>
+        <v>727</v>
       </c>
       <c r="B92" t="s">
-        <v>644</v>
+        <v>728</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>645</v>
+        <v>729</v>
       </c>
       <c r="B93" t="s">
-        <v>646</v>
+        <v>730</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -7572,30 +8842,30 @@
         <v>213</v>
       </c>
       <c r="B94" t="s">
-        <v>647</v>
+        <v>731</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>648</v>
+        <v>732</v>
       </c>
       <c r="B95" t="s">
-        <v>649</v>
+        <v>733</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>650</v>
+        <v>734</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>651</v>
+        <v>735</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>652</v>
+        <v>736</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -7603,12 +8873,12 @@
         <v>155</v>
       </c>
       <c r="B101" t="s">
-        <v>653</v>
+        <v>737</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>654</v>
+        <v>738</v>
       </c>
       <c r="B102" s="2">
         <v>0.3</v>
@@ -7616,7 +8886,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>655</v>
+        <v>739</v>
       </c>
       <c r="B103" s="2">
         <v>0.25</v>
@@ -7624,7 +8894,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>656</v>
+        <v>740</v>
       </c>
       <c r="B104" s="2">
         <v>0.15</v>
@@ -7640,7 +8910,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>657</v>
+        <v>741</v>
       </c>
       <c r="B106" s="2">
         <v>0.15</v>
@@ -7648,70 +8918,70 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>658</v>
+        <v>742</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>659</v>
+        <v>743</v>
       </c>
       <c r="B108" t="s">
-        <v>660</v>
+        <v>744</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>661</v>
+        <v>745</v>
       </c>
       <c r="B109" t="s">
-        <v>662</v>
+        <v>746</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>663</v>
+        <v>747</v>
       </c>
       <c r="B110" t="s">
-        <v>664</v>
+        <v>748</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>665</v>
+        <v>749</v>
       </c>
       <c r="B111" t="s">
-        <v>666</v>
+        <v>750</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>667</v>
+        <v>751</v>
       </c>
       <c r="B112" t="s">
-        <v>668</v>
+        <v>752</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>669</v>
+        <v>753</v>
       </c>
       <c r="B113" t="s">
-        <v>670</v>
+        <v>754</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>671</v>
+        <v>755</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>672</v>
+        <v>756</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>673</v>
+        <v>757</v>
       </c>
       <c r="B118" t="s">
         <v>294</v>
@@ -7719,70 +8989,70 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>674</v>
+        <v>758</v>
       </c>
       <c r="B119" t="s">
-        <v>675</v>
+        <v>759</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>676</v>
+        <v>760</v>
       </c>
       <c r="B120" t="s">
-        <v>677</v>
+        <v>761</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>678</v>
+        <v>762</v>
       </c>
       <c r="B121" t="s">
-        <v>679</v>
+        <v>763</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>680</v>
+        <v>764</v>
       </c>
       <c r="B122" t="s">
-        <v>681</v>
+        <v>765</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>682</v>
+        <v>766</v>
       </c>
       <c r="B123" t="s">
-        <v>683</v>
+        <v>767</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>684</v>
+        <v>768</v>
       </c>
       <c r="B124" t="s">
-        <v>685</v>
+        <v>769</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>686</v>
+        <v>770</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>687</v>
+        <v>771</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>688</v>
+        <v>772</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>689</v>
+        <v>773</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -7829,12 +9099,12 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>690</v>
+        <v>774</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>691</v>
+        <v>775</v>
       </c>
     </row>
     <row r="140" spans="1:1">
@@ -7881,12 +9151,12 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>692</v>
+        <v>776</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>693</v>
+        <v>777</v>
       </c>
     </row>
     <row r="149" spans="1:1">
@@ -7921,192 +9191,192 @@
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>694</v>
+        <v>778</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>695</v>
+        <v>779</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>696</v>
+        <v>780</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>697</v>
+        <v>781</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>698</v>
+        <v>782</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>699</v>
+        <v>783</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>700</v>
+        <v>784</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>701</v>
+        <v>785</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>702</v>
+        <v>786</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>703</v>
+        <v>787</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>704</v>
+        <v>788</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>705</v>
+        <v>789</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>706</v>
+        <v>790</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>707</v>
+        <v>791</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>708</v>
+        <v>792</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>709</v>
+        <v>793</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>710</v>
+        <v>794</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>711</v>
+        <v>795</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>712</v>
+        <v>796</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>713</v>
+        <v>797</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>714</v>
+        <v>798</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>715</v>
+        <v>799</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>716</v>
+        <v>800</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>717</v>
+        <v>801</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>718</v>
+        <v>802</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>719</v>
+        <v>803</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>720</v>
+        <v>804</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>721</v>
+        <v>805</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>643</v>
+        <v>727</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>722</v>
+        <v>806</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>723</v>
+        <v>807</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>724</v>
+        <v>808</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>725</v>
+        <v>809</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>726</v>
+        <v>810</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>727</v>
+        <v>811</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>728</v>
+        <v>812</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>729</v>
+        <v>813</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>730</v>
+        <v>814</v>
       </c>
     </row>
     <row r="196" spans="1:1">
@@ -8116,117 +9386,117 @@
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>731</v>
+        <v>815</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>732</v>
+        <v>816</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>733</v>
+        <v>817</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>734</v>
+        <v>818</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>735</v>
+        <v>819</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>736</v>
+        <v>820</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>737</v>
+        <v>821</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>738</v>
+        <v>822</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>739</v>
+        <v>823</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>740</v>
+        <v>824</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>741</v>
+        <v>825</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>742</v>
+        <v>826</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>743</v>
+        <v>827</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>744</v>
+        <v>828</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>745</v>
+        <v>829</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>746</v>
+        <v>830</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>747</v>
+        <v>831</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>748</v>
+        <v>832</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>749</v>
+        <v>833</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>750</v>
+        <v>834</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>751</v>
+        <v>835</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>752</v>
+        <v>836</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>753</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>

--- a/需求整理/industry_indicator_system.xlsx
+++ b/需求整理/industry_indicator_system.xlsx
@@ -2247,6 +2247,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>云计算</t>
     </r>
     <r>
@@ -2261,6 +2268,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>SaaS（软件即服务）</t>
     </r>
     <r>
@@ -2290,6 +2304,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI PC</t>
     </r>
     <r>
@@ -2319,6 +2340,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>L2+/L3智能驾驶</t>
     </r>
     <r>
@@ -2333,6 +2361,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>Robotaxi（自动驾驶出租车）</t>
     </r>
     <r>
@@ -2356,6 +2391,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>人形机器人</t>
     </r>
     <r>
@@ -2370,6 +2412,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>具身智能</t>
     </r>
     <r>
@@ -2387,6 +2436,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>企业级AI Agent</t>
     </r>
     <r>
@@ -2401,6 +2457,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI办公</t>
     </r>
     <r>
@@ -2415,6 +2478,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI编程</t>
     </r>
     <r>
@@ -2432,6 +2502,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI搜索引擎</t>
     </r>
     <r>
@@ -2446,6 +2523,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI综合助手</t>
     </r>
     <r>
@@ -2460,6 +2544,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI创作</t>
     </r>
     <r>
@@ -2483,6 +2574,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI+工业制造</t>
     </r>
     <r>
@@ -2497,6 +2595,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI+医疗健康</t>
     </r>
     <r>
@@ -2511,6 +2616,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI+金融</t>
     </r>
     <r>
@@ -2525,6 +2637,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>AI+教育</t>
     </r>
     <r>
@@ -3329,16 +3448,16 @@
     </font>
     <font>
       <b/>
-      <sz val="10.5"/>
+      <sz val="12"/>
       <color rgb="FF060A26"/>
-      <name val="Consolas"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10.5"/>
       <color rgb="FF060A26"/>
-      <name val="宋体"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -3860,7 +3979,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3909,7 +4028,6 @@
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3933,9 +4051,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4371,253 +4486,253 @@
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="6" ht="72" spans="1:6">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="3" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="3" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="15" ht="100.8" spans="1:6">
-      <c r="A15" s="44" t="s">
+      <c r="A15" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="44" t="s">
+      <c r="C15" s="42" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4642,41 +4757,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="48" t="s">
+      <c r="D1" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="48" t="s">
+      <c r="E1" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="48" t="s">
+      <c r="F1" s="46" t="s">
         <v>73</v>
       </c>
       <c r="G1" s="10"/>
     </row>
     <row r="2" ht="115.2" spans="1:7">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="47" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="47" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="D2" s="47" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49" t="s">
+      <c r="E2" s="47"/>
+      <c r="F2" s="47" t="s">
         <v>78</v>
       </c>
       <c r="G2" s="10" t="s">
@@ -4684,16 +4799,16 @@
       </c>
     </row>
     <row r="3" ht="273.6" spans="1:7">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="49" t="s">
+      <c r="A3" s="47"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="49" t="s">
+      <c r="F3" s="47" t="s">
         <v>82</v>
       </c>
       <c r="G3" s="10" t="s">
@@ -4701,14 +4816,14 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="49"/>
-      <c r="B4" s="49"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="49" t="s">
+      <c r="A4" s="47"/>
+      <c r="B4" s="47"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49" t="s">
+      <c r="E4" s="47"/>
+      <c r="F4" s="47" t="s">
         <v>85</v>
       </c>
       <c r="G4" s="10" t="s">
@@ -4716,398 +4831,398 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="49"/>
-      <c r="B5" s="49"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="49" t="s">
+      <c r="A5" s="47"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="49"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
       <c r="G5" s="10"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="49"/>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="49" t="s">
+      <c r="A6" s="47"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="10"/>
     </row>
     <row r="7" ht="72" spans="1:7">
-      <c r="A7" s="49"/>
-      <c r="B7" s="49"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="49" t="s">
+      <c r="A7" s="47"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="49"/>
+      <c r="F7" s="47"/>
       <c r="G7" s="10"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="49"/>
-      <c r="B8" s="49" t="s">
+      <c r="A8" s="47"/>
+      <c r="B8" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
+      <c r="E8" s="47"/>
+      <c r="F8" s="47"/>
       <c r="G8" s="10"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="49"/>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49" t="s">
+      <c r="A9" s="47"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
+      <c r="E9" s="47"/>
+      <c r="F9" s="47"/>
       <c r="G9" s="10"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="49"/>
-      <c r="B10" s="49"/>
-      <c r="C10" s="49"/>
-      <c r="D10" s="49" t="s">
+      <c r="A10" s="47"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="49"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
       <c r="G10" s="10"/>
     </row>
     <row r="11" ht="57.6" spans="1:7">
-      <c r="A11" s="49"/>
-      <c r="B11" s="49"/>
-      <c r="C11" s="49"/>
-      <c r="D11" s="49" t="s">
+      <c r="A11" s="47"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="49" t="s">
+      <c r="E11" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="49"/>
+      <c r="F11" s="47"/>
       <c r="G11" s="10"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="49"/>
-      <c r="B12" s="49" t="s">
+      <c r="A12" s="47"/>
+      <c r="B12" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="49" t="s">
+      <c r="C12" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
       <c r="G12" s="10"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="49"/>
-      <c r="B13" s="49"/>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49" t="s">
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="49"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
       <c r="G13" s="10"/>
     </row>
     <row r="14" ht="43.2" spans="1:7">
-      <c r="A14" s="49"/>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49" t="s">
+      <c r="A14" s="47"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="49" t="s">
+      <c r="E14" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="49"/>
+      <c r="F14" s="47"/>
       <c r="G14" s="10"/>
     </row>
     <row r="15" ht="57.6" spans="1:7">
-      <c r="A15" s="49"/>
-      <c r="B15" s="49" t="s">
+      <c r="A15" s="47"/>
+      <c r="B15" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="51" t="s">
+      <c r="C15" s="47"/>
+      <c r="D15" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="49" t="s">
+      <c r="E15" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="49"/>
+      <c r="F15" s="47"/>
       <c r="G15" s="10"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="49" t="s">
+      <c r="A16" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="49" t="s">
+      <c r="B16" s="47" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="49" t="s">
+      <c r="C16" s="47" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="49" t="s">
+      <c r="E16" s="47" t="s">
         <v>110</v>
       </c>
-      <c r="F16" s="49"/>
+      <c r="F16" s="47"/>
       <c r="G16" s="10"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="49"/>
-      <c r="B17" s="49"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49" t="s">
+      <c r="A17" s="47"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="49" t="s">
+      <c r="E17" s="47" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="49"/>
+      <c r="F17" s="47"/>
       <c r="G17" s="10"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="49"/>
-      <c r="B18" s="49" t="s">
+      <c r="A18" s="47"/>
+      <c r="B18" s="47" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="47" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="51" t="s">
+      <c r="D18" s="49" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="51"/>
-      <c r="F18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="47"/>
       <c r="G18" s="10"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49" t="s">
+      <c r="A19" s="47"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
       <c r="G19" s="10"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="49"/>
-      <c r="B20" s="49" t="s">
+      <c r="A20" s="47"/>
+      <c r="B20" s="47" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="49" t="s">
+      <c r="D20" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="49" t="s">
+      <c r="E20" s="47" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="49"/>
+      <c r="F20" s="47"/>
       <c r="G20" s="10"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="49"/>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49" t="s">
+      <c r="A21" s="47"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="47"/>
+      <c r="D21" s="47" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="49" t="s">
+      <c r="E21" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="49"/>
+      <c r="F21" s="47"/>
       <c r="G21" s="10"/>
     </row>
     <row r="22" ht="72" spans="1:7">
-      <c r="A22" s="49"/>
-      <c r="B22" s="49" t="s">
+      <c r="A22" s="47"/>
+      <c r="B22" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49" t="s">
+      <c r="D22" s="47"/>
+      <c r="E22" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="49"/>
+      <c r="F22" s="47"/>
       <c r="G22" s="10"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="49" t="s">
+      <c r="A23" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="49" t="s">
+      <c r="B23" s="47" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="47" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="47" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="49"/>
-      <c r="F23" s="49"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
       <c r="G23" s="10"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="49"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49" t="s">
+      <c r="A24" s="47"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="47" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="49"/>
-      <c r="F24" s="49"/>
+      <c r="E24" s="47"/>
+      <c r="F24" s="47"/>
       <c r="G24" s="10"/>
     </row>
     <row r="25" ht="43.2" spans="1:7">
-      <c r="A25" s="49"/>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50" t="s">
+      <c r="A25" s="47"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="48" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49" t="s">
+      <c r="D25" s="47"/>
+      <c r="E25" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="50"/>
+      <c r="F25" s="48"/>
       <c r="G25" s="10"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="49"/>
-      <c r="B26" s="49" t="s">
+      <c r="A26" s="47"/>
+      <c r="B26" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="49" t="s">
+      <c r="C26" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49"/>
-      <c r="F26" s="49"/>
+      <c r="D26" s="47"/>
+      <c r="E26" s="47"/>
+      <c r="F26" s="47"/>
       <c r="G26" s="10"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="49"/>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49" t="s">
+      <c r="A27" s="47"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="49"/>
-      <c r="F27" s="49"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
       <c r="G27" s="10"/>
     </row>
     <row r="28" ht="43.2" spans="1:7">
-      <c r="A28" s="49"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="50" t="s">
+      <c r="A28" s="47"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="48" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49" t="s">
+      <c r="D28" s="47"/>
+      <c r="E28" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="49"/>
+      <c r="F28" s="47"/>
       <c r="G28" s="10"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="49"/>
-      <c r="B29" s="49" t="s">
+      <c r="A29" s="47"/>
+      <c r="B29" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="49" t="s">
+      <c r="D29" s="47" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="50"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48"/>
       <c r="G29" s="10"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="49"/>
-      <c r="B30" s="49"/>
-      <c r="C30" s="50" t="s">
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
+      <c r="C30" s="48" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="47" t="s">
         <v>143</v>
       </c>
-      <c r="E30" s="49"/>
-      <c r="F30" s="50"/>
+      <c r="E30" s="47"/>
+      <c r="F30" s="48"/>
       <c r="G30" s="10"/>
     </row>
     <row r="31" ht="43.2" spans="1:7">
-      <c r="A31" s="49"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="50" t="s">
+      <c r="A31" s="47"/>
+      <c r="B31" s="47"/>
+      <c r="C31" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="49" t="s">
+      <c r="D31" s="49"/>
+      <c r="E31" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="50"/>
+      <c r="F31" s="48"/>
       <c r="G31" s="10"/>
     </row>
     <row r="32" ht="57.6" spans="1:7">
-      <c r="A32" s="49"/>
-      <c r="B32" s="50" t="s">
+      <c r="A32" s="47"/>
+      <c r="B32" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="50" t="s">
+      <c r="C32" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="49" t="s">
+      <c r="D32" s="49"/>
+      <c r="E32" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="F32" s="50"/>
+      <c r="F32" s="48"/>
       <c r="G32" s="10"/>
     </row>
     <row r="33" ht="158.4" spans="1:7">
-      <c r="A33" s="51" t="s">
+      <c r="A33" s="49" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="32" t="s">
+      <c r="B33" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="32" t="s">
+      <c r="C33" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="32" t="s">
+      <c r="D33" s="31" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="51"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="49"/>
       <c r="G33" s="10"/>
     </row>
   </sheetData>
@@ -5149,17 +5264,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" ht="20.4" spans="1:4">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="15" t="s">
@@ -5182,7 +5297,7 @@
       <c r="B4" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="24">
         <v>0.35</v>
       </c>
       <c r="D4" s="16" t="s">
@@ -5196,7 +5311,7 @@
       <c r="B5" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="24">
         <v>0.25</v>
       </c>
       <c r="D5" s="16" t="s">
@@ -5210,7 +5325,7 @@
       <c r="B6" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="24">
         <v>0.15</v>
       </c>
       <c r="D6" s="16" t="s">
@@ -5224,7 +5339,7 @@
       <c r="B7" s="16" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="24">
         <v>0.15</v>
       </c>
       <c r="D7" s="16" t="s">
@@ -5238,7 +5353,7 @@
       <c r="B8" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="24">
         <v>0.1</v>
       </c>
       <c r="D8" s="16" t="s">
@@ -5246,17 +5361,17 @@
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:4">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="25" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" ht="19.2" spans="1:4">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="26" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="28" t="s">
+      <c r="A13" s="27" t="s">
         <v>140</v>
       </c>
       <c r="B13" s="13" t="s">
@@ -5270,7 +5385,7 @@
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="29"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="14" t="s">
         <v>178</v>
       </c>
@@ -5282,7 +5397,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="29"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="14" t="s">
         <v>181</v>
       </c>
@@ -5294,7 +5409,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="30"/>
+      <c r="A16" s="29"/>
       <c r="B16" s="14" t="s">
         <v>184</v>
       </c>
@@ -5306,7 +5421,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="27" t="s">
         <v>161</v>
       </c>
       <c r="B18" s="13" t="s">
@@ -5320,7 +5435,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="29"/>
+      <c r="A19" s="28"/>
       <c r="B19" s="14" t="s">
         <v>187</v>
       </c>
@@ -5332,7 +5447,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="29"/>
+      <c r="A20" s="28"/>
       <c r="B20" s="14" t="s">
         <v>190</v>
       </c>
@@ -5344,7 +5459,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="30"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="14" t="s">
         <v>193</v>
       </c>
@@ -5356,95 +5471,95 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="30" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="29"/>
-      <c r="B25" s="32" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="32" t="s">
+      <c r="C25" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="31" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="29"/>
-      <c r="B26" s="32" t="s">
+      <c r="A26" s="28"/>
+      <c r="B26" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="31" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="31" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="30"/>
-      <c r="B27" s="32" t="s">
+      <c r="A27" s="29"/>
+      <c r="B27" s="31" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="32" t="s">
+      <c r="D27" s="31" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="33" t="s">
+      <c r="A29" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="32" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="34" t="s">
+      <c r="D29" s="32" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="33"/>
-      <c r="B30" s="32" t="s">
+      <c r="A30" s="4"/>
+      <c r="B30" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="D30" s="32" t="s">
+      <c r="D30" s="31" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="33"/>
-      <c r="B31" s="32" t="s">
+      <c r="A31" s="4"/>
+      <c r="B31" s="31" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="32" t="s">
+      <c r="C31" s="31" t="s">
         <v>210</v>
       </c>
-      <c r="D31" s="32" t="s">
+      <c r="D31" s="31" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="35" t="s">
+      <c r="A33" s="33" t="s">
         <v>212</v>
       </c>
       <c r="B33" s="13" t="s">
@@ -5458,7 +5573,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="35"/>
+      <c r="A34" s="33"/>
       <c r="B34" s="14" t="s">
         <v>213</v>
       </c>
@@ -5470,7 +5585,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="35"/>
+      <c r="A35" s="33"/>
       <c r="B35" s="14" t="s">
         <v>216</v>
       </c>
@@ -5482,7 +5597,7 @@
       </c>
     </row>
     <row r="38" ht="20.4" spans="1:4">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="34" t="s">
         <v>219</v>
       </c>
     </row>
@@ -5527,7 +5642,7 @@
       </c>
     </row>
     <row r="47" ht="15.6" spans="1:4">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="25" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5572,7 +5687,7 @@
       </c>
     </row>
     <row r="56" ht="20.4" spans="1:3">
-      <c r="A56" s="36" t="s">
+      <c r="A56" s="34" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5621,7 +5736,7 @@
       </c>
     </row>
     <row r="65" ht="37.8" spans="1:8">
-      <c r="A65" s="36" t="s">
+      <c r="A65" s="34" t="s">
         <v>254</v>
       </c>
     </row>
@@ -5664,13 +5779,13 @@
       <c r="D68" s="14">
         <v>6</v>
       </c>
-      <c r="E68" s="37">
+      <c r="E68" s="35">
         <v>0.082</v>
       </c>
       <c r="F68" s="14">
         <v>4</v>
       </c>
-      <c r="G68" s="38">
+      <c r="G68" s="36">
         <v>0.4</v>
       </c>
       <c r="H68" s="14" t="s">
@@ -5690,13 +5805,13 @@
       <c r="D69" s="14">
         <v>8</v>
       </c>
-      <c r="E69" s="37">
+      <c r="E69" s="35">
         <v>0.075</v>
       </c>
       <c r="F69" s="14">
         <v>3</v>
       </c>
-      <c r="G69" s="38">
+      <c r="G69" s="36">
         <v>0.25</v>
       </c>
       <c r="H69" s="14" t="s">
@@ -5716,13 +5831,13 @@
       <c r="D70" s="14">
         <v>4</v>
       </c>
-      <c r="E70" s="37">
+      <c r="E70" s="35">
         <v>0.051</v>
       </c>
       <c r="F70" s="14">
         <v>6</v>
       </c>
-      <c r="G70" s="38">
+      <c r="G70" s="36">
         <v>-0.3</v>
       </c>
       <c r="H70" s="14" t="s">
@@ -5730,15 +5845,15 @@
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="39"/>
+      <c r="A72" s="37"/>
     </row>
     <row r="73" ht="20.4" spans="1:8">
-      <c r="A73" s="40" t="s">
+      <c r="A73" s="38" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="76" ht="20.4" spans="1:8">
-      <c r="A76" s="36" t="s">
+      <c r="A76" s="34" t="s">
         <v>265</v>
       </c>
     </row>
@@ -5831,7 +5946,7 @@
       </c>
     </row>
     <row r="87" ht="37.8" spans="1:5">
-      <c r="A87" s="36" t="s">
+      <c r="A87" s="34" t="s">
         <v>290</v>
       </c>
     </row>
@@ -6057,15 +6172,15 @@
       </c>
     </row>
     <row r="103" ht="20.4" spans="1:5">
-      <c r="A103" s="36" t="s">
+      <c r="A103" s="34" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="104" ht="19.2" spans="1:5">
-      <c r="A104" s="41" t="s">
+      <c r="A104" s="39" t="s">
         <v>325</v>
       </c>
-      <c r="B104" s="22"/>
+      <c r="B104" s="3"/>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="15" t="s">
@@ -6172,15 +6287,15 @@
       </c>
     </row>
     <row r="119" ht="19.2" spans="1:2">
-      <c r="A119" s="42" t="s">
+      <c r="A119" s="40" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="43" t="s">
+      <c r="A121" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="B121" s="43" t="s">
+      <c r="B121" s="41" t="s">
         <v>268</v>
       </c>
     </row>
@@ -6249,15 +6364,15 @@
       </c>
     </row>
     <row r="131" ht="19.2" spans="1:2">
-      <c r="A131" s="42" t="s">
+      <c r="A131" s="40" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="43" t="s">
+      <c r="A133" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="B133" s="43" t="s">
+      <c r="B133" s="41" t="s">
         <v>268</v>
       </c>
     </row>
@@ -6326,15 +6441,15 @@
       </c>
     </row>
     <row r="143" ht="19.2" spans="1:2">
-      <c r="A143" s="42" t="s">
+      <c r="A143" s="40" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="43" t="s">
+      <c r="A145" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="B145" s="43" t="s">
+      <c r="B145" s="41" t="s">
         <v>268</v>
       </c>
     </row>
@@ -6395,121 +6510,121 @@
       </c>
     </row>
     <row r="154" ht="19.2" spans="1:2">
-      <c r="A154" s="42" t="s">
+      <c r="A154" s="40" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="43" t="s">
+      <c r="A156" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="B156" s="43" t="s">
+      <c r="B156" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="44" t="s">
+      <c r="A157" s="42" t="s">
         <v>329</v>
       </c>
-      <c r="B157" s="44" t="s">
+      <c r="B157" s="42" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="44" t="s">
+      <c r="A158" s="42" t="s">
         <v>377</v>
       </c>
-      <c r="B158" s="44" t="s">
+      <c r="B158" s="42" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="44" t="s">
+      <c r="A159" s="42" t="s">
         <v>379</v>
       </c>
-      <c r="B159" s="44" t="s">
+      <c r="B159" s="42" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="44" t="s">
+      <c r="A160" s="42" t="s">
         <v>381</v>
       </c>
-      <c r="B160" s="44" t="s">
+      <c r="B160" s="42" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="44" t="s">
+      <c r="A161" s="42" t="s">
         <v>383</v>
       </c>
-      <c r="B161" s="44" t="s">
+      <c r="B161" s="42" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="44" t="s">
+      <c r="A162" s="42" t="s">
         <v>385</v>
       </c>
-      <c r="B162" s="44" t="s">
+      <c r="B162" s="42" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="165" ht="19.2" spans="1:4">
-      <c r="A165" s="42" t="s">
+      <c r="A165" s="40" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="43" t="s">
+      <c r="A167" s="41" t="s">
         <v>326</v>
       </c>
-      <c r="B167" s="43" t="s">
+      <c r="B167" s="41" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="44" t="s">
+      <c r="A168" s="42" t="s">
         <v>352</v>
       </c>
-      <c r="B168" s="44" t="s">
+      <c r="B168" s="42" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="44" t="s">
+      <c r="A169" s="42" t="s">
         <v>388</v>
       </c>
-      <c r="B169" s="44" t="s">
+      <c r="B169" s="42" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="44" t="s">
+      <c r="A170" s="42" t="s">
         <v>390</v>
       </c>
-      <c r="B170" s="44" t="s">
+      <c r="B170" s="42" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="44" t="s">
+      <c r="A171" s="42" t="s">
         <v>392</v>
       </c>
-      <c r="B171" s="44" t="s">
+      <c r="B171" s="42" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="44" t="s">
+      <c r="A172" s="42" t="s">
         <v>394</v>
       </c>
-      <c r="B172" s="44" t="s">
+      <c r="B172" s="42" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="174" ht="20.4" spans="1:4">
-      <c r="A174" s="36" t="s">
+      <c r="A174" s="34" t="s">
         <v>396</v>
       </c>
     </row>
@@ -6528,7 +6643,7 @@
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="45" t="s">
+      <c r="A177" s="43" t="s">
         <v>401</v>
       </c>
       <c r="B177" s="14" t="s">
@@ -6542,7 +6657,7 @@
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="46"/>
+      <c r="A178" s="44"/>
       <c r="B178" s="14" t="s">
         <v>184</v>
       </c>
@@ -6554,7 +6669,7 @@
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="47"/>
+      <c r="A179" s="45"/>
       <c r="B179" s="14" t="s">
         <v>405</v>
       </c>
@@ -6566,7 +6681,7 @@
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="45" t="s">
+      <c r="A180" s="43" t="s">
         <v>407</v>
       </c>
       <c r="B180" s="14" t="s">
@@ -6580,7 +6695,7 @@
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="46"/>
+      <c r="A181" s="44"/>
       <c r="B181" s="14" t="s">
         <v>410</v>
       </c>
@@ -6592,7 +6707,7 @@
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="46"/>
+      <c r="A182" s="44"/>
       <c r="B182" s="14" t="s">
         <v>412</v>
       </c>
@@ -6604,7 +6719,7 @@
       </c>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="47"/>
+      <c r="A183" s="45"/>
       <c r="B183" s="14" t="s">
         <v>193</v>
       </c>
@@ -6616,7 +6731,7 @@
       </c>
     </row>
     <row r="184" ht="28.8" spans="1:4">
-      <c r="A184" s="45" t="s">
+      <c r="A184" s="43" t="s">
         <v>415</v>
       </c>
       <c r="B184" s="14" t="s">
@@ -6630,7 +6745,7 @@
       </c>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="46"/>
+      <c r="A185" s="44"/>
       <c r="B185" s="14" t="s">
         <v>418</v>
       </c>
@@ -6642,7 +6757,7 @@
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="47"/>
+      <c r="A186" s="45"/>
       <c r="B186" s="14" t="s">
         <v>420</v>
       </c>
@@ -6654,7 +6769,7 @@
       </c>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="45" t="s">
+      <c r="A187" s="43" t="s">
         <v>422</v>
       </c>
       <c r="B187" s="14" t="s">
@@ -6668,7 +6783,7 @@
       </c>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="46"/>
+      <c r="A188" s="44"/>
       <c r="B188" s="14" t="s">
         <v>425</v>
       </c>
@@ -6680,7 +6795,7 @@
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="47"/>
+      <c r="A189" s="45"/>
       <c r="B189" s="14" t="s">
         <v>427</v>
       </c>
@@ -6692,7 +6807,7 @@
       </c>
     </row>
     <row r="191" ht="20.4" spans="1:4">
-      <c r="A191" s="36" t="s">
+      <c r="A191" s="34" t="s">
         <v>429</v>
       </c>
     </row>
@@ -6842,15 +6957,15 @@
       </c>
     </row>
     <row r="200" ht="20.4" spans="1:9">
-      <c r="A200" s="36" t="s">
+      <c r="A200" s="34" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="202" ht="15.6" spans="1:9">
-      <c r="A202" s="41" t="s">
+      <c r="A202" s="39" t="s">
         <v>438</v>
       </c>
-      <c r="B202" s="22"/>
+      <c r="B202" s="3"/>
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="15" t="s">
@@ -6885,11 +7000,11 @@
       </c>
     </row>
     <row r="208" ht="15.6" spans="1:9">
-      <c r="A208" s="41" t="s">
+      <c r="A208" s="39" t="s">
         <v>442</v>
       </c>
-      <c r="B208" s="22"/>
-      <c r="C208" s="22"/>
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
     </row>
     <row r="209" spans="1:3">
       <c r="A209" s="15" t="s">
@@ -6996,22 +7111,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="3" t="s">
         <v>467</v>
       </c>
     </row>

--- a/需求整理/industry_indicator_system.xlsx
+++ b/需求整理/industry_indicator_system.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" firstSheet="1" activeTab="5"/>
+    <workbookView windowWidth="30720" windowHeight="13500" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Industry Indicators" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="837">
   <si>
     <t>指标名称</t>
   </si>
@@ -2100,9 +2100,6 @@
   </si>
   <si>
     <t>产品</t>
-  </si>
-  <si>
-    <t>板块景气度</t>
   </si>
   <si>
     <t>板块订单情况</t>
@@ -7594,18 +7591,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:J63"/>
+  <dimension ref="B2:I63"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="3" width="32.1111111111111" customWidth="1"/>
     <col min="4" max="4" width="20.8888888888889" customWidth="1"/>
     <col min="5" max="5" width="50.1111111111111" customWidth="1"/>
-    <col min="6" max="6" width="11.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="14.1111111111111" customWidth="1"/>
-    <col min="8" max="8" width="37.7777777777778" customWidth="1"/>
+    <col min="6" max="6" width="14.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="37.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:9">
       <c r="B2" s="3" t="s">
         <v>562</v>
       </c>
@@ -7630,840 +7626,776 @@
       <c r="I2" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="J2" s="3" t="s">
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" s="4" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="3" spans="2:10">
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>573</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>574</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="2:10">
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="4"/>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
       <c r="E4" s="6" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="2:10">
+    </row>
+    <row r="5" spans="2:9">
       <c r="B5" s="4"/>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
       <c r="E5" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="2:10">
+    </row>
+    <row r="6" spans="2:9">
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="6" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="2:10">
+    </row>
+    <row r="7" spans="2:9">
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
       <c r="D7" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>578</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>579</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="2:10">
+    </row>
+    <row r="8" spans="2:9">
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
       <c r="E8" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="2:10">
+    </row>
+    <row r="9" spans="2:9">
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="2:10">
+    </row>
+    <row r="10" spans="2:9">
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
       <c r="D10" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>582</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>583</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="2:10">
+    </row>
+    <row r="11" spans="2:9">
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="2:10">
+    </row>
+    <row r="12" spans="2:9">
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="2:10">
+    </row>
+    <row r="13" spans="2:9">
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="6" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="2:10">
+    </row>
+    <row r="14" spans="2:9">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="6" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-    </row>
-    <row r="15" spans="2:10">
+    </row>
+    <row r="15" spans="2:9">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>588</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>589</v>
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16" spans="2:10">
+    </row>
+    <row r="16" spans="2:9">
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="2:10">
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="2:10">
+    </row>
+    <row r="18" spans="2:9">
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-    </row>
-    <row r="19" spans="2:10">
+    </row>
+    <row r="19" spans="2:9">
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>593</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>594</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="2:10">
+    </row>
+    <row r="20" spans="2:9">
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="2:10">
+    </row>
+    <row r="21" spans="2:9">
       <c r="B21" s="4"/>
       <c r="C21" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>596</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="6" t="s">
         <v>597</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>598</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-    </row>
-    <row r="22" spans="2:10">
+    </row>
+    <row r="22" spans="2:9">
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-    </row>
-    <row r="23" spans="2:10">
+    </row>
+    <row r="23" spans="2:9">
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-    </row>
-    <row r="24" spans="2:10">
+    </row>
+    <row r="24" spans="2:9">
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>601</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>602</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-    </row>
-    <row r="25" spans="2:10">
+    </row>
+    <row r="25" spans="2:9">
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="6" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-    </row>
-    <row r="26" spans="2:10">
+    </row>
+    <row r="26" spans="2:9">
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" spans="2:10">
+    </row>
+    <row r="27" spans="2:9">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-    </row>
-    <row r="28" spans="2:10">
+    </row>
+    <row r="28" spans="2:9">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>606</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>607</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-    </row>
-    <row r="29" spans="2:10">
+    </row>
+    <row r="29" spans="2:9">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="6" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-    </row>
-    <row r="30" spans="2:10">
+    </row>
+    <row r="30" spans="2:9">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="6" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-    </row>
-    <row r="31" spans="2:10">
+    </row>
+    <row r="31" spans="2:9">
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
       <c r="E31" s="6" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="3"/>
-    </row>
-    <row r="32" spans="2:10">
+    </row>
+    <row r="32" spans="2:9">
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
       <c r="E32" s="6" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-    </row>
-    <row r="33" spans="2:10">
+    </row>
+    <row r="33" spans="2:9">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
       <c r="E33" s="6" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="3"/>
-    </row>
-    <row r="34" ht="19.2" spans="2:10">
+    </row>
+    <row r="34" ht="19.2" spans="2:9">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>613</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>614</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-    </row>
-    <row r="35" ht="19.2" spans="2:10">
+    </row>
+    <row r="35" ht="19.2" spans="2:9">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="3"/>
-    </row>
-    <row r="36" spans="2:10">
+    </row>
+    <row r="36" spans="2:9">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
       <c r="E36" s="6" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-    </row>
-    <row r="37" spans="2:10">
+    </row>
+    <row r="37" spans="2:9">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
       <c r="E37" s="6" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="3"/>
-    </row>
-    <row r="38" spans="2:10">
+    </row>
+    <row r="38" spans="2:9">
       <c r="B38" s="4"/>
       <c r="C38" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="D38" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="E38" s="6" t="s">
         <v>619</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>620</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-    </row>
-    <row r="39" ht="19.2" spans="2:10">
+    </row>
+    <row r="39" ht="19.2" spans="2:9">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
       <c r="E39" s="6" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
-    </row>
-    <row r="40" spans="2:10">
+    </row>
+    <row r="40" spans="2:9">
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
       <c r="E40" s="6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="41" spans="2:10">
+    </row>
+    <row r="41" spans="2:9">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
       <c r="E41" s="6" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-    </row>
-    <row r="42" spans="2:10">
+    </row>
+    <row r="42" spans="2:9">
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
       <c r="E42" s="6" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-    </row>
-    <row r="43" spans="2:10">
+    </row>
+    <row r="43" spans="2:9">
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
       <c r="E43" s="6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="44" ht="19.2" spans="2:10">
+    </row>
+    <row r="44" ht="19.2" spans="2:9">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="E44" s="6" t="s">
         <v>626</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>627</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-    </row>
-    <row r="45" ht="19.2" spans="2:10">
+    </row>
+    <row r="45" ht="19.2" spans="2:9">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
       <c r="E45" s="6" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-    </row>
-    <row r="46" spans="2:10">
+    </row>
+    <row r="46" spans="2:9">
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
       <c r="E46" s="6" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="3"/>
-    </row>
-    <row r="47" spans="2:10">
+    </row>
+    <row r="47" spans="2:9">
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="6" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-    </row>
-    <row r="48" ht="19.2" spans="2:10">
+    </row>
+    <row r="48" ht="19.2" spans="2:9">
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>631</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>632</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="3"/>
-    </row>
-    <row r="49" ht="15.6" spans="2:10">
+    </row>
+    <row r="49" ht="15.6" spans="2:9">
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="6" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-    </row>
-    <row r="50" ht="19.2" spans="2:10">
+    </row>
+    <row r="50" ht="19.2" spans="2:9">
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="E50" s="6" t="s">
         <v>634</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>635</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="3"/>
-    </row>
-    <row r="51" ht="19.2" spans="2:10">
+    </row>
+    <row r="51" ht="19.2" spans="2:9">
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
       <c r="E51" s="6" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-    </row>
-    <row r="52" ht="19.2" spans="2:10">
+    </row>
+    <row r="52" ht="19.2" spans="2:9">
       <c r="B52" s="4"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
       <c r="E52" s="6" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="3"/>
-    </row>
-    <row r="53" ht="19.2" spans="2:10">
+    </row>
+    <row r="53" ht="19.2" spans="2:9">
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>638</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>639</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-    </row>
-    <row r="54" ht="19.2" spans="2:10">
+    </row>
+    <row r="54" ht="19.2" spans="2:9">
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
       <c r="E54" s="6" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
-      <c r="J54" s="3"/>
-    </row>
-    <row r="55" ht="19.2" spans="2:10">
+    </row>
+    <row r="55" ht="19.2" spans="2:9">
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
       <c r="D55" s="5"/>
       <c r="E55" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-    </row>
-    <row r="56" spans="2:10">
+    </row>
+    <row r="56" spans="2:9">
       <c r="B56" s="4"/>
       <c r="C56" s="5"/>
       <c r="D56" s="5"/>
       <c r="E56" s="6" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-      <c r="J56" s="3"/>
-    </row>
-    <row r="57" spans="2:10">
+    </row>
+    <row r="57" spans="2:9">
       <c r="B57" s="4"/>
       <c r="C57" s="5"/>
       <c r="D57" s="5"/>
       <c r="E57" s="6" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-    </row>
-    <row r="58" ht="15.6" spans="2:10">
+    </row>
+    <row r="58" ht="15.6" spans="2:9">
       <c r="B58" s="4"/>
       <c r="C58" s="5"/>
       <c r="D58" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="E58" s="6" t="s">
         <v>644</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>645</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-    </row>
-    <row r="59" ht="15.6" spans="2:10">
+    </row>
+    <row r="59" ht="15.6" spans="2:9">
       <c r="B59" s="4"/>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="6" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-    </row>
-    <row r="60" ht="15.6" spans="2:10">
+    </row>
+    <row r="60" ht="15.6" spans="2:9">
       <c r="B60" s="4"/>
       <c r="C60" s="5"/>
       <c r="D60" s="5"/>
       <c r="E60" s="6" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-    </row>
-    <row r="61" ht="19.2" spans="2:10">
+    </row>
+    <row r="61" ht="19.2" spans="2:9">
       <c r="B61" s="4"/>
       <c r="C61" s="5"/>
       <c r="D61" s="5"/>
       <c r="E61" s="6" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-    </row>
-    <row r="62" spans="2:10">
+    </row>
+    <row r="62" spans="2:9">
       <c r="B62" s="4"/>
       <c r="C62" s="5"/>
       <c r="D62" s="5"/>
       <c r="E62" s="6" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-    </row>
-    <row r="63" spans="2:10">
+    </row>
+    <row r="63" spans="2:9">
       <c r="B63" s="4"/>
       <c r="C63" s="5"/>
       <c r="D63" s="5"/>
       <c r="E63" s="6" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -8500,117 +8432,117 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8620,12 +8552,12 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -8641,7 +8573,7 @@
         <v>332</v>
       </c>
       <c r="B37" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -8649,7 +8581,7 @@
         <v>342</v>
       </c>
       <c r="B38" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -8657,7 +8589,7 @@
         <v>344</v>
       </c>
       <c r="B39" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8665,7 +8597,7 @@
         <v>346</v>
       </c>
       <c r="B40" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8673,59 +8605,59 @@
         <v>340</v>
       </c>
       <c r="B41" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
+        <v>684</v>
+      </c>
+      <c r="B48" t="s">
         <v>685</v>
-      </c>
-      <c r="B48" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>686</v>
+      </c>
+      <c r="B49" t="s">
         <v>687</v>
-      </c>
-      <c r="B49" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>688</v>
+      </c>
+      <c r="B50" t="s">
         <v>689</v>
-      </c>
-      <c r="B50" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>690</v>
+      </c>
+      <c r="B51" t="s">
         <v>691</v>
-      </c>
-      <c r="B51" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -8733,123 +8665,123 @@
         <v>46056</v>
       </c>
       <c r="B52" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>693</v>
+      </c>
+      <c r="B53" t="s">
         <v>694</v>
-      </c>
-      <c r="B53" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B59" t="s">
         <v>342</v>
       </c>
       <c r="C59" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>700</v>
+      </c>
+      <c r="B60" t="s">
+        <v>700</v>
+      </c>
+      <c r="C60" t="s">
         <v>701</v>
-      </c>
-      <c r="B60" t="s">
-        <v>701</v>
-      </c>
-      <c r="C60" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B61" t="s">
+        <v>702</v>
+      </c>
+      <c r="C61" t="s">
         <v>703</v>
-      </c>
-      <c r="C61" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B62" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C62" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B63" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C63" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B72" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -8857,7 +8789,7 @@
         <v>46024</v>
       </c>
       <c r="B73" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -8865,7 +8797,7 @@
         <v>46086</v>
       </c>
       <c r="B74" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -8873,30 +8805,30 @@
         <v>46183</v>
       </c>
       <c r="B75" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
+        <v>716</v>
+      </c>
+      <c r="B76" t="s">
         <v>717</v>
-      </c>
-      <c r="B76" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -8907,17 +8839,17 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8930,26 +8862,26 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
+        <v>724</v>
+      </c>
+      <c r="B91" t="s">
         <v>725</v>
-      </c>
-      <c r="B91" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
+        <v>726</v>
+      </c>
+      <c r="B92" t="s">
         <v>727</v>
-      </c>
-      <c r="B92" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
+        <v>728</v>
+      </c>
+      <c r="B93" t="s">
         <v>729</v>
-      </c>
-      <c r="B93" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8957,30 +8889,30 @@
         <v>213</v>
       </c>
       <c r="B94" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
+        <v>731</v>
+      </c>
+      <c r="B95" t="s">
         <v>732</v>
-      </c>
-      <c r="B95" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8988,12 +8920,12 @@
         <v>155</v>
       </c>
       <c r="B101" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B102" s="2">
         <v>0.3</v>
@@ -9001,7 +8933,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B103" s="2">
         <v>0.25</v>
@@ -9009,7 +8941,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B104" s="2">
         <v>0.15</v>
@@ -9025,7 +8957,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B106" s="2">
         <v>0.15</v>
@@ -9033,70 +8965,70 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>742</v>
+      </c>
+      <c r="B108" t="s">
         <v>743</v>
-      </c>
-      <c r="B108" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>744</v>
+      </c>
+      <c r="B109" t="s">
         <v>745</v>
-      </c>
-      <c r="B109" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>746</v>
+      </c>
+      <c r="B110" t="s">
         <v>747</v>
-      </c>
-      <c r="B110" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>748</v>
+      </c>
+      <c r="B111" t="s">
         <v>749</v>
-      </c>
-      <c r="B111" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
+        <v>750</v>
+      </c>
+      <c r="B112" t="s">
         <v>751</v>
-      </c>
-      <c r="B112" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
+        <v>752</v>
+      </c>
+      <c r="B113" t="s">
         <v>753</v>
-      </c>
-      <c r="B113" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B118" t="s">
         <v>294</v>
@@ -9104,70 +9036,70 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>757</v>
+      </c>
+      <c r="B119" t="s">
         <v>758</v>
-      </c>
-      <c r="B119" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>759</v>
+      </c>
+      <c r="B120" t="s">
         <v>760</v>
-      </c>
-      <c r="B120" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>761</v>
+      </c>
+      <c r="B121" t="s">
         <v>762</v>
-      </c>
-      <c r="B121" t="s">
-        <v>763</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
+        <v>763</v>
+      </c>
+      <c r="B122" t="s">
         <v>764</v>
-      </c>
-      <c r="B122" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
+        <v>765</v>
+      </c>
+      <c r="B123" t="s">
         <v>766</v>
-      </c>
-      <c r="B123" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
+        <v>767</v>
+      </c>
+      <c r="B124" t="s">
         <v>768</v>
-      </c>
-      <c r="B124" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -9214,12 +9146,12 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="140" spans="1:1">
@@ -9266,12 +9198,12 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="149" spans="1:1">
@@ -9306,192 +9238,192 @@
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="196" spans="1:1">
@@ -9501,117 +9433,117 @@
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>

--- a/需求整理/industry_indicator_system.xlsx
+++ b/需求整理/industry_indicator_system.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="886">
   <si>
     <t>指标名称</t>
   </si>
@@ -2660,6 +2660,153 @@
     <t>数字营销/电子政务/在线教育/智慧医疗/游戏</t>
   </si>
   <si>
+    <t>产业链环节</t>
+  </si>
+  <si>
+    <t>分类/子领域</t>
+  </si>
+  <si>
+    <t>具体项</t>
+  </si>
+  <si>
+    <t>详细说明与代表企业</t>
+  </si>
+  <si>
+    <t>上游</t>
+  </si>
+  <si>
+    <t>材料</t>
+  </si>
+  <si>
+    <t>硅片</t>
+  </si>
+  <si>
+    <t>信越（日，35%）、沪硅（中，20%）</t>
+  </si>
+  <si>
+    <t>光刻胶</t>
+  </si>
+  <si>
+    <t>陶氏（美，EUV）、上海新阳（中，28nm）</t>
+  </si>
+  <si>
+    <t>电子气体</t>
+  </si>
+  <si>
+    <t>林德（德，40%）、华特（中）</t>
+  </si>
+  <si>
+    <t>CMP材料</t>
+  </si>
+  <si>
+    <t>应用材料（美）、安集（中，纳米级）</t>
+  </si>
+  <si>
+    <t>设备</t>
+  </si>
+  <si>
+    <t>光刻机</t>
+  </si>
+  <si>
+    <t>ASML（荷，EUV）、上海微电子（中，28nm DUV）</t>
+  </si>
+  <si>
+    <t>刻蚀机/薄膜设备</t>
+  </si>
+  <si>
+    <t>泛林（美）、中微（中，5nm）、北方华创（中，14nm）</t>
+  </si>
+  <si>
+    <t>中游</t>
+  </si>
+  <si>
+    <t>设计</t>
+  </si>
+  <si>
+    <t>SoC</t>
+  </si>
+  <si>
+    <t>高通（美，手机）、海思（中，麒麟）、寒武纪（中）</t>
+  </si>
+  <si>
+    <t>GPU/AI</t>
+  </si>
+  <si>
+    <t>英伟达（美，H100）、寒武纪（中）</t>
+  </si>
+  <si>
+    <t>存储</t>
+  </si>
+  <si>
+    <t>兆易（中，NOR）、美光（美，DRAM）</t>
+  </si>
+  <si>
+    <t>制造</t>
+  </si>
+  <si>
+    <t>先进制程</t>
+  </si>
+  <si>
+    <t>台积电（台，3nm）、中芯国际（中，28nm）</t>
+  </si>
+  <si>
+    <t>成熟制程</t>
+  </si>
+  <si>
+    <t>长鑫（中，DRAM）、SK海力士（韩，NAND）</t>
+  </si>
+  <si>
+    <t>封测</t>
+  </si>
+  <si>
+    <t>先进封装</t>
+  </si>
+  <si>
+    <t>长电（中，SiP）、日月光（台）</t>
+  </si>
+  <si>
+    <t>下游</t>
+  </si>
+  <si>
+    <t>消费电子</t>
+  </si>
+  <si>
+    <t>手机</t>
+  </si>
+  <si>
+    <t>苹果（A系列）、小米（采购SoC）</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>英特尔（CPU）、AMD（GPU）</t>
+  </si>
+  <si>
+    <t>汽车电子</t>
+  </si>
+  <si>
+    <t>自动驾驶</t>
+  </si>
+  <si>
+    <t>特斯拉（HW芯片）、地平线（征程）、比亚迪（IGBT）、英飞凌（SiC）</t>
+  </si>
+  <si>
+    <t>电驱</t>
+  </si>
+  <si>
+    <t>华为（天罡芯片）、中兴（基站）</t>
+  </si>
+  <si>
+    <t>工业通信</t>
+  </si>
+  <si>
+    <t>工业</t>
+  </si>
+  <si>
+    <t>德州仪器（MCU）、兆易（工控）</t>
+  </si>
+  <si>
     <t>📊 量价关系分析模块需求文档（PRD）</t>
   </si>
   <si>
@@ -3231,13 +3378,26 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="33">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Alibaba PuHuiTi 2.0"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Alibaba PuHuiTi 2.0"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -3458,12 +3618,36 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F3FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6FFED"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -3492,12 +3676,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3670,7 +3848,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -3689,6 +3867,21 @@
         <color auto="1"/>
       </top>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -3846,137 +4039,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3990,72 +4183,90 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -4064,22 +4275,19 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -4087,7 +4295,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4463,22 +4674,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
     </row>
@@ -4569,7 +4780,7 @@
       <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="22" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -4723,13 +4934,13 @@
       </c>
     </row>
     <row r="15" ht="100.8" spans="1:6">
-      <c r="A15" s="42" t="s">
+      <c r="A15" s="48" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="48" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4754,473 +4965,473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="52" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="C1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="D1" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="52" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="46" t="s">
+      <c r="F1" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="10"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" ht="115.2" spans="1:7">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="53" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="53" t="s">
         <v>77</v>
       </c>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47" t="s">
+      <c r="E2" s="53"/>
+      <c r="F2" s="53" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="16" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" ht="273.6" spans="1:7">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="47" t="s">
+      <c r="A3" s="53"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="E3" s="53" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47" t="s">
+      <c r="A4" s="53"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47" t="s">
+      <c r="E4" s="53"/>
+      <c r="F4" s="53" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="47"/>
-      <c r="B5" s="47"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="47" t="s">
+      <c r="A5" s="53"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="E5" s="47"/>
-      <c r="F5" s="47"/>
-      <c r="G5" s="10"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="16"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="47"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="47" t="s">
+      <c r="A6" s="53"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="10"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="16"/>
     </row>
     <row r="7" ht="72" spans="1:7">
-      <c r="A7" s="47"/>
-      <c r="B7" s="47"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="47" t="s">
+      <c r="A7" s="53"/>
+      <c r="B7" s="53"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="53" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="53" t="s">
         <v>89</v>
       </c>
-      <c r="F7" s="47"/>
-      <c r="G7" s="10"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="16"/>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="47"/>
-      <c r="B8" s="47" t="s">
+      <c r="A8" s="53"/>
+      <c r="B8" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="10"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="16"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="47"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47" t="s">
+      <c r="A9" s="53"/>
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="10"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="16"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="47"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47" t="s">
+      <c r="A10" s="53"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="53"/>
+      <c r="D10" s="53" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="10"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="16"/>
     </row>
     <row r="11" ht="57.6" spans="1:7">
-      <c r="A11" s="47"/>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="47" t="s">
+      <c r="A11" s="53"/>
+      <c r="B11" s="53"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="47" t="s">
+      <c r="E11" s="53" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="47"/>
-      <c r="G11" s="10"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="16"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="47"/>
-      <c r="B12" s="47" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="53" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D12" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="10"/>
+      <c r="E12" s="53"/>
+      <c r="F12" s="53"/>
+      <c r="G12" s="16"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="47" t="s">
+      <c r="A13" s="53"/>
+      <c r="B13" s="53"/>
+      <c r="C13" s="53"/>
+      <c r="D13" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="10"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" ht="43.2" spans="1:7">
-      <c r="A14" s="47"/>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47" t="s">
+      <c r="A14" s="53"/>
+      <c r="B14" s="53"/>
+      <c r="C14" s="53"/>
+      <c r="D14" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="E14" s="47" t="s">
+      <c r="E14" s="53" t="s">
         <v>102</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="10"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="16"/>
     </row>
     <row r="15" ht="57.6" spans="1:7">
-      <c r="A15" s="47"/>
-      <c r="B15" s="47" t="s">
+      <c r="A15" s="53"/>
+      <c r="B15" s="53" t="s">
         <v>103</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="49" t="s">
+      <c r="C15" s="53"/>
+      <c r="D15" s="55" t="s">
         <v>104</v>
       </c>
-      <c r="E15" s="47" t="s">
+      <c r="E15" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="F15" s="47"/>
-      <c r="G15" s="10"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="47" t="s">
+      <c r="A16" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="53" t="s">
         <v>107</v>
       </c>
-      <c r="C16" s="47" t="s">
+      <c r="C16" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="53" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="47" t="s">
+      <c r="E16" s="53" t="s">
         <v>110</v>
       </c>
-      <c r="F16" s="47"/>
-      <c r="G16" s="10"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="16"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="47"/>
-      <c r="B17" s="47"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="47" t="s">
+      <c r="A17" s="53"/>
+      <c r="B17" s="53"/>
+      <c r="C17" s="53"/>
+      <c r="D17" s="53" t="s">
         <v>111</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="E17" s="53" t="s">
         <v>112</v>
       </c>
-      <c r="F17" s="47"/>
-      <c r="G17" s="10"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="16"/>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="47"/>
-      <c r="B18" s="47" t="s">
+      <c r="A18" s="53"/>
+      <c r="B18" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="47" t="s">
+      <c r="C18" s="53" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="55" t="s">
         <v>115</v>
       </c>
-      <c r="E18" s="49"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="10"/>
+      <c r="E18" s="55"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="47"/>
-      <c r="B19" s="47"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47" t="s">
+      <c r="A19" s="53"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="10"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="16"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="47"/>
-      <c r="B20" s="47" t="s">
+      <c r="A20" s="53"/>
+      <c r="B20" s="53" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="47" t="s">
+      <c r="C20" s="53" t="s">
         <v>118</v>
       </c>
-      <c r="D20" s="47" t="s">
+      <c r="D20" s="53" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="E20" s="53" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="47"/>
-      <c r="G20" s="10"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="16"/>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="47"/>
-      <c r="B21" s="47"/>
-      <c r="C21" s="47"/>
-      <c r="D21" s="47" t="s">
+      <c r="A21" s="53"/>
+      <c r="B21" s="53"/>
+      <c r="C21" s="53"/>
+      <c r="D21" s="53" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="53" t="s">
         <v>122</v>
       </c>
-      <c r="F21" s="47"/>
-      <c r="G21" s="10"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" ht="72" spans="1:7">
-      <c r="A22" s="47"/>
-      <c r="B22" s="47" t="s">
+      <c r="A22" s="53"/>
+      <c r="B22" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="D22" s="47"/>
-      <c r="E22" s="47" t="s">
+      <c r="D22" s="53"/>
+      <c r="E22" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="F22" s="47"/>
-      <c r="G22" s="10"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="53" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="53" t="s">
         <v>128</v>
       </c>
-      <c r="D23" s="47" t="s">
+      <c r="D23" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="10"/>
+      <c r="E23" s="53"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="16"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="47"/>
-      <c r="B24" s="47"/>
-      <c r="C24" s="47" t="s">
+      <c r="A24" s="53"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="D24" s="47" t="s">
+      <c r="D24" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="10"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" ht="43.2" spans="1:7">
-      <c r="A25" s="47"/>
-      <c r="B25" s="47"/>
-      <c r="C25" s="48" t="s">
+      <c r="A25" s="53"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47" t="s">
+      <c r="D25" s="53"/>
+      <c r="E25" s="53" t="s">
         <v>133</v>
       </c>
-      <c r="F25" s="48"/>
-      <c r="G25" s="10"/>
+      <c r="F25" s="54"/>
+      <c r="G25" s="16"/>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="47"/>
-      <c r="B26" s="47" t="s">
+      <c r="A26" s="53"/>
+      <c r="B26" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="53" t="s">
         <v>135</v>
       </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="10"/>
+      <c r="D26" s="53"/>
+      <c r="E26" s="53"/>
+      <c r="F26" s="53"/>
+      <c r="G26" s="16"/>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="47"/>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47" t="s">
+      <c r="A27" s="53"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53" t="s">
         <v>136</v>
       </c>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="10"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="16"/>
     </row>
     <row r="28" ht="43.2" spans="1:7">
-      <c r="A28" s="47"/>
-      <c r="B28" s="47"/>
-      <c r="C28" s="48" t="s">
+      <c r="A28" s="53"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="D28" s="47"/>
-      <c r="E28" s="47" t="s">
+      <c r="D28" s="53"/>
+      <c r="E28" s="53" t="s">
         <v>138</v>
       </c>
-      <c r="F28" s="47"/>
-      <c r="G28" s="10"/>
+      <c r="F28" s="53"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="47"/>
-      <c r="B29" s="47" t="s">
+      <c r="A29" s="53"/>
+      <c r="B29" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="53" t="s">
         <v>141</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="10"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="16"/>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
-      <c r="C30" s="48" t="s">
+      <c r="A30" s="53"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="47" t="s">
+      <c r="D30" s="53" t="s">
         <v>143</v>
       </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="10"/>
+      <c r="E30" s="53"/>
+      <c r="F30" s="54"/>
+      <c r="G30" s="16"/>
     </row>
     <row r="31" ht="43.2" spans="1:7">
-      <c r="A31" s="47"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="48" t="s">
+      <c r="A31" s="53"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="54" t="s">
         <v>144</v>
       </c>
-      <c r="D31" s="49"/>
-      <c r="E31" s="47" t="s">
+      <c r="D31" s="55"/>
+      <c r="E31" s="53" t="s">
         <v>145</v>
       </c>
-      <c r="F31" s="48"/>
-      <c r="G31" s="10"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="16"/>
     </row>
     <row r="32" ht="57.6" spans="1:7">
-      <c r="A32" s="47"/>
-      <c r="B32" s="48" t="s">
+      <c r="A32" s="53"/>
+      <c r="B32" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="C32" s="48" t="s">
+      <c r="C32" s="54" t="s">
         <v>147</v>
       </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="47" t="s">
+      <c r="D32" s="55"/>
+      <c r="E32" s="53" t="s">
         <v>148</v>
       </c>
-      <c r="F32" s="48"/>
-      <c r="G32" s="10"/>
+      <c r="F32" s="54"/>
+      <c r="G32" s="16"/>
     </row>
     <row r="33" ht="158.4" spans="1:7">
-      <c r="A33" s="49" t="s">
+      <c r="A33" s="55" t="s">
         <v>149</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="D33" s="31" t="s">
+      <c r="D33" s="37" t="s">
         <v>152</v>
       </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="49"/>
-      <c r="G33" s="10"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -5261,12 +5472,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="28" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="2" ht="20.4" spans="1:4">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="29" t="s">
         <v>154</v>
       </c>
       <c r="B2" s="3"/>
@@ -5274,246 +5485,246 @@
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="21" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="4" ht="28.8" spans="1:4">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="30">
         <v>0.35</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="22" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="5" ht="28.8" spans="1:4">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="30">
         <v>0.25</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="22" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="6" ht="28.8" spans="1:4">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="30">
         <v>0.15</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="22" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="30">
         <v>0.15</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="22" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="22" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="30">
         <v>0.1</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="22" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" ht="15.6" spans="1:4">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="31" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" ht="19.2" spans="1:4">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="32" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="19" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="28"/>
-      <c r="B14" s="14" t="s">
+      <c r="A14" s="34"/>
+      <c r="B14" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="20" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="28"/>
-      <c r="B15" s="14" t="s">
+      <c r="A15" s="34"/>
+      <c r="B15" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="20" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="29"/>
-      <c r="B16" s="14" t="s">
+      <c r="A16" s="35"/>
+      <c r="B16" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="20" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="19" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="28"/>
-      <c r="B19" s="14" t="s">
+      <c r="A19" s="34"/>
+      <c r="B19" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="20" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="28"/>
-      <c r="B20" s="14" t="s">
+      <c r="A20" s="34"/>
+      <c r="B20" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="20" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="29"/>
-      <c r="B21" s="14" t="s">
+      <c r="A21" s="35"/>
+      <c r="B21" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="20" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="30" t="s">
+      <c r="C24" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="30" t="s">
+      <c r="D24" s="36" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="28"/>
-      <c r="B25" s="31" t="s">
+      <c r="A25" s="34"/>
+      <c r="B25" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="D25" s="31" t="s">
+      <c r="D25" s="37" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="28"/>
-      <c r="B26" s="31" t="s">
+      <c r="A26" s="34"/>
+      <c r="B26" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="D26" s="31" t="s">
+      <c r="D26" s="37" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="29"/>
-      <c r="B27" s="31" t="s">
+      <c r="A27" s="35"/>
+      <c r="B27" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="37" t="s">
         <v>204</v>
       </c>
     </row>
@@ -5521,1562 +5732,1562 @@
       <c r="A29" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="32" t="s">
+      <c r="C29" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="38" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="4"/>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="37" t="s">
         <v>206</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="37" t="s">
         <v>207</v>
       </c>
-      <c r="D30" s="31" t="s">
+      <c r="D30" s="37" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="4"/>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="D31" s="31" t="s">
+      <c r="D31" s="37" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="19" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="33"/>
-      <c r="B34" s="14" t="s">
+      <c r="A34" s="39"/>
+      <c r="B34" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="20" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="33"/>
-      <c r="B35" s="14" t="s">
+      <c r="A35" s="39"/>
+      <c r="B35" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="20" t="s">
         <v>217</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="20" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="38" ht="20.4" spans="1:4">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="40" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="19" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="41" ht="28.8" spans="1:4">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="20" t="s">
         <v>222</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="20" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="42" ht="28.8" spans="1:4">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="20" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="43" ht="28.8" spans="1:4">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B43" s="20" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B44" s="20" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="47" ht="15.6" spans="1:4">
-      <c r="A47" s="25" t="s">
+      <c r="A47" s="31" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="19" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="20" t="s">
         <v>233</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B50" s="20" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="14" t="s">
+      <c r="A51" s="20" t="s">
         <v>235</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B51" s="20" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B52" s="20" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B53" s="20" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="56" ht="20.4" spans="1:3">
-      <c r="A56" s="34" t="s">
+      <c r="A56" s="40" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="19" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="20" t="s">
         <v>245</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="20" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="B60" s="14" t="s">
+      <c r="B60" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="C60" s="14" t="s">
+      <c r="C60" s="20" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="B61" s="14" t="s">
+      <c r="B61" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="C61" s="14" t="s">
+      <c r="C61" s="20" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="65" ht="37.8" spans="1:8">
-      <c r="A65" s="34" t="s">
+      <c r="A65" s="40" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="67" ht="28.8" spans="1:8">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="C67" s="13" t="s">
+      <c r="C67" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="D67" s="13" t="s">
+      <c r="D67" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E67" s="13" t="s">
+      <c r="E67" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="F67" s="13" t="s">
+      <c r="F67" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="G67" s="13" t="s">
+      <c r="G67" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="H67" s="13" t="s">
+      <c r="H67" s="19" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="14">
+      <c r="A68" s="20">
         <v>1</v>
       </c>
-      <c r="B68" s="14" t="s">
+      <c r="B68" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="C68" s="14">
+      <c r="C68" s="20">
         <v>91</v>
       </c>
-      <c r="D68" s="14">
+      <c r="D68" s="20">
         <v>6</v>
       </c>
-      <c r="E68" s="35">
+      <c r="E68" s="41">
         <v>0.082</v>
       </c>
-      <c r="F68" s="14">
+      <c r="F68" s="20">
         <v>4</v>
       </c>
-      <c r="G68" s="36">
+      <c r="G68" s="42">
         <v>0.4</v>
       </c>
-      <c r="H68" s="14" t="s">
+      <c r="H68" s="20" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="14">
+      <c r="A69" s="20">
         <v>2</v>
       </c>
-      <c r="B69" s="14" t="s">
+      <c r="B69" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="C69" s="14">
+      <c r="C69" s="20">
         <v>88</v>
       </c>
-      <c r="D69" s="14">
+      <c r="D69" s="20">
         <v>8</v>
       </c>
-      <c r="E69" s="35">
+      <c r="E69" s="41">
         <v>0.075</v>
       </c>
-      <c r="F69" s="14">
+      <c r="F69" s="20">
         <v>3</v>
       </c>
-      <c r="G69" s="36">
+      <c r="G69" s="42">
         <v>0.25</v>
       </c>
-      <c r="H69" s="14" t="s">
+      <c r="H69" s="20" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="14">
+      <c r="A70" s="20">
         <v>3</v>
       </c>
-      <c r="B70" s="14" t="s">
+      <c r="B70" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="C70" s="14">
+      <c r="C70" s="20">
         <v>82</v>
       </c>
-      <c r="D70" s="14">
+      <c r="D70" s="20">
         <v>4</v>
       </c>
-      <c r="E70" s="35">
+      <c r="E70" s="41">
         <v>0.051</v>
       </c>
-      <c r="F70" s="14">
+      <c r="F70" s="20">
         <v>6</v>
       </c>
-      <c r="G70" s="36">
+      <c r="G70" s="42">
         <v>-0.3</v>
       </c>
-      <c r="H70" s="14" t="s">
+      <c r="H70" s="20" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="37"/>
+      <c r="A72" s="43"/>
     </row>
     <row r="73" ht="20.4" spans="1:8">
-      <c r="A73" s="38" t="s">
+      <c r="A73" s="44" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="76" ht="20.4" spans="1:8">
-      <c r="A76" s="34" t="s">
+      <c r="A76" s="40" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="B77" s="15" t="s">
+      <c r="B77" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="C77" s="15" t="s">
+      <c r="C77" s="21" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="16" t="s">
+      <c r="A78" s="22" t="s">
         <v>269</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B78" s="22" t="s">
         <v>270</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="22" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="16" t="s">
+      <c r="A79" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="22" t="s">
         <v>273</v>
       </c>
-      <c r="C79" s="16" t="s">
+      <c r="C79" s="22" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="16" t="s">
+      <c r="A80" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="B80" s="16" t="s">
+      <c r="B80" s="22" t="s">
         <v>276</v>
       </c>
-      <c r="C80" s="16" t="s">
+      <c r="C80" s="22" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="81" spans="1:5">
-      <c r="A81" s="16" t="s">
+      <c r="A81" s="22" t="s">
         <v>278</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B81" s="22" t="s">
         <v>279</v>
       </c>
-      <c r="C81" s="16" t="s">
+      <c r="C81" s="22" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="B82" s="16" t="s">
+      <c r="B82" s="22" t="s">
         <v>282</v>
       </c>
-      <c r="C82" s="16" t="s">
+      <c r="C82" s="22" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="83" spans="1:5">
-      <c r="A83" s="16" t="s">
+      <c r="A83" s="22" t="s">
         <v>284</v>
       </c>
-      <c r="B83" s="16" t="s">
+      <c r="B83" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="C83" s="16" t="s">
+      <c r="C83" s="22" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="84" spans="1:5">
-      <c r="A84" s="16" t="s">
+      <c r="A84" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="B84" s="16" t="s">
+      <c r="B84" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="22" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="87" ht="37.8" spans="1:5">
-      <c r="A87" s="34" t="s">
+      <c r="A87" s="40" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="89" spans="1:5">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="D89" s="13" t="s">
+      <c r="D89" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="E89" s="13" t="s">
+      <c r="E89" s="19" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="14">
+      <c r="A90" s="20">
         <v>1</v>
       </c>
-      <c r="B90" s="14" t="s">
+      <c r="B90" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="C90" s="14" t="s">
+      <c r="C90" s="20" t="s">
         <v>269</v>
       </c>
-      <c r="D90" s="14" t="s">
+      <c r="D90" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="E90" s="14" t="s">
+      <c r="E90" s="20" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="91" spans="1:5">
-      <c r="A91" s="14">
+      <c r="A91" s="20">
         <v>2</v>
       </c>
-      <c r="B91" s="14" t="s">
+      <c r="B91" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="C91" s="14" t="s">
+      <c r="C91" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D91" s="14" t="s">
+      <c r="D91" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="E91" s="14" t="s">
+      <c r="E91" s="20" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="92" spans="1:5">
-      <c r="A92" s="14">
+      <c r="A92" s="20">
         <v>3</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="D92" s="14" t="s">
+      <c r="D92" s="20" t="s">
         <v>302</v>
       </c>
-      <c r="E92" s="14" t="s">
+      <c r="E92" s="20" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="93" spans="1:5">
-      <c r="A93" s="14">
+      <c r="A93" s="20">
         <v>4</v>
       </c>
-      <c r="B93" s="14" t="s">
+      <c r="B93" s="20" t="s">
         <v>303</v>
       </c>
-      <c r="C93" s="14" t="s">
+      <c r="C93" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D93" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="E93" s="14" t="s">
+      <c r="E93" s="20" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="94" spans="1:5">
-      <c r="A94" s="14">
+      <c r="A94" s="20">
         <v>5</v>
       </c>
-      <c r="B94" s="14" t="s">
+      <c r="B94" s="20" t="s">
         <v>306</v>
       </c>
-      <c r="C94" s="14" t="s">
+      <c r="C94" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="D94" s="14" t="s">
+      <c r="D94" s="20" t="s">
         <v>307</v>
       </c>
-      <c r="E94" s="14" t="s">
+      <c r="E94" s="20" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="95" spans="1:5">
-      <c r="A95" s="14">
+      <c r="A95" s="20">
         <v>6</v>
       </c>
-      <c r="B95" s="14" t="s">
+      <c r="B95" s="20" t="s">
         <v>308</v>
       </c>
-      <c r="C95" s="14" t="s">
+      <c r="C95" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="D95" s="14" t="s">
+      <c r="D95" s="20" t="s">
         <v>309</v>
       </c>
-      <c r="E95" s="14" t="s">
+      <c r="E95" s="20" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="96" spans="1:5">
-      <c r="A96" s="14">
+      <c r="A96" s="20">
         <v>7</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" s="20" t="s">
         <v>310</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D96" s="14" t="s">
+      <c r="D96" s="20" t="s">
         <v>311</v>
       </c>
-      <c r="E96" s="14" t="s">
+      <c r="E96" s="20" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="14">
+      <c r="A97" s="20">
         <v>8</v>
       </c>
-      <c r="B97" s="14" t="s">
+      <c r="B97" s="20" t="s">
         <v>312</v>
       </c>
-      <c r="C97" s="14" t="s">
+      <c r="C97" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="D97" s="14" t="s">
+      <c r="D97" s="20" t="s">
         <v>313</v>
       </c>
-      <c r="E97" s="14" t="s">
+      <c r="E97" s="20" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="98" spans="1:5">
-      <c r="A98" s="14">
+      <c r="A98" s="20">
         <v>9</v>
       </c>
-      <c r="B98" s="14" t="s">
+      <c r="B98" s="20" t="s">
         <v>314</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="D98" s="14" t="s">
+      <c r="D98" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="E98" s="14" t="s">
+      <c r="E98" s="20" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="99" spans="1:5">
-      <c r="A99" s="14">
+      <c r="A99" s="20">
         <v>10</v>
       </c>
-      <c r="B99" s="14" t="s">
+      <c r="B99" s="20" t="s">
         <v>316</v>
       </c>
-      <c r="C99" s="14" t="s">
+      <c r="C99" s="20" t="s">
         <v>317</v>
       </c>
-      <c r="D99" s="14" t="s">
+      <c r="D99" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="E99" s="14" t="s">
+      <c r="E99" s="20" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="100" spans="1:5">
-      <c r="A100" s="14">
+      <c r="A100" s="20">
         <v>11</v>
       </c>
-      <c r="B100" s="14" t="s">
+      <c r="B100" s="20" t="s">
         <v>319</v>
       </c>
-      <c r="C100" s="14" t="s">
+      <c r="C100" s="20" t="s">
         <v>275</v>
       </c>
-      <c r="D100" s="14" t="s">
+      <c r="D100" s="20" t="s">
         <v>320</v>
       </c>
-      <c r="E100" s="14" t="s">
+      <c r="E100" s="20" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="101" spans="1:5">
-      <c r="A101" s="14">
+      <c r="A101" s="20">
         <v>12</v>
       </c>
-      <c r="B101" s="14" t="s">
+      <c r="B101" s="20" t="s">
         <v>322</v>
       </c>
-      <c r="C101" s="14" t="s">
+      <c r="C101" s="20" t="s">
         <v>278</v>
       </c>
-      <c r="D101" s="14" t="s">
+      <c r="D101" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="E101" s="14" t="s">
+      <c r="E101" s="20" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="103" ht="20.4" spans="1:5">
-      <c r="A103" s="34" t="s">
+      <c r="A103" s="40" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="104" ht="19.2" spans="1:5">
-      <c r="A104" s="39" t="s">
+      <c r="A104" s="45" t="s">
         <v>325</v>
       </c>
       <c r="B104" s="3"/>
     </row>
     <row r="105" spans="1:5">
-      <c r="A105" s="15" t="s">
+      <c r="A105" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="21" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="106" spans="1:5">
-      <c r="A106" s="16" t="s">
+      <c r="A106" s="22" t="s">
         <v>327</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B106" s="22" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="107" spans="1:5">
-      <c r="A107" s="16" t="s">
+      <c r="A107" s="22" t="s">
         <v>329</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="22" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="108" spans="1:5">
-      <c r="A108" s="16" t="s">
+      <c r="A108" s="22" t="s">
         <v>331</v>
       </c>
-      <c r="B108" s="16" t="s">
+      <c r="B108" s="22" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="109" spans="1:5">
-      <c r="A109" s="16" t="s">
+      <c r="A109" s="22" t="s">
         <v>333</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B109" s="22" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="110" spans="1:5">
-      <c r="A110" s="16" t="s">
+      <c r="A110" s="22" t="s">
         <v>335</v>
       </c>
-      <c r="B110" s="16" t="s">
+      <c r="B110" s="22" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="111" spans="1:5">
-      <c r="A111" s="16" t="s">
+      <c r="A111" s="22" t="s">
         <v>337</v>
       </c>
-      <c r="B111" s="16" t="s">
+      <c r="B111" s="22" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="112" spans="1:5">
-      <c r="A112" s="16" t="s">
+      <c r="A112" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="B112" s="16" t="s">
+      <c r="B112" s="22" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="16" t="s">
+      <c r="A113" s="22" t="s">
         <v>341</v>
       </c>
-      <c r="B113" s="16" t="s">
+      <c r="B113" s="22" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="114" spans="1:2">
-      <c r="A114" s="16" t="s">
+      <c r="A114" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="B114" s="16" t="s">
+      <c r="B114" s="22" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="16" t="s">
+      <c r="A115" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="B115" s="16" t="s">
+      <c r="B115" s="22" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="116" spans="1:2">
-      <c r="A116" s="16" t="s">
+      <c r="A116" s="22" t="s">
         <v>347</v>
       </c>
-      <c r="B116" s="16" t="s">
+      <c r="B116" s="22" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="16" t="s">
+      <c r="A117" s="22" t="s">
         <v>349</v>
       </c>
-      <c r="B117" s="16" t="s">
+      <c r="B117" s="22" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="119" ht="19.2" spans="1:2">
-      <c r="A119" s="40" t="s">
+      <c r="A119" s="46" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="41" t="s">
+      <c r="A121" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="B121" s="41" t="s">
+      <c r="B121" s="47" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="122" spans="1:2">
-      <c r="A122" s="16" t="s">
+      <c r="A122" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="B122" s="16" t="s">
+      <c r="B122" s="22" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="16" t="s">
+      <c r="A123" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="B123" s="16" t="s">
+      <c r="B123" s="22" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="16" t="s">
+      <c r="A124" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="B124" s="16" t="s">
+      <c r="B124" s="22" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="16" t="s">
+      <c r="A125" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="B125" s="16" t="s">
+      <c r="B125" s="22" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" s="16" t="s">
+      <c r="A126" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="B126" s="16" t="s">
+      <c r="B126" s="22" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="16" t="s">
+      <c r="A127" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="B127" s="16" t="s">
+      <c r="B127" s="22" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="128" spans="1:2">
-      <c r="A128" s="16" t="s">
+      <c r="A128" s="22" t="s">
         <v>358</v>
       </c>
-      <c r="B128" s="16" t="s">
+      <c r="B128" s="22" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="16" t="s">
+      <c r="A129" s="22" t="s">
         <v>360</v>
       </c>
-      <c r="B129" s="16" t="s">
+      <c r="B129" s="22" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="131" ht="19.2" spans="1:2">
-      <c r="A131" s="40" t="s">
+      <c r="A131" s="46" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="41" t="s">
+      <c r="A133" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="B133" s="41" t="s">
+      <c r="B133" s="47" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="134" spans="1:2">
-      <c r="A134" s="16" t="s">
+      <c r="A134" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="B134" s="16" t="s">
+      <c r="B134" s="22" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="16" t="s">
+      <c r="A135" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="B135" s="16" t="s">
+      <c r="B135" s="22" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="136" spans="1:2">
-      <c r="A136" s="16" t="s">
+      <c r="A136" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="B136" s="16" t="s">
+      <c r="B136" s="22" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="16" t="s">
+      <c r="A137" s="22" t="s">
         <v>339</v>
       </c>
-      <c r="B137" s="16" t="s">
+      <c r="B137" s="22" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="138" spans="1:2">
-      <c r="A138" s="16" t="s">
+      <c r="A138" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="B138" s="16" t="s">
+      <c r="B138" s="22" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="16" t="s">
+      <c r="A139" s="22" t="s">
         <v>345</v>
       </c>
-      <c r="B139" s="16" t="s">
+      <c r="B139" s="22" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="140" spans="1:2">
-      <c r="A140" s="16" t="s">
+      <c r="A140" s="22" t="s">
         <v>358</v>
       </c>
-      <c r="B140" s="16" t="s">
+      <c r="B140" s="22" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="16" t="s">
+      <c r="A141" s="22" t="s">
         <v>360</v>
       </c>
-      <c r="B141" s="16" t="s">
+      <c r="B141" s="22" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="143" ht="19.2" spans="1:2">
-      <c r="A143" s="40" t="s">
+      <c r="A143" s="46" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="41" t="s">
+      <c r="A145" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="B145" s="41" t="s">
+      <c r="B145" s="47" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:2">
-      <c r="A146" s="16" t="s">
+      <c r="A146" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="B146" s="16" t="s">
+      <c r="B146" s="22" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="16" t="s">
+      <c r="A147" s="22" t="s">
         <v>364</v>
       </c>
-      <c r="B147" s="16" t="s">
+      <c r="B147" s="22" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="148" spans="1:2">
-      <c r="A148" s="16" t="s">
+      <c r="A148" s="22" t="s">
         <v>366</v>
       </c>
-      <c r="B148" s="16" t="s">
+      <c r="B148" s="22" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="16" t="s">
+      <c r="A149" s="22" t="s">
         <v>368</v>
       </c>
-      <c r="B149" s="16" t="s">
+      <c r="B149" s="22" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="150" spans="1:2">
-      <c r="A150" s="16" t="s">
+      <c r="A150" s="22" t="s">
         <v>370</v>
       </c>
-      <c r="B150" s="16" t="s">
+      <c r="B150" s="22" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="16" t="s">
+      <c r="A151" s="22" t="s">
         <v>372</v>
       </c>
-      <c r="B151" s="16" t="s">
+      <c r="B151" s="22" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="152" spans="1:2">
-      <c r="A152" s="16" t="s">
+      <c r="A152" s="22" t="s">
         <v>374</v>
       </c>
-      <c r="B152" s="16" t="s">
+      <c r="B152" s="22" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="154" ht="19.2" spans="1:2">
-      <c r="A154" s="40" t="s">
+      <c r="A154" s="46" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="156" spans="1:2">
-      <c r="A156" s="41" t="s">
+      <c r="A156" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="B156" s="41" t="s">
+      <c r="B156" s="47" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="42" t="s">
+      <c r="A157" s="48" t="s">
         <v>329</v>
       </c>
-      <c r="B157" s="42" t="s">
+      <c r="B157" s="48" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="158" spans="1:2">
-      <c r="A158" s="42" t="s">
+      <c r="A158" s="48" t="s">
         <v>377</v>
       </c>
-      <c r="B158" s="42" t="s">
+      <c r="B158" s="48" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="42" t="s">
+      <c r="A159" s="48" t="s">
         <v>379</v>
       </c>
-      <c r="B159" s="42" t="s">
+      <c r="B159" s="48" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="42" t="s">
+      <c r="A160" s="48" t="s">
         <v>381</v>
       </c>
-      <c r="B160" s="42" t="s">
+      <c r="B160" s="48" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="161" spans="1:4">
-      <c r="A161" s="42" t="s">
+      <c r="A161" s="48" t="s">
         <v>383</v>
       </c>
-      <c r="B161" s="42" t="s">
+      <c r="B161" s="48" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="162" spans="1:4">
-      <c r="A162" s="42" t="s">
+      <c r="A162" s="48" t="s">
         <v>385</v>
       </c>
-      <c r="B162" s="42" t="s">
+      <c r="B162" s="48" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="165" ht="19.2" spans="1:4">
-      <c r="A165" s="40" t="s">
+      <c r="A165" s="46" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="167" spans="1:4">
-      <c r="A167" s="41" t="s">
+      <c r="A167" s="47" t="s">
         <v>326</v>
       </c>
-      <c r="B167" s="41" t="s">
+      <c r="B167" s="47" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="168" spans="1:4">
-      <c r="A168" s="42" t="s">
+      <c r="A168" s="48" t="s">
         <v>352</v>
       </c>
-      <c r="B168" s="42" t="s">
+      <c r="B168" s="48" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="169" spans="1:4">
-      <c r="A169" s="42" t="s">
+      <c r="A169" s="48" t="s">
         <v>388</v>
       </c>
-      <c r="B169" s="42" t="s">
+      <c r="B169" s="48" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="170" spans="1:4">
-      <c r="A170" s="42" t="s">
+      <c r="A170" s="48" t="s">
         <v>390</v>
       </c>
-      <c r="B170" s="42" t="s">
+      <c r="B170" s="48" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="171" spans="1:4">
-      <c r="A171" s="42" t="s">
+      <c r="A171" s="48" t="s">
         <v>392</v>
       </c>
-      <c r="B171" s="42" t="s">
+      <c r="B171" s="48" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="172" spans="1:4">
-      <c r="A172" s="42" t="s">
+      <c r="A172" s="48" t="s">
         <v>394</v>
       </c>
-      <c r="B172" s="42" t="s">
+      <c r="B172" s="48" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="174" ht="20.4" spans="1:4">
-      <c r="A174" s="34" t="s">
+      <c r="A174" s="40" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="176" spans="1:4">
-      <c r="A176" s="13" t="s">
+      <c r="A176" s="19" t="s">
         <v>397</v>
       </c>
-      <c r="B176" s="13" t="s">
+      <c r="B176" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="C176" s="13" t="s">
+      <c r="C176" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="D176" s="13" t="s">
+      <c r="D176" s="19" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="177" spans="1:4">
-      <c r="A177" s="43" t="s">
+      <c r="A177" s="49" t="s">
         <v>401</v>
       </c>
-      <c r="B177" s="14" t="s">
+      <c r="B177" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="C177" s="14" t="s">
+      <c r="C177" s="20" t="s">
         <v>403</v>
       </c>
-      <c r="D177" s="14" t="s">
+      <c r="D177" s="20" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="178" spans="1:4">
-      <c r="A178" s="44"/>
-      <c r="B178" s="14" t="s">
+      <c r="A178" s="50"/>
+      <c r="B178" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C178" s="14" t="s">
+      <c r="C178" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="D178" s="14" t="s">
+      <c r="D178" s="20" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="179" spans="1:4">
-      <c r="A179" s="45"/>
-      <c r="B179" s="14" t="s">
+      <c r="A179" s="51"/>
+      <c r="B179" s="20" t="s">
         <v>405</v>
       </c>
-      <c r="C179" s="14" t="s">
+      <c r="C179" s="20" t="s">
         <v>406</v>
       </c>
-      <c r="D179" s="14" t="s">
+      <c r="D179" s="20" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="180" spans="1:4">
-      <c r="A180" s="43" t="s">
+      <c r="A180" s="49" t="s">
         <v>407</v>
       </c>
-      <c r="B180" s="14" t="s">
+      <c r="B180" s="20" t="s">
         <v>408</v>
       </c>
-      <c r="C180" s="14" t="s">
+      <c r="C180" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="D180" s="14" t="s">
+      <c r="D180" s="20" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="181" spans="1:4">
-      <c r="A181" s="44"/>
-      <c r="B181" s="14" t="s">
+      <c r="A181" s="50"/>
+      <c r="B181" s="20" t="s">
         <v>410</v>
       </c>
-      <c r="C181" s="14" t="s">
+      <c r="C181" s="20" t="s">
         <v>411</v>
       </c>
-      <c r="D181" s="14" t="s">
+      <c r="D181" s="20" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="182" spans="1:4">
-      <c r="A182" s="44"/>
-      <c r="B182" s="14" t="s">
+      <c r="A182" s="50"/>
+      <c r="B182" s="20" t="s">
         <v>412</v>
       </c>
-      <c r="C182" s="14" t="s">
+      <c r="C182" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="D182" s="14" t="s">
+      <c r="D182" s="20" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="183" spans="1:4">
-      <c r="A183" s="45"/>
-      <c r="B183" s="14" t="s">
+      <c r="A183" s="51"/>
+      <c r="B183" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C183" s="14" t="s">
+      <c r="C183" s="20" t="s">
         <v>414</v>
       </c>
-      <c r="D183" s="14" t="s">
+      <c r="D183" s="20" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="184" ht="28.8" spans="1:4">
-      <c r="A184" s="43" t="s">
+      <c r="A184" s="49" t="s">
         <v>415</v>
       </c>
-      <c r="B184" s="14" t="s">
+      <c r="B184" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="C184" s="14" t="s">
+      <c r="C184" s="20" t="s">
         <v>416</v>
       </c>
-      <c r="D184" s="14" t="s">
+      <c r="D184" s="20" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="185" spans="1:4">
-      <c r="A185" s="44"/>
-      <c r="B185" s="14" t="s">
+      <c r="A185" s="50"/>
+      <c r="B185" s="20" t="s">
         <v>418</v>
       </c>
-      <c r="C185" s="14" t="s">
+      <c r="C185" s="20" t="s">
         <v>419</v>
       </c>
-      <c r="D185" s="14" t="s">
+      <c r="D185" s="20" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="186" spans="1:4">
-      <c r="A186" s="45"/>
-      <c r="B186" s="14" t="s">
+      <c r="A186" s="51"/>
+      <c r="B186" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="C186" s="14" t="s">
+      <c r="C186" s="20" t="s">
         <v>421</v>
       </c>
-      <c r="D186" s="14" t="s">
+      <c r="D186" s="20" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="187" spans="1:4">
-      <c r="A187" s="43" t="s">
+      <c r="A187" s="49" t="s">
         <v>422</v>
       </c>
-      <c r="B187" s="14" t="s">
+      <c r="B187" s="20" t="s">
         <v>423</v>
       </c>
-      <c r="C187" s="14" t="s">
+      <c r="C187" s="20" t="s">
         <v>424</v>
       </c>
-      <c r="D187" s="14" t="s">
+      <c r="D187" s="20" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="188" spans="1:4">
-      <c r="A188" s="44"/>
-      <c r="B188" s="14" t="s">
+      <c r="A188" s="50"/>
+      <c r="B188" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="C188" s="14" t="s">
+      <c r="C188" s="20" t="s">
         <v>426</v>
       </c>
-      <c r="D188" s="14" t="s">
+      <c r="D188" s="20" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="189" spans="1:4">
-      <c r="A189" s="45"/>
-      <c r="B189" s="14" t="s">
+      <c r="A189" s="51"/>
+      <c r="B189" s="20" t="s">
         <v>427</v>
       </c>
-      <c r="C189" s="14" t="s">
+      <c r="C189" s="20" t="s">
         <v>428</v>
       </c>
-      <c r="D189" s="14" t="s">
+      <c r="D189" s="20" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="191" ht="20.4" spans="1:4">
-      <c r="A191" s="34" t="s">
+      <c r="A191" s="40" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="193" ht="43.2" spans="1:9">
-      <c r="A193" s="13" t="s">
+      <c r="A193" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="B193" s="13" t="s">
+      <c r="B193" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="C193" s="13" t="s">
+      <c r="C193" s="19" t="s">
         <v>430</v>
       </c>
-      <c r="D193" s="13" t="s">
+      <c r="D193" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="E193" s="13" t="s">
+      <c r="E193" s="19" t="s">
         <v>432</v>
       </c>
-      <c r="F193" s="13" t="s">
+      <c r="F193" s="19" t="s">
         <v>433</v>
       </c>
-      <c r="G193" s="13" t="s">
+      <c r="G193" s="19" t="s">
         <v>434</v>
       </c>
-      <c r="H193" s="13" t="s">
+      <c r="H193" s="19" t="s">
         <v>435</v>
       </c>
-      <c r="I193" s="13" t="s">
+      <c r="I193" s="19" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194" s="14">
+      <c r="A194" s="20">
         <v>1</v>
       </c>
-      <c r="B194" s="14" t="s">
+      <c r="B194" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="C194" s="14">
+      <c r="C194" s="20">
         <v>92</v>
       </c>
-      <c r="D194" s="14">
+      <c r="D194" s="20">
         <v>88</v>
       </c>
-      <c r="E194" s="14">
+      <c r="E194" s="20">
         <v>85</v>
       </c>
-      <c r="F194" s="14">
+      <c r="F194" s="20">
         <v>90</v>
       </c>
-      <c r="G194" s="14">
+      <c r="G194" s="20">
         <v>87</v>
       </c>
-      <c r="H194" s="14">
+      <c r="H194" s="20">
         <v>89</v>
       </c>
-      <c r="I194" s="14" t="s">
+      <c r="I194" s="20" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="195" spans="1:9">
-      <c r="A195" s="14">
+      <c r="A195" s="20">
         <v>2</v>
       </c>
-      <c r="B195" s="14" t="s">
+      <c r="B195" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="C195" s="14">
+      <c r="C195" s="20">
         <v>90</v>
       </c>
-      <c r="D195" s="14">
+      <c r="D195" s="20">
         <v>91</v>
       </c>
-      <c r="E195" s="14">
+      <c r="E195" s="20">
         <v>82</v>
       </c>
-      <c r="F195" s="14">
+      <c r="F195" s="20">
         <v>86</v>
       </c>
-      <c r="G195" s="14">
+      <c r="G195" s="20">
         <v>85</v>
       </c>
-      <c r="H195" s="14">
+      <c r="H195" s="20">
         <v>88.1</v>
       </c>
-      <c r="I195" s="14" t="s">
+      <c r="I195" s="20" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="196" spans="1:9">
-      <c r="A196" s="14">
+      <c r="A196" s="20">
         <v>3</v>
       </c>
-      <c r="B196" s="14" t="s">
+      <c r="B196" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="C196" s="14">
+      <c r="C196" s="20">
         <v>75</v>
       </c>
-      <c r="D196" s="14">
+      <c r="D196" s="20">
         <v>70</v>
       </c>
-      <c r="E196" s="14">
+      <c r="E196" s="20">
         <v>60</v>
       </c>
-      <c r="F196" s="14">
+      <c r="F196" s="20">
         <v>80</v>
       </c>
-      <c r="G196" s="14">
+      <c r="G196" s="20">
         <v>65</v>
       </c>
-      <c r="H196" s="14">
+      <c r="H196" s="20">
         <v>72</v>
       </c>
-      <c r="I196" s="14" t="s">
+      <c r="I196" s="20" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="197" spans="1:9">
-      <c r="A197" s="14">
+      <c r="A197" s="20">
         <v>4</v>
       </c>
-      <c r="B197" s="14" t="s">
+      <c r="B197" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="C197" s="14">
+      <c r="C197" s="20">
         <v>40</v>
       </c>
-      <c r="D197" s="14">
+      <c r="D197" s="20">
         <v>35</v>
       </c>
-      <c r="E197" s="14">
+      <c r="E197" s="20">
         <v>20</v>
       </c>
-      <c r="F197" s="14">
+      <c r="F197" s="20">
         <v>50</v>
       </c>
-      <c r="G197" s="14">
+      <c r="G197" s="20">
         <v>30</v>
       </c>
-      <c r="H197" s="14">
+      <c r="H197" s="20">
         <v>36.5</v>
       </c>
-      <c r="I197" s="14" t="s">
+      <c r="I197" s="20" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="200" ht="20.4" spans="1:9">
-      <c r="A200" s="34" t="s">
+      <c r="A200" s="40" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="202" ht="15.6" spans="1:9">
-      <c r="A202" s="39" t="s">
+      <c r="A202" s="45" t="s">
         <v>438</v>
       </c>
       <c r="B202" s="3"/>
     </row>
     <row r="203" spans="1:9">
-      <c r="A203" s="15" t="s">
+      <c r="A203" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="B203" s="15" t="s">
+      <c r="B203" s="21" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="204" spans="1:9">
-      <c r="A204" s="16" t="s">
+      <c r="A204" s="22" t="s">
         <v>298</v>
       </c>
-      <c r="B204" s="16" t="s">
+      <c r="B204" s="22" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="205" spans="1:9">
-      <c r="A205" s="16" t="s">
+      <c r="A205" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="B205" s="16" t="s">
+      <c r="B205" s="22" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="206" spans="1:9">
-      <c r="A206" s="16" t="s">
+      <c r="A206" s="22" t="s">
         <v>321</v>
       </c>
-      <c r="B206" s="16" t="s">
+      <c r="B206" s="22" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="208" ht="15.6" spans="1:9">
-      <c r="A208" s="39" t="s">
+      <c r="A208" s="45" t="s">
         <v>442</v>
       </c>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
     </row>
     <row r="209" spans="1:3">
-      <c r="A209" s="15" t="s">
+      <c r="A209" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="B209" s="15" t="s">
+      <c r="B209" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="C209" s="15" t="s">
+      <c r="C209" s="21" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="210" spans="1:3">
-      <c r="A210" s="16" t="s">
+      <c r="A210" s="22" t="s">
         <v>446</v>
       </c>
-      <c r="B210" s="16" t="s">
+      <c r="B210" s="22" t="s">
         <v>447</v>
       </c>
-      <c r="C210" s="16" t="s">
+      <c r="C210" s="22" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="211" spans="1:3">
-      <c r="A211" s="16" t="s">
+      <c r="A211" s="22" t="s">
         <v>449</v>
       </c>
-      <c r="B211" s="16" t="s">
+      <c r="B211" s="22" t="s">
         <v>450</v>
       </c>
-      <c r="C211" s="16" t="s">
+      <c r="C211" s="22" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:3">
-      <c r="A212" s="16" t="s">
+      <c r="A212" s="22" t="s">
         <v>452</v>
       </c>
-      <c r="B212" s="16" t="s">
+      <c r="B212" s="22" t="s">
         <v>453</v>
       </c>
-      <c r="C212" s="16" t="s">
+      <c r="C212" s="22" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:3">
-      <c r="A213" s="16" t="s">
+      <c r="A213" s="22" t="s">
         <v>455</v>
       </c>
-      <c r="B213" s="16" t="s">
+      <c r="B213" s="22" t="s">
         <v>456</v>
       </c>
-      <c r="C213" s="16" t="s">
+      <c r="C213" s="22" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="214" spans="1:3">
-      <c r="A214" s="16" t="s">
+      <c r="A214" s="22" t="s">
         <v>458</v>
       </c>
-      <c r="B214" s="16" t="s">
+      <c r="B214" s="22" t="s">
         <v>459</v>
       </c>
-      <c r="C214" s="16" t="s">
+      <c r="C214" s="22" t="s">
         <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="16" t="s">
+      <c r="A215" s="22" t="s">
         <v>461</v>
       </c>
-      <c r="B215" s="16" t="s">
+      <c r="B215" s="22" t="s">
         <v>462</v>
       </c>
-      <c r="C215" s="16" t="s">
+      <c r="C215" s="22" t="s">
         <v>463</v>
       </c>
     </row>
@@ -7145,285 +7356,285 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="13" t="s">
         <v>468</v>
       </c>
-      <c r="B1" s="8"/>
+      <c r="B1" s="14"/>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="15" t="s">
         <v>469</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="15" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="16" t="s">
         <v>471</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="16" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="16" t="s">
         <v>473</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="16" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="16" t="s">
         <v>475</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="16" t="s">
         <v>476</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="16" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="16" t="s">
         <v>479</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="16" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="17" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="11" ht="20.4" spans="1:3">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="18" t="s">
         <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="19" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="20" t="s">
         <v>485</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="20" t="s">
         <v>486</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="20" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="20" t="s">
         <v>488</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="20" t="s">
         <v>489</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="20" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="16" ht="28.8" spans="1:3">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="20" t="s">
         <v>491</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="20" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="20" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="20" t="s">
         <v>494</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="20" t="s">
         <v>495</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="20" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="19" ht="20.4" spans="1:3">
-      <c r="A19" s="12" t="s">
+      <c r="A19" s="18" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="21" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:3">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="22" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="23" spans="1:3">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="22" t="s">
         <v>500</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="22" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="24" ht="28.8" spans="1:3">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="22" t="s">
         <v>502</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="22" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="25" spans="1:3">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="22" t="s">
         <v>504</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="22" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="27" ht="20.4" spans="1:3">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="18" t="s">
         <v>506</v>
       </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="19" t="s">
         <v>326</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="19" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="20" t="s">
         <v>507</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="20" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="31" spans="1:3">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="20" t="s">
         <v>509</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="20" t="s">
         <v>510</v>
       </c>
     </row>
     <row r="32" spans="1:3">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="20" t="s">
         <v>511</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="20" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="20" t="s">
         <v>513</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" s="20" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="35" ht="20.4" spans="1:2">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="18" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="21" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="22" t="s">
         <v>516</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="22" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="16" t="s">
+      <c r="A39" s="22" t="s">
         <v>518</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="22" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="22" t="s">
         <v>520</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="22" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="43" ht="20.4" spans="1:2">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="18" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="B45" s="21" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="16" t="s">
+      <c r="A46" s="22" t="s">
         <v>524</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="22" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="22" t="s">
         <v>526</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="22" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="16" t="s">
+      <c r="A48" s="22" t="s">
         <v>528</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="22" t="s">
         <v>529</v>
       </c>
     </row>
@@ -7433,148 +7644,148 @@
       </c>
     </row>
     <row r="53" ht="16.8" spans="1:2">
-      <c r="A53" s="17" t="s">
+      <c r="A53" s="23" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="56" ht="27" spans="1:2">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="17" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="15" t="s">
+      <c r="A58" s="21" t="s">
         <v>533</v>
       </c>
-      <c r="B58" s="15" t="s">
+      <c r="B58" s="21" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="22" t="s">
         <v>535</v>
       </c>
-      <c r="B59" s="16" t="s">
+      <c r="B59" s="22" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="16"/>
-      <c r="B60" s="16" t="s">
+      <c r="A60" s="22"/>
+      <c r="B60" s="22" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="16"/>
-      <c r="B61" s="16" t="s">
+      <c r="A61" s="22"/>
+      <c r="B61" s="22" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="16"/>
-      <c r="B62" s="16" t="s">
+      <c r="A62" s="22"/>
+      <c r="B62" s="22" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="16"/>
-      <c r="B63" s="16" t="s">
+      <c r="A63" s="22"/>
+      <c r="B63" s="22" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="16" t="s">
+      <c r="A64" s="22" t="s">
         <v>541</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="22" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="16"/>
-      <c r="B65" s="16" t="s">
+      <c r="A65" s="22"/>
+      <c r="B65" s="22" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="16"/>
-      <c r="B66" s="16" t="s">
+      <c r="A66" s="22"/>
+      <c r="B66" s="22" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="16"/>
-      <c r="B67" s="16" t="s">
+      <c r="A67" s="22"/>
+      <c r="B67" s="22" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="70" ht="22.2" spans="1:2">
-      <c r="A70" s="18" t="s">
+      <c r="A70" s="24" t="s">
         <v>546</v>
       </c>
     </row>
     <row r="72" ht="15.6" spans="1:2">
-      <c r="A72" s="19" t="s">
+      <c r="A72" s="25" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="74" ht="19.2" spans="1:2">
-      <c r="A74" s="20" t="s">
+      <c r="A74" s="26" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="75" ht="19.2" spans="1:2">
-      <c r="A75" s="20" t="s">
+      <c r="A75" s="26" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="76" ht="15.6" spans="1:2">
-      <c r="A76" s="20" t="s">
+      <c r="A76" s="26" t="s">
         <v>550</v>
       </c>
     </row>
     <row r="80" spans="1:2">
-      <c r="A80" s="21" t="s">
+      <c r="A80" s="27" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="82" spans="1:2">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="19" t="s">
         <v>552</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="19" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="14" t="s">
+      <c r="A83" s="20" t="s">
         <v>554</v>
       </c>
-      <c r="B83" s="14" t="s">
+      <c r="B83" s="20" t="s">
         <v>555</v>
       </c>
     </row>
     <row r="84" spans="1:2">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="B84" s="14" t="s">
+      <c r="B84" s="20" t="s">
         <v>557</v>
       </c>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="20" t="s">
         <v>558</v>
       </c>
-      <c r="B85" s="14" t="s">
+      <c r="B85" s="20" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="86" spans="1:2">
-      <c r="A86" s="14" t="s">
+      <c r="A86" s="20" t="s">
         <v>560</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" s="20" t="s">
         <v>561</v>
       </c>
     </row>
@@ -7591,7 +7802,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:I63"/>
+  <dimension ref="B2:I88"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="3" width="32.1111111111111" customWidth="1"/>
@@ -7601,7 +7812,7 @@
     <col min="7" max="7" width="37.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9">
+    <row r="2" customHeight="1" spans="2:9">
       <c r="B2" s="3" t="s">
         <v>562</v>
       </c>
@@ -7669,7 +7880,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="2:9">
+    <row r="6" customHeight="1" spans="2:9">
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -7695,7 +7906,7 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" customHeight="1" spans="2:9">
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -7733,7 +7944,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="2:9">
+    <row r="11" customHeight="1" spans="2:9">
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -7769,7 +7980,7 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" customHeight="1" spans="2:9">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -7795,7 +8006,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="2:9">
+    <row r="16" customHeight="1" spans="2:9">
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -7831,7 +8042,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" customHeight="1" spans="2:9">
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5" t="s">
@@ -8397,12 +8608,228 @@
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
     </row>
+    <row r="70" ht="15.15"/>
+    <row r="71" ht="16.35" spans="2:5">
+      <c r="B71" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="72" ht="15.15" spans="2:5">
+      <c r="B72" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="73" ht="15.15" spans="2:5">
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="74" ht="15.15" spans="2:5">
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="75" ht="15.15" spans="2:5">
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="76" ht="15.15" spans="2:5">
+      <c r="B76" s="8"/>
+      <c r="C76" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="77" ht="29.55" spans="2:5">
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="78" ht="15.15" spans="2:5">
+      <c r="B78" s="11" t="s">
+        <v>669</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="79" ht="15.15" spans="2:5">
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="80" ht="15.15" spans="2:5">
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="81" ht="15.15" spans="2:5">
+      <c r="B81" s="11"/>
+      <c r="C81" s="11" t="s">
+        <v>677</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="82" ht="15.15" spans="2:5">
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="83" ht="15.15" spans="2:5">
+      <c r="B83" s="11"/>
+      <c r="C83" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="84" ht="15.15" spans="2:5">
+      <c r="B84" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>686</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>687</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="85" ht="15.15" spans="2:5">
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="86" ht="29.55" spans="2:5">
+      <c r="B86" s="12"/>
+      <c r="C86" s="12" t="s">
+        <v>691</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="87" ht="15.15" spans="2:5">
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="88" ht="15.15" spans="2:5">
+      <c r="B88" s="12"/>
+      <c r="C88" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>697</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>698</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="28">
     <mergeCell ref="B3:B63"/>
+    <mergeCell ref="B72:B77"/>
+    <mergeCell ref="B78:B83"/>
+    <mergeCell ref="B84:B88"/>
     <mergeCell ref="C3:C20"/>
     <mergeCell ref="C21:C37"/>
     <mergeCell ref="C38:C63"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="C76:C77"/>
+    <mergeCell ref="C78:C80"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="C86:C87"/>
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="D10:D14"/>
@@ -8432,117 +8859,117 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>650</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>651</v>
+        <v>700</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>652</v>
+        <v>701</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>653</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>654</v>
+        <v>703</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>655</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>656</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>657</v>
+        <v>706</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>658</v>
+        <v>707</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>659</v>
+        <v>708</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>660</v>
+        <v>709</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>661</v>
+        <v>710</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>662</v>
+        <v>711</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>663</v>
+        <v>712</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>664</v>
+        <v>713</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>665</v>
+        <v>714</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>666</v>
+        <v>715</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>667</v>
+        <v>716</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>668</v>
+        <v>717</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>669</v>
+        <v>718</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>670</v>
+        <v>719</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>671</v>
+        <v>720</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>672</v>
+        <v>721</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -8552,12 +8979,12 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>673</v>
+        <v>722</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>674</v>
+        <v>723</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -8573,7 +9000,7 @@
         <v>332</v>
       </c>
       <c r="B37" t="s">
-        <v>675</v>
+        <v>724</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -8581,7 +9008,7 @@
         <v>342</v>
       </c>
       <c r="B38" t="s">
-        <v>676</v>
+        <v>725</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -8589,7 +9016,7 @@
         <v>344</v>
       </c>
       <c r="B39" t="s">
-        <v>677</v>
+        <v>726</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -8597,7 +9024,7 @@
         <v>346</v>
       </c>
       <c r="B40" t="s">
-        <v>678</v>
+        <v>727</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -8605,59 +9032,59 @@
         <v>340</v>
       </c>
       <c r="B41" t="s">
-        <v>679</v>
+        <v>728</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>680</v>
+        <v>729</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>681</v>
+        <v>730</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>682</v>
+        <v>731</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>683</v>
+        <v>732</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>684</v>
+        <v>733</v>
       </c>
       <c r="B48" t="s">
-        <v>685</v>
+        <v>734</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>686</v>
+        <v>735</v>
       </c>
       <c r="B49" t="s">
-        <v>687</v>
+        <v>736</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>688</v>
+        <v>737</v>
       </c>
       <c r="B50" t="s">
-        <v>689</v>
+        <v>738</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>690</v>
+        <v>739</v>
       </c>
       <c r="B51" t="s">
-        <v>691</v>
+        <v>740</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -8665,123 +9092,123 @@
         <v>46056</v>
       </c>
       <c r="B52" t="s">
-        <v>692</v>
+        <v>741</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>693</v>
+        <v>742</v>
       </c>
       <c r="B53" t="s">
-        <v>694</v>
+        <v>743</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>695</v>
+        <v>744</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>696</v>
+        <v>745</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>697</v>
+        <v>746</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>698</v>
+        <v>747</v>
       </c>
       <c r="B59" t="s">
         <v>342</v>
       </c>
       <c r="C59" t="s">
-        <v>699</v>
+        <v>748</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>700</v>
+        <v>749</v>
       </c>
       <c r="B60" t="s">
-        <v>700</v>
+        <v>749</v>
       </c>
       <c r="C60" t="s">
-        <v>701</v>
+        <v>750</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>700</v>
+        <v>749</v>
       </c>
       <c r="B61" t="s">
-        <v>702</v>
+        <v>751</v>
       </c>
       <c r="C61" t="s">
-        <v>703</v>
+        <v>752</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>702</v>
+        <v>751</v>
       </c>
       <c r="B62" t="s">
-        <v>700</v>
+        <v>749</v>
       </c>
       <c r="C62" t="s">
-        <v>704</v>
+        <v>753</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>702</v>
+        <v>751</v>
       </c>
       <c r="B63" t="s">
-        <v>702</v>
+        <v>751</v>
       </c>
       <c r="C63" t="s">
-        <v>705</v>
+        <v>754</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>706</v>
+        <v>755</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>707</v>
+        <v>756</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>708</v>
+        <v>757</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>709</v>
+        <v>758</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>710</v>
+        <v>759</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>711</v>
+        <v>760</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>712</v>
+        <v>761</v>
       </c>
       <c r="B72" t="s">
-        <v>685</v>
+        <v>734</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -8789,7 +9216,7 @@
         <v>46024</v>
       </c>
       <c r="B73" t="s">
-        <v>713</v>
+        <v>762</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -8797,7 +9224,7 @@
         <v>46086</v>
       </c>
       <c r="B74" t="s">
-        <v>714</v>
+        <v>763</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -8805,30 +9232,30 @@
         <v>46183</v>
       </c>
       <c r="B75" t="s">
-        <v>715</v>
+        <v>764</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>716</v>
+        <v>765</v>
       </c>
       <c r="B76" t="s">
-        <v>717</v>
+        <v>766</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>718</v>
+        <v>767</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>719</v>
+        <v>768</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>720</v>
+        <v>769</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -8839,17 +9266,17 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>721</v>
+        <v>770</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>722</v>
+        <v>771</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>723</v>
+        <v>772</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -8862,26 +9289,26 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>724</v>
+        <v>773</v>
       </c>
       <c r="B91" t="s">
-        <v>725</v>
+        <v>774</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>726</v>
+        <v>775</v>
       </c>
       <c r="B92" t="s">
-        <v>727</v>
+        <v>776</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>728</v>
+        <v>777</v>
       </c>
       <c r="B93" t="s">
-        <v>729</v>
+        <v>778</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -8889,30 +9316,30 @@
         <v>213</v>
       </c>
       <c r="B94" t="s">
-        <v>730</v>
+        <v>779</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>731</v>
+        <v>780</v>
       </c>
       <c r="B95" t="s">
-        <v>732</v>
+        <v>781</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>733</v>
+        <v>782</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>734</v>
+        <v>783</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>735</v>
+        <v>784</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -8920,12 +9347,12 @@
         <v>155</v>
       </c>
       <c r="B101" t="s">
-        <v>736</v>
+        <v>785</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>737</v>
+        <v>786</v>
       </c>
       <c r="B102" s="2">
         <v>0.3</v>
@@ -8933,7 +9360,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>738</v>
+        <v>787</v>
       </c>
       <c r="B103" s="2">
         <v>0.25</v>
@@ -8941,7 +9368,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>739</v>
+        <v>788</v>
       </c>
       <c r="B104" s="2">
         <v>0.15</v>
@@ -8957,7 +9384,7 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>740</v>
+        <v>789</v>
       </c>
       <c r="B106" s="2">
         <v>0.15</v>
@@ -8965,70 +9392,70 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>741</v>
+        <v>790</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>742</v>
+        <v>791</v>
       </c>
       <c r="B108" t="s">
-        <v>743</v>
+        <v>792</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>744</v>
+        <v>793</v>
       </c>
       <c r="B109" t="s">
-        <v>745</v>
+        <v>794</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>746</v>
+        <v>795</v>
       </c>
       <c r="B110" t="s">
-        <v>747</v>
+        <v>796</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>748</v>
+        <v>797</v>
       </c>
       <c r="B111" t="s">
-        <v>749</v>
+        <v>798</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>750</v>
+        <v>799</v>
       </c>
       <c r="B112" t="s">
-        <v>751</v>
+        <v>800</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>752</v>
+        <v>801</v>
       </c>
       <c r="B113" t="s">
-        <v>753</v>
+        <v>802</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>754</v>
+        <v>803</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>755</v>
+        <v>804</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>756</v>
+        <v>805</v>
       </c>
       <c r="B118" t="s">
         <v>294</v>
@@ -9036,70 +9463,70 @@
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>757</v>
+        <v>806</v>
       </c>
       <c r="B119" t="s">
-        <v>758</v>
+        <v>807</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>759</v>
+        <v>808</v>
       </c>
       <c r="B120" t="s">
-        <v>760</v>
+        <v>809</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>761</v>
+        <v>810</v>
       </c>
       <c r="B121" t="s">
-        <v>762</v>
+        <v>811</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>763</v>
+        <v>812</v>
       </c>
       <c r="B122" t="s">
-        <v>764</v>
+        <v>813</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>765</v>
+        <v>814</v>
       </c>
       <c r="B123" t="s">
-        <v>766</v>
+        <v>815</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>767</v>
+        <v>816</v>
       </c>
       <c r="B124" t="s">
-        <v>768</v>
+        <v>817</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>769</v>
+        <v>818</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>770</v>
+        <v>819</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>771</v>
+        <v>820</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>772</v>
+        <v>821</v>
       </c>
     </row>
     <row r="131" spans="1:1">
@@ -9146,12 +9573,12 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>773</v>
+        <v>822</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>774</v>
+        <v>823</v>
       </c>
     </row>
     <row r="140" spans="1:1">
@@ -9198,12 +9625,12 @@
     </row>
     <row r="147" spans="1:1">
       <c r="A147" t="s">
-        <v>775</v>
+        <v>824</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>776</v>
+        <v>825</v>
       </c>
     </row>
     <row r="149" spans="1:1">
@@ -9238,192 +9665,192 @@
     </row>
     <row r="154" spans="1:1">
       <c r="A154" t="s">
-        <v>777</v>
+        <v>826</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>778</v>
+        <v>827</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>779</v>
+        <v>828</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>780</v>
+        <v>829</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>781</v>
+        <v>830</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>782</v>
+        <v>831</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>783</v>
+        <v>832</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>784</v>
+        <v>833</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>785</v>
+        <v>834</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>786</v>
+        <v>835</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>787</v>
+        <v>836</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>788</v>
+        <v>837</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>789</v>
+        <v>838</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>790</v>
+        <v>839</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" t="s">
-        <v>791</v>
+        <v>840</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>792</v>
+        <v>841</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>793</v>
+        <v>842</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" t="s">
-        <v>794</v>
+        <v>843</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" t="s">
-        <v>795</v>
+        <v>844</v>
       </c>
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>796</v>
+        <v>845</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>797</v>
+        <v>846</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>798</v>
+        <v>847</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>799</v>
+        <v>848</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>800</v>
+        <v>849</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>801</v>
+        <v>850</v>
       </c>
     </row>
     <row r="182" spans="1:1">
       <c r="A182" t="s">
-        <v>802</v>
+        <v>851</v>
       </c>
     </row>
     <row r="184" spans="1:1">
       <c r="A184" t="s">
-        <v>803</v>
+        <v>852</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" t="s">
-        <v>804</v>
+        <v>853</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>726</v>
+        <v>775</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>805</v>
+        <v>854</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>806</v>
+        <v>855</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" t="s">
-        <v>807</v>
+        <v>856</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" t="s">
-        <v>808</v>
+        <v>857</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>809</v>
+        <v>858</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>810</v>
+        <v>859</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" t="s">
-        <v>811</v>
+        <v>860</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" t="s">
-        <v>812</v>
+        <v>861</v>
       </c>
     </row>
     <row r="195" spans="1:1">
       <c r="A195" t="s">
-        <v>813</v>
+        <v>862</v>
       </c>
     </row>
     <row r="196" spans="1:1">
@@ -9433,117 +9860,117 @@
     </row>
     <row r="197" spans="1:1">
       <c r="A197" t="s">
-        <v>814</v>
+        <v>863</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" t="s">
-        <v>815</v>
+        <v>864</v>
       </c>
     </row>
     <row r="201" spans="1:1">
       <c r="A201" t="s">
-        <v>816</v>
+        <v>865</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" t="s">
-        <v>817</v>
+        <v>866</v>
       </c>
     </row>
     <row r="205" spans="1:1">
       <c r="A205" t="s">
-        <v>818</v>
+        <v>867</v>
       </c>
     </row>
     <row r="206" spans="1:1">
       <c r="A206" t="s">
-        <v>819</v>
+        <v>868</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" t="s">
-        <v>820</v>
+        <v>869</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" t="s">
-        <v>821</v>
+        <v>870</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" t="s">
-        <v>822</v>
+        <v>871</v>
       </c>
     </row>
     <row r="211" spans="1:1">
       <c r="A211" t="s">
-        <v>823</v>
+        <v>872</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" t="s">
-        <v>824</v>
+        <v>873</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" t="s">
-        <v>825</v>
+        <v>874</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" t="s">
-        <v>826</v>
+        <v>875</v>
       </c>
     </row>
     <row r="216" spans="1:1">
       <c r="A216" t="s">
-        <v>827</v>
+        <v>876</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" t="s">
-        <v>828</v>
+        <v>877</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" t="s">
-        <v>829</v>
+        <v>878</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" t="s">
-        <v>830</v>
+        <v>879</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" t="s">
-        <v>831</v>
+        <v>880</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" t="s">
-        <v>832</v>
+        <v>881</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" t="s">
-        <v>833</v>
+        <v>882</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" t="s">
-        <v>834</v>
+        <v>883</v>
       </c>
     </row>
     <row r="228" spans="1:1">
       <c r="A228" t="s">
-        <v>835</v>
+        <v>884</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" t="s">
-        <v>836</v>
+        <v>885</v>
       </c>
     </row>
   </sheetData>
